--- a/Asignación Proyectos/3. Output/Propuesta_Reasignacion_PM_Blend360.xlsx
+++ b/Asignación Proyectos/3. Output/Propuesta_Reasignacion_PM_Blend360.xlsx
@@ -881,7 +881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L180"/>
+  <dimension ref="A1:L183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3747,7 +3747,7 @@
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="21" t="inlineStr">
         <is>
-          <t>▶  Diana Rojas  –  15 sub-proyectos  |  ~156h est./mes  (80% capacidad)</t>
+          <t>▶  Diana Rojas  –  18 sub-proyectos  |  ~156h est./mes  (81% capacidad)</t>
         </is>
       </c>
     </row>
@@ -3788,13 +3788,13 @@
         </is>
       </c>
       <c r="H58" s="8" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="I58" s="18" t="n">
-        <v>0.09699999999999999</v>
+        <v>9.4</v>
+      </c>
+      <c r="I58" s="9" t="n">
+        <v>0.049</v>
       </c>
       <c r="J58" s="8" t="n">
-        <v>1650.9</v>
+        <v>825.5</v>
       </c>
       <c r="K58" s="10" t="inlineStr">
         <is>
@@ -3844,13 +3844,13 @@
         </is>
       </c>
       <c r="H59" s="8" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="I59" s="18" t="n">
-        <v>0.09699999999999999</v>
+        <v>9.4</v>
+      </c>
+      <c r="I59" s="9" t="n">
+        <v>0.049</v>
       </c>
       <c r="J59" s="8" t="n">
-        <v>1650.9</v>
+        <v>825.5</v>
       </c>
       <c r="K59" s="10" t="inlineStr">
         <is>
@@ -3900,13 +3900,13 @@
         </is>
       </c>
       <c r="H60" s="14" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="I60" s="18" t="n">
-        <v>0.09699999999999999</v>
+        <v>9.4</v>
+      </c>
+      <c r="I60" s="9" t="n">
+        <v>0.049</v>
       </c>
       <c r="J60" s="14" t="n">
-        <v>1650.9</v>
+        <v>825.5</v>
       </c>
       <c r="K60" s="15" t="inlineStr">
         <is>
@@ -3956,13 +3956,13 @@
         </is>
       </c>
       <c r="H61" s="8" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="I61" s="18" t="n">
-        <v>0.09699999999999999</v>
+        <v>9.4</v>
+      </c>
+      <c r="I61" s="9" t="n">
+        <v>0.049</v>
       </c>
       <c r="J61" s="8" t="n">
-        <v>1650.9</v>
+        <v>825.5</v>
       </c>
       <c r="K61" s="10" t="inlineStr">
         <is>
@@ -4012,13 +4012,13 @@
         </is>
       </c>
       <c r="H62" s="14" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="I62" s="18" t="n">
-        <v>0.09699999999999999</v>
+        <v>9.4</v>
+      </c>
+      <c r="I62" s="9" t="n">
+        <v>0.049</v>
       </c>
       <c r="J62" s="14" t="n">
-        <v>1650.9</v>
+        <v>825.5</v>
       </c>
       <c r="K62" s="15" t="inlineStr">
         <is>
@@ -4039,42 +4039,42 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>P1949</t>
+          <t>P2847</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>MMN</t>
+          <t>ADR</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>MMN - Cloud Sistema de Recaudo - Fixed</t>
+          <t>ADR - peración Auditoria Cuentas Medicas - Ret</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>Empresa De Transporte Masivo Del Valle De Aburrá Limitada</t>
+          <t>La Administradora de los Recursos del Sistema General de Seguridad Social en Salud</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>Implementación</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Ret</t>
         </is>
       </c>
       <c r="H63" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="I63" s="9" t="n">
-        <v>0.015</v>
+        <v>15.7</v>
+      </c>
+      <c r="I63" s="18" t="n">
+        <v>0.081</v>
       </c>
       <c r="J63" s="8" t="n">
-        <v>215.8</v>
+        <v>1375.8</v>
       </c>
       <c r="K63" s="10" t="inlineStr">
         <is>
@@ -4095,22 +4095,22 @@
       </c>
       <c r="B64" s="12" t="inlineStr">
         <is>
-          <t>P1950</t>
+          <t>P2848</t>
         </is>
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>MMN</t>
+          <t>ADR</t>
         </is>
       </c>
       <c r="D64" s="13" t="inlineStr">
         <is>
-          <t>MMN - Cloud Sistema de Recaudo - Cloud</t>
+          <t>ADR - peración Auditoria Cuentas Medicas - Cloud</t>
         </is>
       </c>
       <c r="E64" s="13" t="inlineStr">
         <is>
-          <t>Empresa De Transporte Masivo Del Valle De Aburrá Limitada</t>
+          <t>La Administradora de los Recursos del Sistema General de Seguridad Social en Salud</t>
         </is>
       </c>
       <c r="F64" s="12" t="inlineStr">
@@ -4124,13 +4124,13 @@
         </is>
       </c>
       <c r="H64" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="I64" s="9" t="n">
-        <v>0.015</v>
+        <v>15.7</v>
+      </c>
+      <c r="I64" s="18" t="n">
+        <v>0.081</v>
       </c>
       <c r="J64" s="14" t="n">
-        <v>215.8</v>
+        <v>1375.8</v>
       </c>
       <c r="K64" s="15" t="inlineStr">
         <is>
@@ -4151,42 +4151,42 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>P2225</t>
+          <t>P2849</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>MMN</t>
+          <t>ADR</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>MMN - Cloud Sistema de Recaudo - Ret Other Vendors</t>
+          <t>ADR - peración Auditoria Cuentas Medicas - Ret Sw</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>Empresa De Transporte Masivo Del Valle De Aburrá Limitada</t>
+          <t>La Administradora de los Recursos del Sistema General de Seguridad Social en Salud</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>Operación</t>
+          <t>Software SW</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>Ret Other Vendors</t>
+          <t>Ret Sw</t>
         </is>
       </c>
       <c r="H65" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="I65" s="9" t="n">
-        <v>0.015</v>
+        <v>15.7</v>
+      </c>
+      <c r="I65" s="18" t="n">
+        <v>0.081</v>
       </c>
       <c r="J65" s="8" t="n">
-        <v>215.8</v>
+        <v>1375.8</v>
       </c>
       <c r="K65" s="10" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="B66" s="12" t="inlineStr">
         <is>
-          <t>P2310</t>
+          <t>P1949</t>
         </is>
       </c>
       <c r="C66" s="12" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="D66" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">MMN - Cloud Sistema de Recaudo - Ret </t>
+          <t>MMN - Cloud Sistema de Recaudo - Fixed</t>
         </is>
       </c>
       <c r="E66" s="13" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="F66" s="12" t="inlineStr">
         <is>
-          <t>Operación</t>
+          <t>Implementación</t>
         </is>
       </c>
       <c r="G66" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ret </t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H66" s="14" t="n">
@@ -4263,51 +4263,51 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>P2723</t>
+          <t>P1950</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>SPD</t>
+          <t>MMN</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>SPD - Renovacion observatorio de datos- - Fixed</t>
+          <t>MMN - Cloud Sistema de Recaudo - Cloud</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>Superintendencia Servicios Públicos Domiciliarios</t>
+          <t>Empresa De Transporte Masivo Del Valle De Aburrá Limitada</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>Implementación</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="H67" s="8" t="n">
-        <v>6.2</v>
+        <v>3</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>0.032</v>
+        <v>0.015</v>
       </c>
       <c r="J67" s="8" t="n">
-        <v>103.1</v>
-      </c>
-      <c r="K67" s="19" t="inlineStr">
-        <is>
-          <t>🔄 Reasignado</t>
+        <v>215.8</v>
+      </c>
+      <c r="K67" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>Miguel Garcia</t>
+          <t>Diana Rojas</t>
         </is>
       </c>
     </row>
@@ -4319,51 +4319,51 @@
       </c>
       <c r="B68" s="12" t="inlineStr">
         <is>
-          <t>P2724</t>
+          <t>P2225</t>
         </is>
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>SPD</t>
+          <t>MMN</t>
         </is>
       </c>
       <c r="D68" s="13" t="inlineStr">
         <is>
-          <t>SPD - Renovacion observatorio de datos- - Ret SW</t>
+          <t>MMN - Cloud Sistema de Recaudo - Ret Other Vendors</t>
         </is>
       </c>
       <c r="E68" s="13" t="inlineStr">
         <is>
-          <t>Superintendencia Servicios Públicos Domiciliarios</t>
+          <t>Empresa De Transporte Masivo Del Valle De Aburrá Limitada</t>
         </is>
       </c>
       <c r="F68" s="12" t="inlineStr">
         <is>
-          <t>Software SW</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="G68" s="12" t="inlineStr">
         <is>
-          <t>Ret SW</t>
+          <t>Ret Other Vendors</t>
         </is>
       </c>
       <c r="H68" s="14" t="n">
-        <v>6.2</v>
+        <v>3</v>
       </c>
       <c r="I68" s="9" t="n">
-        <v>0.032</v>
+        <v>0.015</v>
       </c>
       <c r="J68" s="14" t="n">
-        <v>103.1</v>
-      </c>
-      <c r="K68" s="19" t="inlineStr">
-        <is>
-          <t>🔄 Reasignado</t>
+        <v>215.8</v>
+      </c>
+      <c r="K68" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="L68" s="11" t="inlineStr">
         <is>
-          <t>Miguel Garcia</t>
+          <t>Diana Rojas</t>
         </is>
       </c>
     </row>
@@ -4375,51 +4375,51 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>P2725</t>
+          <t>P2310</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>SPD</t>
+          <t>MMN</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>SPD - Renovacion observatorio de datos- - Cloud</t>
+          <t xml:space="preserve">MMN - Cloud Sistema de Recaudo - Ret </t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>Superintendencia Servicios Públicos Domiciliarios</t>
+          <t>Empresa De Transporte Masivo Del Valle De Aburrá Limitada</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t xml:space="preserve">Ret </t>
         </is>
       </c>
       <c r="H69" s="8" t="n">
-        <v>6.2</v>
+        <v>3</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>0.032</v>
+        <v>0.015</v>
       </c>
       <c r="J69" s="8" t="n">
-        <v>103.1</v>
-      </c>
-      <c r="K69" s="19" t="inlineStr">
-        <is>
-          <t>🔄 Reasignado</t>
+        <v>215.8</v>
+      </c>
+      <c r="K69" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="L69" s="5" t="inlineStr">
         <is>
-          <t>Miguel Garcia</t>
+          <t>Diana Rojas</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="B70" s="12" t="inlineStr">
         <is>
-          <t>P2726</t>
+          <t>P2723</t>
         </is>
       </c>
       <c r="C70" s="12" t="inlineStr">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="D70" s="13" t="inlineStr">
         <is>
-          <t>SPD - Renovacion observatorio de datos- - Ret</t>
+          <t>SPD - Renovacion observatorio de datos- - Fixed</t>
         </is>
       </c>
       <c r="E70" s="13" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="F70" s="12" t="inlineStr">
         <is>
-          <t>Operación</t>
+          <t>Implementación</t>
         </is>
       </c>
       <c r="G70" s="12" t="inlineStr">
         <is>
-          <t>Ret</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H70" s="14" t="n">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>P1966</t>
+          <t>P2724</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>SPD - Repositorio Único de Datos - Ret SW</t>
+          <t>SPD - Renovacion observatorio de datos- - Ret SW</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
@@ -4516,13 +4516,13 @@
         </is>
       </c>
       <c r="H71" s="8" t="n">
-        <v>12.5</v>
+        <v>6.2</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>0.065</v>
+        <v>0.032</v>
       </c>
       <c r="J71" s="8" t="n">
-        <v>206.1</v>
+        <v>103.1</v>
       </c>
       <c r="K71" s="19" t="inlineStr">
         <is>
@@ -4543,343 +4543,343 @@
       </c>
       <c r="B72" s="12" t="inlineStr">
         <is>
+          <t>P2725</t>
+        </is>
+      </c>
+      <c r="C72" s="12" t="inlineStr">
+        <is>
+          <t>SPD</t>
+        </is>
+      </c>
+      <c r="D72" s="13" t="inlineStr">
+        <is>
+          <t>SPD - Renovacion observatorio de datos- - Cloud</t>
+        </is>
+      </c>
+      <c r="E72" s="13" t="inlineStr">
+        <is>
+          <t>Superintendencia Servicios Públicos Domiciliarios</t>
+        </is>
+      </c>
+      <c r="F72" s="12" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="G72" s="12" t="inlineStr">
+        <is>
+          <t>Cloud</t>
+        </is>
+      </c>
+      <c r="H72" s="14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I72" s="9" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="J72" s="14" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="K72" s="19" t="inlineStr">
+        <is>
+          <t>🔄 Reasignado</t>
+        </is>
+      </c>
+      <c r="L72" s="11" t="inlineStr">
+        <is>
+          <t>Miguel Garcia</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="18" customHeight="1">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>Diana Rojas</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>P2726</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>SPD</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>SPD - Renovacion observatorio de datos- - Ret</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>Superintendencia Servicios Públicos Domiciliarios</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>Operación</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>Ret</t>
+        </is>
+      </c>
+      <c r="H73" s="8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I73" s="9" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="J73" s="8" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="K73" s="19" t="inlineStr">
+        <is>
+          <t>🔄 Reasignado</t>
+        </is>
+      </c>
+      <c r="L73" s="5" t="inlineStr">
+        <is>
+          <t>Miguel Garcia</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="18" customHeight="1">
+      <c r="A74" s="11" t="inlineStr">
+        <is>
+          <t>Diana Rojas</t>
+        </is>
+      </c>
+      <c r="B74" s="12" t="inlineStr">
+        <is>
+          <t>P1966</t>
+        </is>
+      </c>
+      <c r="C74" s="12" t="inlineStr">
+        <is>
+          <t>SPD</t>
+        </is>
+      </c>
+      <c r="D74" s="13" t="inlineStr">
+        <is>
+          <t>SPD - Repositorio Único de Datos - Ret SW</t>
+        </is>
+      </c>
+      <c r="E74" s="13" t="inlineStr">
+        <is>
+          <t>Superintendencia Servicios Públicos Domiciliarios</t>
+        </is>
+      </c>
+      <c r="F74" s="12" t="inlineStr">
+        <is>
+          <t>Software SW</t>
+        </is>
+      </c>
+      <c r="G74" s="12" t="inlineStr">
+        <is>
+          <t>Ret SW</t>
+        </is>
+      </c>
+      <c r="H74" s="14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I74" s="9" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="J74" s="14" t="n">
+        <v>206.1</v>
+      </c>
+      <c r="K74" s="19" t="inlineStr">
+        <is>
+          <t>🔄 Reasignado</t>
+        </is>
+      </c>
+      <c r="L74" s="11" t="inlineStr">
+        <is>
+          <t>Miguel Garcia</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="18" customHeight="1">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>Diana Rojas</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
           <t>P1967</t>
         </is>
       </c>
-      <c r="C72" s="12" t="inlineStr">
+      <c r="C75" s="6" t="inlineStr">
         <is>
           <t>SPD</t>
         </is>
       </c>
-      <c r="D72" s="13" t="inlineStr">
+      <c r="D75" s="7" t="inlineStr">
         <is>
           <t>SPD - Repositorio Único de Datos - Cloud</t>
         </is>
       </c>
-      <c r="E72" s="13" t="inlineStr">
+      <c r="E75" s="7" t="inlineStr">
         <is>
           <t>Superintendencia Servicios Públicos Domiciliarios</t>
         </is>
       </c>
-      <c r="F72" s="12" t="inlineStr">
+      <c r="F75" s="6" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="G72" s="12" t="inlineStr">
+      <c r="G75" s="6" t="inlineStr">
         <is>
           <t>Cloud</t>
         </is>
       </c>
-      <c r="H72" s="14" t="n">
+      <c r="H75" s="8" t="n">
         <v>12.5</v>
       </c>
-      <c r="I72" s="9" t="n">
+      <c r="I75" s="9" t="n">
         <v>0.065</v>
       </c>
-      <c r="J72" s="14" t="n">
+      <c r="J75" s="8" t="n">
         <v>206.1</v>
       </c>
-      <c r="K72" s="19" t="inlineStr">
+      <c r="K75" s="19" t="inlineStr">
         <is>
           <t>🔄 Reasignado</t>
         </is>
       </c>
-      <c r="L72" s="11" t="inlineStr">
+      <c r="L75" s="5" t="inlineStr">
         <is>
           <t>Miguel Garcia</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="22" customHeight="1">
-      <c r="A73" s="22" t="inlineStr">
+    <row r="76" ht="22" customHeight="1">
+      <c r="A76" s="22" t="inlineStr">
         <is>
           <t>▶  Fernando Ortega  –  1 sub-proyectos  |  ~4h est./mes  (2% capacidad)</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="18" customHeight="1">
-      <c r="A74" s="5" t="inlineStr">
+    <row r="77" ht="18" customHeight="1">
+      <c r="A77" s="11" t="inlineStr">
         <is>
           <t>Fernando Ortega</t>
         </is>
       </c>
-      <c r="B74" s="6" t="inlineStr">
+      <c r="B77" s="12" t="inlineStr">
         <is>
           <t>P2083</t>
         </is>
       </c>
-      <c r="C74" s="6" t="inlineStr">
+      <c r="C77" s="12" t="inlineStr">
         <is>
           <t>BLD</t>
         </is>
       </c>
-      <c r="D74" s="7" t="inlineStr">
+      <c r="D77" s="13" t="inlineStr">
         <is>
           <t>BLD - Producto - Houndoc - Internal</t>
         </is>
       </c>
-      <c r="E74" s="7" t="inlineStr">
+      <c r="E77" s="13" t="inlineStr">
         <is>
           <t>Blend360</t>
         </is>
       </c>
-      <c r="F74" s="6" t="inlineStr">
+      <c r="F77" s="12" t="inlineStr">
         <is>
           <t>Interno</t>
         </is>
       </c>
-      <c r="G74" s="6" t="inlineStr">
+      <c r="G77" s="12" t="inlineStr">
         <is>
           <t>Internal</t>
         </is>
       </c>
-      <c r="H74" s="8" t="n">
+      <c r="H77" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="I74" s="9" t="n">
+      <c r="I77" s="9" t="n">
         <v>0.021</v>
       </c>
-      <c r="J74" s="8" t="n">
+      <c r="J77" s="14" t="n">
         <v>1691</v>
       </c>
-      <c r="K74" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L74" s="5" t="inlineStr">
+      <c r="K77" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L77" s="11" t="inlineStr">
         <is>
           <t>Fernando Ortega</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="22" customHeight="1">
-      <c r="A75" s="23" t="inlineStr">
+    <row r="78" ht="22" customHeight="1">
+      <c r="A78" s="23" t="inlineStr">
         <is>
           <t>▶  Juan Bernal  –  28 sub-proyectos  |  ~149h est./mes  (77% capacidad)</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="18" customHeight="1">
-      <c r="A76" s="5" t="inlineStr">
+    <row r="79" ht="18" customHeight="1">
+      <c r="A79" s="11" t="inlineStr">
         <is>
           <t>Juan Bernal</t>
         </is>
       </c>
-      <c r="B76" s="6" t="inlineStr">
+      <c r="B79" s="12" t="inlineStr">
         <is>
           <t>P2615</t>
         </is>
       </c>
-      <c r="C76" s="6" t="inlineStr">
+      <c r="C79" s="12" t="inlineStr">
         <is>
           <t>CJU</t>
         </is>
       </c>
-      <c r="D76" s="7" t="inlineStr">
+      <c r="D79" s="13" t="inlineStr">
         <is>
           <t>CJU - CJU - Localizados - Cloud</t>
         </is>
       </c>
-      <c r="E76" s="7" t="inlineStr">
+      <c r="E79" s="13" t="inlineStr">
         <is>
           <t>Coljuegos</t>
         </is>
       </c>
-      <c r="F76" s="6" t="inlineStr">
+      <c r="F79" s="12" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="G76" s="6" t="inlineStr">
+      <c r="G79" s="12" t="inlineStr">
         <is>
           <t>Cloud</t>
         </is>
       </c>
-      <c r="H76" s="8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="I76" s="9" t="n">
-        <v>0.006999999999999999</v>
-      </c>
-      <c r="J76" s="8" t="n">
-        <v>76.5</v>
-      </c>
-      <c r="K76" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L76" s="5" t="inlineStr">
-        <is>
-          <t>Juan Bernal</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="18" customHeight="1">
-      <c r="A77" s="5" t="inlineStr">
-        <is>
-          <t>Juan Bernal</t>
-        </is>
-      </c>
-      <c r="B77" s="6" t="inlineStr">
-        <is>
-          <t>P2616</t>
-        </is>
-      </c>
-      <c r="C77" s="6" t="inlineStr">
-        <is>
-          <t>CJU</t>
-        </is>
-      </c>
-      <c r="D77" s="7" t="inlineStr">
-        <is>
-          <t>CJU - CJU - Localizados - Fixed</t>
-        </is>
-      </c>
-      <c r="E77" s="7" t="inlineStr">
-        <is>
-          <t>Coljuegos</t>
-        </is>
-      </c>
-      <c r="F77" s="6" t="inlineStr">
-        <is>
-          <t>Implementación</t>
-        </is>
-      </c>
-      <c r="G77" s="6" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="H77" s="8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="I77" s="9" t="n">
-        <v>0.006999999999999999</v>
-      </c>
-      <c r="J77" s="8" t="n">
-        <v>76.5</v>
-      </c>
-      <c r="K77" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L77" s="5" t="inlineStr">
-        <is>
-          <t>Juan Bernal</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="18" customHeight="1">
-      <c r="A78" s="11" t="inlineStr">
-        <is>
-          <t>Juan Bernal</t>
-        </is>
-      </c>
-      <c r="B78" s="12" t="inlineStr">
-        <is>
-          <t>P2617</t>
-        </is>
-      </c>
-      <c r="C78" s="12" t="inlineStr">
-        <is>
-          <t>CJU</t>
-        </is>
-      </c>
-      <c r="D78" s="13" t="inlineStr">
-        <is>
-          <t>CJU - CJU - Localizados - Ret</t>
-        </is>
-      </c>
-      <c r="E78" s="13" t="inlineStr">
-        <is>
-          <t>Coljuegos</t>
-        </is>
-      </c>
-      <c r="F78" s="12" t="inlineStr">
-        <is>
-          <t>Operación</t>
-        </is>
-      </c>
-      <c r="G78" s="12" t="inlineStr">
-        <is>
-          <t>Ret</t>
-        </is>
-      </c>
-      <c r="H78" s="14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="I78" s="9" t="n">
-        <v>0.006999999999999999</v>
-      </c>
-      <c r="J78" s="14" t="n">
-        <v>76.5</v>
-      </c>
-      <c r="K78" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L78" s="11" t="inlineStr">
-        <is>
-          <t>Juan Bernal</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="18" customHeight="1">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t>Juan Bernal</t>
-        </is>
-      </c>
-      <c r="B79" s="6" t="inlineStr">
-        <is>
-          <t>P2618</t>
-        </is>
-      </c>
-      <c r="C79" s="6" t="inlineStr">
-        <is>
-          <t>CJU</t>
-        </is>
-      </c>
-      <c r="D79" s="7" t="inlineStr">
-        <is>
-          <t>CJU - CJU - Localizados - Ret SW</t>
-        </is>
-      </c>
-      <c r="E79" s="7" t="inlineStr">
-        <is>
-          <t>Coljuegos</t>
-        </is>
-      </c>
-      <c r="F79" s="6" t="inlineStr">
-        <is>
-          <t>Software SW</t>
-        </is>
-      </c>
-      <c r="G79" s="6" t="inlineStr">
-        <is>
-          <t>Ret SW</t>
-        </is>
-      </c>
-      <c r="H79" s="8" t="n">
+      <c r="H79" s="14" t="n">
         <v>1.4</v>
       </c>
       <c r="I79" s="9" t="n">
         <v>0.006999999999999999</v>
       </c>
-      <c r="J79" s="8" t="n">
+      <c r="J79" s="14" t="n">
         <v>76.5</v>
       </c>
-      <c r="K79" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L79" s="5" t="inlineStr">
+      <c r="K79" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="11" t="inlineStr">
         <is>
           <t>Juan Bernal</t>
         </is>
@@ -4893,7 +4893,7 @@
       </c>
       <c r="B80" s="12" t="inlineStr">
         <is>
-          <t>P2619</t>
+          <t>P2616</t>
         </is>
       </c>
       <c r="C80" s="12" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="D80" s="13" t="inlineStr">
         <is>
-          <t>CJU - CJU - STecnica - Cloud</t>
+          <t>CJU - CJU - Localizados - Fixed</t>
         </is>
       </c>
       <c r="E80" s="13" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="F80" s="12" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Implementación</t>
         </is>
       </c>
       <c r="G80" s="12" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H80" s="14" t="n">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>P2620</t>
+          <t>P2617</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>CJU - CJU - STecnica - Fixed</t>
+          <t>CJU - CJU - Localizados - Ret</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
@@ -4969,12 +4969,12 @@
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>Implementación</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Ret</t>
         </is>
       </c>
       <c r="H81" s="8" t="n">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="B82" s="12" t="inlineStr">
         <is>
-          <t>P2621</t>
+          <t>P2618</t>
         </is>
       </c>
       <c r="C82" s="12" t="inlineStr">
@@ -5015,7 +5015,7 @@
       </c>
       <c r="D82" s="13" t="inlineStr">
         <is>
-          <t>CJU - CJU - STecnica - Ret</t>
+          <t>CJU - CJU - Localizados - Ret SW</t>
         </is>
       </c>
       <c r="E82" s="13" t="inlineStr">
@@ -5025,12 +5025,12 @@
       </c>
       <c r="F82" s="12" t="inlineStr">
         <is>
-          <t>Operación</t>
+          <t>Software SW</t>
         </is>
       </c>
       <c r="G82" s="12" t="inlineStr">
         <is>
-          <t>Ret</t>
+          <t>Ret SW</t>
         </is>
       </c>
       <c r="H82" s="14" t="n">
@@ -5061,7 +5061,7 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>P2622</t>
+          <t>P2619</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>CJU - CJU - STecnica - Ret SW</t>
+          <t>CJU - CJU - STecnica - Cloud</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="F83" s="6" t="inlineStr">
         <is>
-          <t>Software SW</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
-          <t>Ret SW</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="H83" s="8" t="n">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="B84" s="12" t="inlineStr">
         <is>
-          <t>P2019</t>
+          <t>P2620</t>
         </is>
       </c>
       <c r="C84" s="12" t="inlineStr">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="D84" s="13" t="inlineStr">
         <is>
-          <t>CJU - Vigilancia y MET Plus - Fixed</t>
+          <t>CJU - CJU - STecnica - Fixed</t>
         </is>
       </c>
       <c r="E84" s="13" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>P2020</t>
+          <t>P2621</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>CJU - Vigilancia y MET Plus - Cloud</t>
+          <t>CJU - CJU - STecnica - Ret</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
@@ -5193,12 +5193,12 @@
       </c>
       <c r="F85" s="6" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>Ret</t>
         </is>
       </c>
       <c r="H85" s="8" t="n">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="B86" s="12" t="inlineStr">
         <is>
-          <t>P2021</t>
+          <t>P2622</t>
         </is>
       </c>
       <c r="C86" s="12" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="D86" s="13" t="inlineStr">
         <is>
-          <t>CJU - Vigilancia y MET Plus - Ret</t>
+          <t>CJU - CJU - STecnica - Ret SW</t>
         </is>
       </c>
       <c r="E86" s="13" t="inlineStr">
@@ -5249,12 +5249,12 @@
       </c>
       <c r="F86" s="12" t="inlineStr">
         <is>
-          <t>Operación</t>
+          <t>Software SW</t>
         </is>
       </c>
       <c r="G86" s="12" t="inlineStr">
         <is>
-          <t>Ret</t>
+          <t>Ret SW</t>
         </is>
       </c>
       <c r="H86" s="14" t="n">
@@ -5285,7 +5285,7 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>P2022</t>
+          <t>P2019</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
@@ -5295,7 +5295,7 @@
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>CJU - Vigilancia y MET Plus - Ret SW</t>
+          <t>CJU - Vigilancia y MET Plus - Fixed</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
@@ -5305,12 +5305,12 @@
       </c>
       <c r="F87" s="6" t="inlineStr">
         <is>
-          <t>Software SW</t>
+          <t>Implementación</t>
         </is>
       </c>
       <c r="G87" s="6" t="inlineStr">
         <is>
-          <t>Ret SW</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H87" s="8" t="n">
@@ -5341,22 +5341,22 @@
       </c>
       <c r="B88" s="12" t="inlineStr">
         <is>
-          <t>P1932</t>
+          <t>P2020</t>
         </is>
       </c>
       <c r="C88" s="12" t="inlineStr">
         <is>
-          <t>DIA</t>
+          <t>CJU</t>
         </is>
       </c>
       <c r="D88" s="13" t="inlineStr">
         <is>
-          <t>DIA - Aprovisionamiento multinube - Lote 3 - Cloud</t>
+          <t>CJU - Vigilancia y MET Plus - Cloud</t>
         </is>
       </c>
       <c r="E88" s="13" t="inlineStr">
         <is>
-          <t>DIAN</t>
+          <t>Coljuegos</t>
         </is>
       </c>
       <c r="F88" s="12" t="inlineStr">
@@ -5370,13 +5370,13 @@
         </is>
       </c>
       <c r="H88" s="14" t="n">
-        <v>20</v>
-      </c>
-      <c r="I88" s="18" t="n">
-        <v>0.103</v>
+        <v>1.4</v>
+      </c>
+      <c r="I88" s="9" t="n">
+        <v>0.006999999999999999</v>
       </c>
       <c r="J88" s="14" t="n">
-        <v>65.5</v>
+        <v>76.5</v>
       </c>
       <c r="K88" s="15" t="inlineStr">
         <is>
@@ -5397,22 +5397,22 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>P2729</t>
+          <t>P2021</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>CJU</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>ICF - Banco de items Fase 2 - Ret</t>
+          <t>CJU - Vigilancia y MET Plus - Ret</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>Icfes</t>
+          <t>Coljuegos</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr">
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="H89" s="8" t="n">
-        <v>5.7</v>
+        <v>1.4</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>0.029</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="J89" s="8" t="n">
-        <v>64.5</v>
+        <v>76.5</v>
       </c>
       <c r="K89" s="10" t="inlineStr">
         <is>
@@ -5453,42 +5453,42 @@
       </c>
       <c r="B90" s="12" t="inlineStr">
         <is>
-          <t>P2730</t>
+          <t>P2022</t>
         </is>
       </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>CJU</t>
         </is>
       </c>
       <c r="D90" s="13" t="inlineStr">
         <is>
-          <t>ICF - Banco de items Fase 2 - Ret Other Vendors</t>
+          <t>CJU - Vigilancia y MET Plus - Ret SW</t>
         </is>
       </c>
       <c r="E90" s="13" t="inlineStr">
         <is>
-          <t>Icfes</t>
+          <t>Coljuegos</t>
         </is>
       </c>
       <c r="F90" s="12" t="inlineStr">
         <is>
-          <t>Operación</t>
+          <t>Software SW</t>
         </is>
       </c>
       <c r="G90" s="12" t="inlineStr">
         <is>
-          <t>Ret Other Vendors</t>
+          <t>Ret SW</t>
         </is>
       </c>
       <c r="H90" s="14" t="n">
-        <v>5.7</v>
+        <v>1.4</v>
       </c>
       <c r="I90" s="9" t="n">
-        <v>0.029</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="J90" s="14" t="n">
-        <v>64.5</v>
+        <v>76.5</v>
       </c>
       <c r="K90" s="15" t="inlineStr">
         <is>
@@ -5509,22 +5509,22 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>P2731</t>
+          <t>P1932</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>DIA</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>ICF - Banco de items Fase 2 - Cloud</t>
+          <t>DIA - Aprovisionamiento multinube - Lote 3 - Cloud</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>Icfes</t>
+          <t>DIAN</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="H91" s="8" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="I91" s="9" t="n">
-        <v>0.029</v>
+        <v>20</v>
+      </c>
+      <c r="I91" s="18" t="n">
+        <v>0.103</v>
       </c>
       <c r="J91" s="8" t="n">
-        <v>64.5</v>
+        <v>65.5</v>
       </c>
       <c r="K91" s="10" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="B92" s="12" t="inlineStr">
         <is>
-          <t>P2742</t>
+          <t>P2729</t>
         </is>
       </c>
       <c r="C92" s="12" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="D92" s="13" t="inlineStr">
         <is>
-          <t>ICF - Citación con Georreferenciación - Fixed</t>
+          <t>ICF - Banco de items Fase 2 - Ret</t>
         </is>
       </c>
       <c r="E92" s="13" t="inlineStr">
@@ -5585,22 +5585,22 @@
       </c>
       <c r="F92" s="12" t="inlineStr">
         <is>
-          <t>Implementación</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="G92" s="12" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Ret</t>
         </is>
       </c>
       <c r="H92" s="14" t="n">
-        <v>3.4</v>
+        <v>5.7</v>
       </c>
       <c r="I92" s="9" t="n">
-        <v>0.018</v>
+        <v>0.029</v>
       </c>
       <c r="J92" s="14" t="n">
-        <v>38.7</v>
+        <v>64.5</v>
       </c>
       <c r="K92" s="15" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>P2744</t>
+          <t>P2730</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>ICF - Citación con Georreferenciación - Ret</t>
+          <t>ICF - Banco de items Fase 2 - Ret Other Vendors</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr">
@@ -5646,17 +5646,17 @@
       </c>
       <c r="G93" s="6" t="inlineStr">
         <is>
-          <t>Ret</t>
+          <t>Ret Other Vendors</t>
         </is>
       </c>
       <c r="H93" s="8" t="n">
-        <v>3.4</v>
+        <v>5.7</v>
       </c>
       <c r="I93" s="9" t="n">
-        <v>0.018</v>
+        <v>0.029</v>
       </c>
       <c r="J93" s="8" t="n">
-        <v>38.7</v>
+        <v>64.5</v>
       </c>
       <c r="K93" s="10" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
       </c>
       <c r="B94" s="12" t="inlineStr">
         <is>
-          <t>P2745</t>
+          <t>P2731</t>
         </is>
       </c>
       <c r="C94" s="12" t="inlineStr">
@@ -5687,7 +5687,7 @@
       </c>
       <c r="D94" s="13" t="inlineStr">
         <is>
-          <t>ICF - Citación con Georreferenciación - Ret SW</t>
+          <t>ICF - Banco de items Fase 2 - Cloud</t>
         </is>
       </c>
       <c r="E94" s="13" t="inlineStr">
@@ -5697,22 +5697,22 @@
       </c>
       <c r="F94" s="12" t="inlineStr">
         <is>
-          <t>Software SW</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="G94" s="12" t="inlineStr">
         <is>
-          <t>Ret SW</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="H94" s="14" t="n">
-        <v>3.4</v>
+        <v>5.7</v>
       </c>
       <c r="I94" s="9" t="n">
-        <v>0.018</v>
+        <v>0.029</v>
       </c>
       <c r="J94" s="14" t="n">
-        <v>38.7</v>
+        <v>64.5</v>
       </c>
       <c r="K94" s="15" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>P2746</t>
+          <t>P2742</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
@@ -5743,7 +5743,7 @@
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>ICF - Citación con Georreferenciación - Other Vendors</t>
+          <t>ICF - Citación con Georreferenciación - Fixed</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="F95" s="6" t="inlineStr">
         <is>
-          <t>Operación</t>
+          <t>Implementación</t>
         </is>
       </c>
       <c r="G95" s="6" t="inlineStr">
         <is>
-          <t>Other Vendors</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H95" s="8" t="n">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="B96" s="12" t="inlineStr">
         <is>
-          <t>P2747</t>
+          <t>P2744</t>
         </is>
       </c>
       <c r="C96" s="12" t="inlineStr">
@@ -5799,7 +5799,7 @@
       </c>
       <c r="D96" s="13" t="inlineStr">
         <is>
-          <t>ICF - Citación con Georreferenciación - Cloud</t>
+          <t>ICF - Citación con Georreferenciación - Ret</t>
         </is>
       </c>
       <c r="E96" s="13" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="F96" s="12" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="G96" s="12" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>Ret</t>
         </is>
       </c>
       <c r="H96" s="14" t="n">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>P2732</t>
+          <t>P2745</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
@@ -5855,7 +5855,7 @@
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>ICF - Datalake 2026-1 - Ret</t>
+          <t>ICF - Citación con Georreferenciación - Ret SW</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
@@ -5865,22 +5865,22 @@
       </c>
       <c r="F97" s="6" t="inlineStr">
         <is>
-          <t>Operación</t>
+          <t>Software SW</t>
         </is>
       </c>
       <c r="G97" s="6" t="inlineStr">
         <is>
-          <t>Ret</t>
+          <t>Ret SW</t>
         </is>
       </c>
       <c r="H97" s="8" t="n">
-        <v>5.7</v>
+        <v>3.4</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>0.029</v>
+        <v>0.018</v>
       </c>
       <c r="J97" s="8" t="n">
-        <v>64.5</v>
+        <v>38.7</v>
       </c>
       <c r="K97" s="10" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="B98" s="12" t="inlineStr">
         <is>
-          <t>P2733</t>
+          <t>P2746</t>
         </is>
       </c>
       <c r="C98" s="12" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="D98" s="13" t="inlineStr">
         <is>
-          <t>ICF - Datalake 2026-1 - Cloud</t>
+          <t>ICF - Citación con Georreferenciación - Other Vendors</t>
         </is>
       </c>
       <c r="E98" s="13" t="inlineStr">
@@ -5921,22 +5921,22 @@
       </c>
       <c r="F98" s="12" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="G98" s="12" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>Other Vendors</t>
         </is>
       </c>
       <c r="H98" s="14" t="n">
-        <v>5.7</v>
+        <v>3.4</v>
       </c>
       <c r="I98" s="9" t="n">
-        <v>0.029</v>
+        <v>0.018</v>
       </c>
       <c r="J98" s="14" t="n">
-        <v>64.5</v>
+        <v>38.7</v>
       </c>
       <c r="K98" s="15" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>P2734</t>
+          <t>P2747</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
@@ -5967,7 +5967,7 @@
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>ICF - Datalake 2026-1 - Ret Sw</t>
+          <t>ICF - Citación con Georreferenciación - Cloud</t>
         </is>
       </c>
       <c r="E99" s="7" t="inlineStr">
@@ -5977,22 +5977,22 @@
       </c>
       <c r="F99" s="6" t="inlineStr">
         <is>
-          <t>Software SW</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="G99" s="6" t="inlineStr">
         <is>
-          <t>Ret Sw</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="H99" s="8" t="n">
-        <v>5.7</v>
+        <v>3.4</v>
       </c>
       <c r="I99" s="9" t="n">
-        <v>0.029</v>
+        <v>0.018</v>
       </c>
       <c r="J99" s="8" t="n">
-        <v>64.5</v>
+        <v>38.7</v>
       </c>
       <c r="K99" s="10" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
       </c>
       <c r="B100" s="12" t="inlineStr">
         <is>
-          <t>P2240</t>
+          <t>P2732</t>
         </is>
       </c>
       <c r="C100" s="12" t="inlineStr">
@@ -6023,12 +6023,12 @@
       </c>
       <c r="D100" s="13" t="inlineStr">
         <is>
-          <t>ICF - Evolución Datalake Fase 2 2025 - Ret Other Vendors</t>
+          <t>ICF - Datalake 2026-1 - Ret</t>
         </is>
       </c>
       <c r="E100" s="13" t="inlineStr">
         <is>
-          <t>Instituto Colombiano Para La Evaluacion De La Educacion ICFES</t>
+          <t>Icfes</t>
         </is>
       </c>
       <c r="F100" s="12" t="inlineStr">
@@ -6038,17 +6038,17 @@
       </c>
       <c r="G100" s="12" t="inlineStr">
         <is>
-          <t>Ret Other Vendors</t>
+          <t>Ret</t>
         </is>
       </c>
       <c r="H100" s="14" t="n">
-        <v>17</v>
-      </c>
-      <c r="I100" s="18" t="n">
-        <v>0.08800000000000001</v>
+        <v>5.7</v>
+      </c>
+      <c r="I100" s="9" t="n">
+        <v>0.029</v>
       </c>
       <c r="J100" s="14" t="n">
-        <v>193.5</v>
+        <v>64.5</v>
       </c>
       <c r="K100" s="15" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>P2559</t>
+          <t>P2733</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
@@ -6079,32 +6079,32 @@
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>ICF - Operacion en AWS - Ret Other Vendors</t>
+          <t>ICF - Datalake 2026-1 - Cloud</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
-          <t>ICFES</t>
+          <t>Icfes</t>
         </is>
       </c>
       <c r="F101" s="6" t="inlineStr">
         <is>
-          <t>Operación</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="G101" s="6" t="inlineStr">
         <is>
-          <t>Ret Other Vendors</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="H101" s="8" t="n">
-        <v>17</v>
-      </c>
-      <c r="I101" s="18" t="n">
-        <v>0.08800000000000001</v>
+        <v>5.7</v>
+      </c>
+      <c r="I101" s="9" t="n">
+        <v>0.029</v>
       </c>
       <c r="J101" s="8" t="n">
-        <v>193.5</v>
+        <v>64.5</v>
       </c>
       <c r="K101" s="10" t="inlineStr">
         <is>
@@ -6125,51 +6125,51 @@
       </c>
       <c r="B102" s="12" t="inlineStr">
         <is>
-          <t>P1947</t>
+          <t>P2734</t>
         </is>
       </c>
       <c r="C102" s="12" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="D102" s="13" t="inlineStr">
         <is>
-          <t>JPM - Cloud Managed Services 2023-25 - Ret</t>
+          <t>ICF - Datalake 2026-1 - Ret Sw</t>
         </is>
       </c>
       <c r="E102" s="13" t="inlineStr">
         <is>
-          <t>JPMP - Justicia Penal Militar y Policial</t>
+          <t>Icfes</t>
         </is>
       </c>
       <c r="F102" s="12" t="inlineStr">
         <is>
-          <t>Operación</t>
+          <t>Software SW</t>
         </is>
       </c>
       <c r="G102" s="12" t="inlineStr">
         <is>
-          <t>Ret</t>
+          <t>Ret Sw</t>
         </is>
       </c>
       <c r="H102" s="14" t="n">
-        <v>13.5</v>
+        <v>5.7</v>
       </c>
       <c r="I102" s="9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.029</v>
       </c>
       <c r="J102" s="14" t="n">
-        <v>103.8</v>
-      </c>
-      <c r="K102" s="19" t="inlineStr">
-        <is>
-          <t>🔄 Reasignado</t>
+        <v>64.5</v>
+      </c>
+      <c r="K102" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="L102" s="11" t="inlineStr">
         <is>
-          <t>David Cortes</t>
+          <t>Juan Bernal</t>
         </is>
       </c>
     </row>
@@ -6181,280 +6181,280 @@
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>P1948</t>
+          <t>P2240</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
+          <t>ICF</t>
+        </is>
+      </c>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>ICF - Evolución Datalake Fase 2 2025 - Ret Other Vendors</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="inlineStr">
+        <is>
+          <t>Instituto Colombiano Para La Evaluacion De La Educacion ICFES</t>
+        </is>
+      </c>
+      <c r="F103" s="6" t="inlineStr">
+        <is>
+          <t>Operación</t>
+        </is>
+      </c>
+      <c r="G103" s="6" t="inlineStr">
+        <is>
+          <t>Ret Other Vendors</t>
+        </is>
+      </c>
+      <c r="H103" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="I103" s="18" t="n">
+        <v>0.08800000000000001</v>
+      </c>
+      <c r="J103" s="8" t="n">
+        <v>193.5</v>
+      </c>
+      <c r="K103" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L103" s="5" t="inlineStr">
+        <is>
+          <t>Juan Bernal</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="18" customHeight="1">
+      <c r="A104" s="11" t="inlineStr">
+        <is>
+          <t>Juan Bernal</t>
+        </is>
+      </c>
+      <c r="B104" s="12" t="inlineStr">
+        <is>
+          <t>P2559</t>
+        </is>
+      </c>
+      <c r="C104" s="12" t="inlineStr">
+        <is>
+          <t>ICF</t>
+        </is>
+      </c>
+      <c r="D104" s="13" t="inlineStr">
+        <is>
+          <t>ICF - Operacion en AWS - Ret Other Vendors</t>
+        </is>
+      </c>
+      <c r="E104" s="13" t="inlineStr">
+        <is>
+          <t>ICFES</t>
+        </is>
+      </c>
+      <c r="F104" s="12" t="inlineStr">
+        <is>
+          <t>Operación</t>
+        </is>
+      </c>
+      <c r="G104" s="12" t="inlineStr">
+        <is>
+          <t>Ret Other Vendors</t>
+        </is>
+      </c>
+      <c r="H104" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="I104" s="18" t="n">
+        <v>0.08800000000000001</v>
+      </c>
+      <c r="J104" s="14" t="n">
+        <v>193.5</v>
+      </c>
+      <c r="K104" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L104" s="11" t="inlineStr">
+        <is>
+          <t>Juan Bernal</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="18" customHeight="1">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>Juan Bernal</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>P1947</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
           <t>JPM</t>
         </is>
       </c>
-      <c r="D103" s="7" t="inlineStr">
-        <is>
-          <t>JPM - Cloud Managed Services 2023-25 - Cloud</t>
-        </is>
-      </c>
-      <c r="E103" s="7" t="inlineStr">
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>JPM - Cloud Managed Services 2023-25 - Ret</t>
+        </is>
+      </c>
+      <c r="E105" s="7" t="inlineStr">
         <is>
           <t>JPMP - Justicia Penal Militar y Policial</t>
         </is>
       </c>
-      <c r="F103" s="6" t="inlineStr">
-        <is>
-          <t>Data</t>
-        </is>
-      </c>
-      <c r="G103" s="6" t="inlineStr">
-        <is>
-          <t>Cloud</t>
-        </is>
-      </c>
-      <c r="H103" s="8" t="n">
+      <c r="F105" s="6" t="inlineStr">
+        <is>
+          <t>Operación</t>
+        </is>
+      </c>
+      <c r="G105" s="6" t="inlineStr">
+        <is>
+          <t>Ret</t>
+        </is>
+      </c>
+      <c r="H105" s="8" t="n">
         <v>13.5</v>
       </c>
-      <c r="I103" s="9" t="n">
+      <c r="I105" s="9" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="J103" s="8" t="n">
+      <c r="J105" s="8" t="n">
         <v>103.8</v>
       </c>
-      <c r="K103" s="19" t="inlineStr">
+      <c r="K105" s="19" t="inlineStr">
         <is>
           <t>🔄 Reasignado</t>
         </is>
       </c>
-      <c r="L103" s="5" t="inlineStr">
+      <c r="L105" s="5" t="inlineStr">
         <is>
           <t>David Cortes</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="22" customHeight="1">
-      <c r="A104" s="24" t="inlineStr">
-        <is>
-          <t>▶  Kelly Carbonell  –  14 sub-proyectos  |  ~119h est./mes  (62% capacidad)</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="18" customHeight="1">
-      <c r="A105" s="11" t="inlineStr">
-        <is>
-          <t>Kelly Carbonell</t>
-        </is>
-      </c>
-      <c r="B105" s="12" t="inlineStr">
-        <is>
-          <t>P2397</t>
-        </is>
-      </c>
-      <c r="C105" s="12" t="inlineStr">
-        <is>
-          <t>ACA</t>
-        </is>
-      </c>
-      <c r="D105" s="13" t="inlineStr">
-        <is>
-          <t>ACA -  Virtualización infraestructura Cali  - Cloud</t>
-        </is>
-      </c>
-      <c r="E105" s="13" t="inlineStr">
-        <is>
-          <t>Alcaldia de Cali</t>
-        </is>
-      </c>
-      <c r="F105" s="12" t="inlineStr">
-        <is>
-          <t>Data</t>
-        </is>
-      </c>
-      <c r="G105" s="12" t="inlineStr">
-        <is>
-          <t>Cloud</t>
-        </is>
-      </c>
-      <c r="H105" s="14" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="I105" s="9" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="J105" s="14" t="n">
-        <v>226.1</v>
-      </c>
-      <c r="K105" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L105" s="11" t="inlineStr">
-        <is>
-          <t>Kelly Carbonell</t>
         </is>
       </c>
     </row>
     <row r="106" ht="18" customHeight="1">
       <c r="A106" s="11" t="inlineStr">
         <is>
+          <t>Juan Bernal</t>
+        </is>
+      </c>
+      <c r="B106" s="12" t="inlineStr">
+        <is>
+          <t>P1948</t>
+        </is>
+      </c>
+      <c r="C106" s="12" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="D106" s="13" t="inlineStr">
+        <is>
+          <t>JPM - Cloud Managed Services 2023-25 - Cloud</t>
+        </is>
+      </c>
+      <c r="E106" s="13" t="inlineStr">
+        <is>
+          <t>JPMP - Justicia Penal Militar y Policial</t>
+        </is>
+      </c>
+      <c r="F106" s="12" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="G106" s="12" t="inlineStr">
+        <is>
+          <t>Cloud</t>
+        </is>
+      </c>
+      <c r="H106" s="14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="I106" s="9" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="J106" s="14" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="K106" s="19" t="inlineStr">
+        <is>
+          <t>🔄 Reasignado</t>
+        </is>
+      </c>
+      <c r="L106" s="11" t="inlineStr">
+        <is>
+          <t>David Cortes</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="22" customHeight="1">
+      <c r="A107" s="24" t="inlineStr">
+        <is>
+          <t>▶  Kelly Carbonell  –  14 sub-proyectos  |  ~119h est./mes  (62% capacidad)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="18" customHeight="1">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
           <t>Kelly Carbonell</t>
         </is>
       </c>
-      <c r="B106" s="12" t="inlineStr">
-        <is>
-          <t>P2398</t>
-        </is>
-      </c>
-      <c r="C106" s="12" t="inlineStr">
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>P2397</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
         <is>
           <t>ACA</t>
         </is>
       </c>
-      <c r="D106" s="13" t="inlineStr">
-        <is>
-          <t>ACA -  Virtualización infraestructura Cali  - Ret</t>
-        </is>
-      </c>
-      <c r="E106" s="13" t="inlineStr">
+      <c r="D108" s="7" t="inlineStr">
+        <is>
+          <t>ACA -  Virtualización infraestructura Cali  - Cloud</t>
+        </is>
+      </c>
+      <c r="E108" s="7" t="inlineStr">
         <is>
           <t>Alcaldia de Cali</t>
         </is>
       </c>
-      <c r="F106" s="12" t="inlineStr">
-        <is>
-          <t>Operación</t>
-        </is>
-      </c>
-      <c r="G106" s="12" t="inlineStr">
-        <is>
-          <t>Ret</t>
-        </is>
-      </c>
-      <c r="H106" s="14" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="I106" s="9" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="J106" s="14" t="n">
-        <v>226.1</v>
-      </c>
-      <c r="K106" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L106" s="11" t="inlineStr">
-        <is>
-          <t>Kelly Carbonell</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="18" customHeight="1">
-      <c r="A107" s="5" t="inlineStr">
-        <is>
-          <t>Kelly Carbonell</t>
-        </is>
-      </c>
-      <c r="B107" s="6" t="inlineStr">
-        <is>
-          <t>P2399</t>
-        </is>
-      </c>
-      <c r="C107" s="6" t="inlineStr">
-        <is>
-          <t>ACA</t>
-        </is>
-      </c>
-      <c r="D107" s="7" t="inlineStr">
-        <is>
-          <t>ACA -  Virtualización infraestructura Cali  - Ret SW</t>
-        </is>
-      </c>
-      <c r="E107" s="7" t="inlineStr">
-        <is>
-          <t>Alcaldia de Cali</t>
-        </is>
-      </c>
-      <c r="F107" s="6" t="inlineStr">
-        <is>
-          <t>Software SW</t>
-        </is>
-      </c>
-      <c r="G107" s="6" t="inlineStr">
-        <is>
-          <t>Ret SW</t>
-        </is>
-      </c>
-      <c r="H107" s="8" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="I107" s="9" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="J107" s="8" t="n">
-        <v>226.1</v>
-      </c>
-      <c r="K107" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L107" s="5" t="inlineStr">
-        <is>
-          <t>Kelly Carbonell</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="18" customHeight="1">
-      <c r="A108" s="11" t="inlineStr">
-        <is>
-          <t>Kelly Carbonell</t>
-        </is>
-      </c>
-      <c r="B108" s="12" t="inlineStr">
-        <is>
-          <t>P2400</t>
-        </is>
-      </c>
-      <c r="C108" s="12" t="inlineStr">
-        <is>
-          <t>ACA</t>
-        </is>
-      </c>
-      <c r="D108" s="13" t="inlineStr">
-        <is>
-          <t>ACA -  Virtualización infraestructura Cali  - Ret Other Vendors</t>
-        </is>
-      </c>
-      <c r="E108" s="13" t="inlineStr">
-        <is>
-          <t>Alcaldia de Cali</t>
-        </is>
-      </c>
-      <c r="F108" s="12" t="inlineStr">
-        <is>
-          <t>Operación</t>
-        </is>
-      </c>
-      <c r="G108" s="12" t="inlineStr">
-        <is>
-          <t>Ret Other Vendors</t>
-        </is>
-      </c>
-      <c r="H108" s="14" t="n">
+      <c r="F108" s="6" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="inlineStr">
+        <is>
+          <t>Cloud</t>
+        </is>
+      </c>
+      <c r="H108" s="8" t="n">
         <v>6.9</v>
       </c>
       <c r="I108" s="9" t="n">
         <v>0.036</v>
       </c>
-      <c r="J108" s="14" t="n">
+      <c r="J108" s="8" t="n">
         <v>226.1</v>
       </c>
-      <c r="K108" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L108" s="11" t="inlineStr">
+      <c r="K108" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L108" s="5" t="inlineStr">
         <is>
           <t>Kelly Carbonell</t>
         </is>
@@ -6468,7 +6468,7 @@
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>P2404</t>
+          <t>P2398</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>ACA - Fase III DataCali - Fixed</t>
+          <t>ACA -  Virtualización infraestructura Cali  - Ret</t>
         </is>
       </c>
       <c r="E109" s="7" t="inlineStr">
@@ -6488,22 +6488,22 @@
       </c>
       <c r="F109" s="6" t="inlineStr">
         <is>
-          <t>Implementación</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="G109" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Ret</t>
         </is>
       </c>
       <c r="H109" s="8" t="n">
-        <v>13.8</v>
+        <v>6.9</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.036</v>
       </c>
       <c r="J109" s="8" t="n">
-        <v>452.2</v>
+        <v>226.1</v>
       </c>
       <c r="K109" s="10" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
       </c>
       <c r="B110" s="12" t="inlineStr">
         <is>
-          <t>P2405</t>
+          <t>P2399</t>
         </is>
       </c>
       <c r="C110" s="12" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="D110" s="13" t="inlineStr">
         <is>
-          <t>ACA - Fase III DataCali - Ret Other Vendors</t>
+          <t>ACA -  Virtualización infraestructura Cali  - Ret SW</t>
         </is>
       </c>
       <c r="E110" s="13" t="inlineStr">
@@ -6544,22 +6544,22 @@
       </c>
       <c r="F110" s="12" t="inlineStr">
         <is>
-          <t>Operación</t>
+          <t>Software SW</t>
         </is>
       </c>
       <c r="G110" s="12" t="inlineStr">
         <is>
-          <t>Ret Other Vendors</t>
+          <t>Ret SW</t>
         </is>
       </c>
       <c r="H110" s="14" t="n">
-        <v>13.8</v>
+        <v>6.9</v>
       </c>
       <c r="I110" s="9" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.036</v>
       </c>
       <c r="J110" s="14" t="n">
-        <v>452.2</v>
+        <v>226.1</v>
       </c>
       <c r="K110" s="15" t="inlineStr">
         <is>
@@ -6580,7 +6580,7 @@
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>P2541</t>
+          <t>P2400</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>ACA - Hacienda a un Click - Fixed</t>
+          <t>ACA -  Virtualización infraestructura Cali  - Ret Other Vendors</t>
         </is>
       </c>
       <c r="E111" s="7" t="inlineStr">
@@ -6600,12 +6600,12 @@
       </c>
       <c r="F111" s="6" t="inlineStr">
         <is>
-          <t>Implementación</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="G111" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Ret Other Vendors</t>
         </is>
       </c>
       <c r="H111" s="8" t="n">
@@ -6636,7 +6636,7 @@
       </c>
       <c r="B112" s="12" t="inlineStr">
         <is>
-          <t>P2542</t>
+          <t>P2404</t>
         </is>
       </c>
       <c r="C112" s="12" t="inlineStr">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="D112" s="13" t="inlineStr">
         <is>
-          <t>ACA - Hacienda a un Click - Ret</t>
+          <t>ACA - Fase III DataCali - Fixed</t>
         </is>
       </c>
       <c r="E112" s="13" t="inlineStr">
@@ -6656,22 +6656,22 @@
       </c>
       <c r="F112" s="12" t="inlineStr">
         <is>
-          <t>Operación</t>
+          <t>Implementación</t>
         </is>
       </c>
       <c r="G112" s="12" t="inlineStr">
         <is>
-          <t>Ret</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H112" s="14" t="n">
-        <v>6.9</v>
+        <v>13.8</v>
       </c>
       <c r="I112" s="9" t="n">
-        <v>0.036</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="J112" s="14" t="n">
-        <v>226.1</v>
+        <v>452.2</v>
       </c>
       <c r="K112" s="15" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>P2543</t>
+          <t>P2405</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>ACA - Hacienda a un Click - Ret SW</t>
+          <t>ACA - Fase III DataCali - Ret Other Vendors</t>
         </is>
       </c>
       <c r="E113" s="7" t="inlineStr">
@@ -6712,22 +6712,22 @@
       </c>
       <c r="F113" s="6" t="inlineStr">
         <is>
-          <t>Software SW</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="G113" s="6" t="inlineStr">
         <is>
-          <t>Ret SW</t>
+          <t>Ret Other Vendors</t>
         </is>
       </c>
       <c r="H113" s="8" t="n">
-        <v>6.9</v>
+        <v>13.8</v>
       </c>
       <c r="I113" s="9" t="n">
-        <v>0.036</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="J113" s="8" t="n">
-        <v>226.1</v>
+        <v>452.2</v>
       </c>
       <c r="K113" s="10" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
       </c>
       <c r="B114" s="12" t="inlineStr">
         <is>
-          <t>P2544</t>
+          <t>P2541</t>
         </is>
       </c>
       <c r="C114" s="12" t="inlineStr">
@@ -6758,7 +6758,7 @@
       </c>
       <c r="D114" s="13" t="inlineStr">
         <is>
-          <t>ACA - Hacienda a un Click - Ret Other Vendors</t>
+          <t>ACA - Hacienda a un Click - Fixed</t>
         </is>
       </c>
       <c r="E114" s="13" t="inlineStr">
@@ -6768,12 +6768,12 @@
       </c>
       <c r="F114" s="12" t="inlineStr">
         <is>
-          <t>Operación</t>
+          <t>Implementación</t>
         </is>
       </c>
       <c r="G114" s="12" t="inlineStr">
         <is>
-          <t>Ret Other Vendors</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H114" s="14" t="n">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>P2822</t>
+          <t>P2542</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>ACA - Secretaría de Transparencia MVP  - Fixed</t>
+          <t>ACA - Hacienda a un Click - Ret</t>
         </is>
       </c>
       <c r="E115" s="7" t="inlineStr">
@@ -6824,22 +6824,22 @@
       </c>
       <c r="F115" s="6" t="inlineStr">
         <is>
-          <t>Implementación</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="G115" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Ret</t>
         </is>
       </c>
       <c r="H115" s="8" t="n">
-        <v>9.199999999999999</v>
+        <v>6.9</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v>0.048</v>
+        <v>0.036</v>
       </c>
       <c r="J115" s="8" t="n">
-        <v>301.5</v>
+        <v>226.1</v>
       </c>
       <c r="K115" s="10" t="inlineStr">
         <is>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="B116" s="12" t="inlineStr">
         <is>
-          <t>P2823</t>
+          <t>P2543</t>
         </is>
       </c>
       <c r="C116" s="12" t="inlineStr">
@@ -6870,7 +6870,7 @@
       </c>
       <c r="D116" s="13" t="inlineStr">
         <is>
-          <t>ACA - Secretaría de Transparencia MVP  - Ret</t>
+          <t>ACA - Hacienda a un Click - Ret SW</t>
         </is>
       </c>
       <c r="E116" s="13" t="inlineStr">
@@ -6880,22 +6880,22 @@
       </c>
       <c r="F116" s="12" t="inlineStr">
         <is>
-          <t>Operación</t>
+          <t>Software SW</t>
         </is>
       </c>
       <c r="G116" s="12" t="inlineStr">
         <is>
-          <t>Ret</t>
+          <t>Ret SW</t>
         </is>
       </c>
       <c r="H116" s="14" t="n">
-        <v>9.199999999999999</v>
+        <v>6.9</v>
       </c>
       <c r="I116" s="9" t="n">
-        <v>0.048</v>
+        <v>0.036</v>
       </c>
       <c r="J116" s="14" t="n">
-        <v>301.5</v>
+        <v>226.1</v>
       </c>
       <c r="K116" s="15" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>P2824</t>
+          <t>P2544</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>ACA - Secretaría de Transparencia MVP  - Cloud</t>
+          <t>ACA - Hacienda a un Click - Ret Other Vendors</t>
         </is>
       </c>
       <c r="E117" s="7" t="inlineStr">
@@ -6936,22 +6936,22 @@
       </c>
       <c r="F117" s="6" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="G117" s="6" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>Ret Other Vendors</t>
         </is>
       </c>
       <c r="H117" s="8" t="n">
-        <v>9.199999999999999</v>
+        <v>6.9</v>
       </c>
       <c r="I117" s="9" t="n">
-        <v>0.048</v>
+        <v>0.036</v>
       </c>
       <c r="J117" s="8" t="n">
-        <v>301.5</v>
+        <v>226.1</v>
       </c>
       <c r="K117" s="10" t="inlineStr">
         <is>
@@ -6972,272 +6972,272 @@
       </c>
       <c r="B118" s="12" t="inlineStr">
         <is>
-          <t>P1923</t>
+          <t>P2822</t>
         </is>
       </c>
       <c r="C118" s="12" t="inlineStr">
         <is>
-          <t>CCC</t>
+          <t>ACA</t>
         </is>
       </c>
       <c r="D118" s="13" t="inlineStr">
         <is>
-          <t>CCC - IaaS para DRP - Cloud</t>
+          <t>ACA - Secretaría de Transparencia MVP  - Fixed</t>
         </is>
       </c>
       <c r="E118" s="13" t="inlineStr">
         <is>
-          <t>Cámara de Comercio de Cali</t>
+          <t>Alcaldia de Cali</t>
         </is>
       </c>
       <c r="F118" s="12" t="inlineStr">
         <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="G118" s="12" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H118" s="14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="I118" s="9" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="J118" s="14" t="n">
+        <v>301.5</v>
+      </c>
+      <c r="K118" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L118" s="11" t="inlineStr">
+        <is>
+          <t>Kelly Carbonell</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="18" customHeight="1">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t>Kelly Carbonell</t>
+        </is>
+      </c>
+      <c r="B119" s="6" t="inlineStr">
+        <is>
+          <t>P2823</t>
+        </is>
+      </c>
+      <c r="C119" s="6" t="inlineStr">
+        <is>
+          <t>ACA</t>
+        </is>
+      </c>
+      <c r="D119" s="7" t="inlineStr">
+        <is>
+          <t>ACA - Secretaría de Transparencia MVP  - Ret</t>
+        </is>
+      </c>
+      <c r="E119" s="7" t="inlineStr">
+        <is>
+          <t>Alcaldia de Cali</t>
+        </is>
+      </c>
+      <c r="F119" s="6" t="inlineStr">
+        <is>
+          <t>Operación</t>
+        </is>
+      </c>
+      <c r="G119" s="6" t="inlineStr">
+        <is>
+          <t>Ret</t>
+        </is>
+      </c>
+      <c r="H119" s="8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="I119" s="9" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="J119" s="8" t="n">
+        <v>301.5</v>
+      </c>
+      <c r="K119" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L119" s="5" t="inlineStr">
+        <is>
+          <t>Kelly Carbonell</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="18" customHeight="1">
+      <c r="A120" s="11" t="inlineStr">
+        <is>
+          <t>Kelly Carbonell</t>
+        </is>
+      </c>
+      <c r="B120" s="12" t="inlineStr">
+        <is>
+          <t>P2824</t>
+        </is>
+      </c>
+      <c r="C120" s="12" t="inlineStr">
+        <is>
+          <t>ACA</t>
+        </is>
+      </c>
+      <c r="D120" s="13" t="inlineStr">
+        <is>
+          <t>ACA - Secretaría de Transparencia MVP  - Cloud</t>
+        </is>
+      </c>
+      <c r="E120" s="13" t="inlineStr">
+        <is>
+          <t>Alcaldia de Cali</t>
+        </is>
+      </c>
+      <c r="F120" s="12" t="inlineStr">
+        <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="G118" s="12" t="inlineStr">
+      <c r="G120" s="12" t="inlineStr">
         <is>
           <t>Cloud</t>
         </is>
       </c>
-      <c r="H118" s="14" t="n">
-        <v>9</v>
-      </c>
-      <c r="I118" s="9" t="n">
-        <v>0.046</v>
-      </c>
-      <c r="J118" s="14" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="K118" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L118" s="11" t="inlineStr">
+      <c r="H120" s="14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="I120" s="9" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="J120" s="14" t="n">
+        <v>301.5</v>
+      </c>
+      <c r="K120" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L120" s="11" t="inlineStr">
         <is>
           <t>Kelly Carbonell</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="22" customHeight="1">
-      <c r="A119" s="25" t="inlineStr">
-        <is>
-          <t>▶  Miguel Garcia  –  4 sub-proyectos  |  ~179h est./mes  (93% capacidad)</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="18" customHeight="1">
-      <c r="A120" s="5" t="inlineStr">
-        <is>
-          <t>Miguel Garcia</t>
-        </is>
-      </c>
-      <c r="B120" s="6" t="inlineStr">
-        <is>
-          <t>P2457</t>
-        </is>
-      </c>
-      <c r="C120" s="6" t="inlineStr">
-        <is>
-          <t>ADR</t>
-        </is>
-      </c>
-      <c r="D120" s="7" t="inlineStr">
-        <is>
-          <t>ADR - AI Auditoría Médica - Fixed</t>
-        </is>
-      </c>
-      <c r="E120" s="7" t="inlineStr">
-        <is>
-          <t>La Administradora de los Recursos del Sistema General de Seguridad Social en Salud</t>
-        </is>
-      </c>
-      <c r="F120" s="6" t="inlineStr">
-        <is>
-          <t>Implementación</t>
-        </is>
-      </c>
-      <c r="G120" s="6" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="H120" s="8" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="I120" s="16" t="n">
-        <v>0.231</v>
-      </c>
-      <c r="J120" s="8" t="n">
-        <v>2063.6</v>
-      </c>
-      <c r="K120" s="19" t="inlineStr">
-        <is>
-          <t>🔄 Reasignado</t>
-        </is>
-      </c>
-      <c r="L120" s="5" t="inlineStr">
-        <is>
-          <t>Indira Duarte</t>
         </is>
       </c>
     </row>
     <row r="121" ht="18" customHeight="1">
       <c r="A121" s="5" t="inlineStr">
         <is>
+          <t>Kelly Carbonell</t>
+        </is>
+      </c>
+      <c r="B121" s="6" t="inlineStr">
+        <is>
+          <t>P1923</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="inlineStr">
+        <is>
+          <t>CCC</t>
+        </is>
+      </c>
+      <c r="D121" s="7" t="inlineStr">
+        <is>
+          <t>CCC - IaaS para DRP - Cloud</t>
+        </is>
+      </c>
+      <c r="E121" s="7" t="inlineStr">
+        <is>
+          <t>Cámara de Comercio de Cali</t>
+        </is>
+      </c>
+      <c r="F121" s="6" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="G121" s="6" t="inlineStr">
+        <is>
+          <t>Cloud</t>
+        </is>
+      </c>
+      <c r="H121" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="I121" s="9" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="J121" s="8" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="K121" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L121" s="5" t="inlineStr">
+        <is>
+          <t>Kelly Carbonell</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="22" customHeight="1">
+      <c r="A122" s="25" t="inlineStr">
+        <is>
+          <t>▶  Miguel Garcia  –  4 sub-proyectos  |  ~179h est./mes  (93% capacidad)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="18" customHeight="1">
+      <c r="A123" s="11" t="inlineStr">
+        <is>
           <t>Miguel Garcia</t>
         </is>
       </c>
-      <c r="B121" s="6" t="inlineStr">
-        <is>
-          <t>P2470</t>
-        </is>
-      </c>
-      <c r="C121" s="6" t="inlineStr">
+      <c r="B123" s="12" t="inlineStr">
+        <is>
+          <t>P2457</t>
+        </is>
+      </c>
+      <c r="C123" s="12" t="inlineStr">
         <is>
           <t>ADR</t>
         </is>
       </c>
-      <c r="D121" s="7" t="inlineStr">
-        <is>
-          <t>ADR - AI Auditoría Médica - Cloud</t>
-        </is>
-      </c>
-      <c r="E121" s="7" t="inlineStr">
+      <c r="D123" s="13" t="inlineStr">
+        <is>
+          <t>ADR - AI Auditoría Médica - Fixed</t>
+        </is>
+      </c>
+      <c r="E123" s="13" t="inlineStr">
         <is>
           <t>La Administradora de los Recursos del Sistema General de Seguridad Social en Salud</t>
         </is>
       </c>
-      <c r="F121" s="6" t="inlineStr">
-        <is>
-          <t>Data</t>
-        </is>
-      </c>
-      <c r="G121" s="6" t="inlineStr">
-        <is>
-          <t>Cloud</t>
-        </is>
-      </c>
-      <c r="H121" s="8" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="I121" s="16" t="n">
-        <v>0.231</v>
-      </c>
-      <c r="J121" s="8" t="n">
-        <v>2063.6</v>
-      </c>
-      <c r="K121" s="19" t="inlineStr">
-        <is>
-          <t>🔄 Reasignado</t>
-        </is>
-      </c>
-      <c r="L121" s="5" t="inlineStr">
-        <is>
-          <t>Indira Duarte</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="18" customHeight="1">
-      <c r="A122" s="11" t="inlineStr">
-        <is>
-          <t>Miguel Garcia</t>
-        </is>
-      </c>
-      <c r="B122" s="12" t="inlineStr">
-        <is>
-          <t>P2471</t>
-        </is>
-      </c>
-      <c r="C122" s="12" t="inlineStr">
-        <is>
-          <t>ADR</t>
-        </is>
-      </c>
-      <c r="D122" s="13" t="inlineStr">
-        <is>
-          <t>ADR - AI Auditoría Médica - Ret Sw</t>
-        </is>
-      </c>
-      <c r="E122" s="13" t="inlineStr">
-        <is>
-          <t>La Administradora de los Recursos del Sistema General de Seguridad Social en Salud</t>
-        </is>
-      </c>
-      <c r="F122" s="12" t="inlineStr">
-        <is>
-          <t>Software SW</t>
-        </is>
-      </c>
-      <c r="G122" s="12" t="inlineStr">
-        <is>
-          <t>Ret Sw</t>
-        </is>
-      </c>
-      <c r="H122" s="14" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="I122" s="16" t="n">
-        <v>0.231</v>
-      </c>
-      <c r="J122" s="14" t="n">
-        <v>2063.6</v>
-      </c>
-      <c r="K122" s="19" t="inlineStr">
-        <is>
-          <t>🔄 Reasignado</t>
-        </is>
-      </c>
-      <c r="L122" s="11" t="inlineStr">
-        <is>
-          <t>Indira Duarte</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="18" customHeight="1">
-      <c r="A123" s="5" t="inlineStr">
-        <is>
-          <t>Miguel Garcia</t>
-        </is>
-      </c>
-      <c r="B123" s="6" t="inlineStr">
-        <is>
-          <t>P2472</t>
-        </is>
-      </c>
-      <c r="C123" s="6" t="inlineStr">
-        <is>
-          <t>ADR</t>
-        </is>
-      </c>
-      <c r="D123" s="7" t="inlineStr">
-        <is>
-          <t>ADR - AI Auditoría Médica - Ret Other Vendors</t>
-        </is>
-      </c>
-      <c r="E123" s="7" t="inlineStr">
-        <is>
-          <t>La Administradora de los Recursos del Sistema General de Seguridad Social en Salud</t>
-        </is>
-      </c>
-      <c r="F123" s="6" t="inlineStr">
-        <is>
-          <t>Operación</t>
-        </is>
-      </c>
-      <c r="G123" s="6" t="inlineStr">
-        <is>
-          <t>Ret Other Vendors</t>
-        </is>
-      </c>
-      <c r="H123" s="8" t="n">
+      <c r="F123" s="12" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="G123" s="12" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H123" s="14" t="n">
         <v>44.8</v>
       </c>
       <c r="I123" s="16" t="n">
         <v>0.231</v>
       </c>
-      <c r="J123" s="8" t="n">
+      <c r="J123" s="14" t="n">
         <v>2063.6</v>
       </c>
       <c r="K123" s="19" t="inlineStr">
@@ -7245,238 +7245,238 @@
           <t>🔄 Reasignado</t>
         </is>
       </c>
-      <c r="L123" s="5" t="inlineStr">
+      <c r="L123" s="11" t="inlineStr">
         <is>
           <t>Indira Duarte</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="22" customHeight="1">
-      <c r="A124" s="22" t="inlineStr">
-        <is>
-          <t>▶  Oscar Barragan  –  56 sub-proyectos  |  ~215h est./mes  (111% capacidad)</t>
+    <row r="124" ht="18" customHeight="1">
+      <c r="A124" s="11" t="inlineStr">
+        <is>
+          <t>Miguel Garcia</t>
+        </is>
+      </c>
+      <c r="B124" s="12" t="inlineStr">
+        <is>
+          <t>P2470</t>
+        </is>
+      </c>
+      <c r="C124" s="12" t="inlineStr">
+        <is>
+          <t>ADR</t>
+        </is>
+      </c>
+      <c r="D124" s="13" t="inlineStr">
+        <is>
+          <t>ADR - AI Auditoría Médica - Cloud</t>
+        </is>
+      </c>
+      <c r="E124" s="13" t="inlineStr">
+        <is>
+          <t>La Administradora de los Recursos del Sistema General de Seguridad Social en Salud</t>
+        </is>
+      </c>
+      <c r="F124" s="12" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="G124" s="12" t="inlineStr">
+        <is>
+          <t>Cloud</t>
+        </is>
+      </c>
+      <c r="H124" s="14" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="I124" s="16" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="J124" s="14" t="n">
+        <v>2063.6</v>
+      </c>
+      <c r="K124" s="19" t="inlineStr">
+        <is>
+          <t>🔄 Reasignado</t>
+        </is>
+      </c>
+      <c r="L124" s="11" t="inlineStr">
+        <is>
+          <t>Indira Duarte</t>
         </is>
       </c>
     </row>
     <row r="125" ht="18" customHeight="1">
-      <c r="A125" s="11" t="inlineStr">
-        <is>
-          <t>Oscar Barragan</t>
-        </is>
-      </c>
-      <c r="B125" s="12" t="inlineStr">
-        <is>
-          <t>P2635</t>
-        </is>
-      </c>
-      <c r="C125" s="12" t="inlineStr">
-        <is>
-          <t>AGR</t>
-        </is>
-      </c>
-      <c r="D125" s="13" t="inlineStr">
-        <is>
-          <t>AGR - CP Suite ( Smartcash) Operación 2026 - Fixed</t>
-        </is>
-      </c>
-      <c r="E125" s="13" t="inlineStr">
-        <is>
-          <t>Fiduagraria</t>
-        </is>
-      </c>
-      <c r="F125" s="12" t="inlineStr">
-        <is>
-          <t>Implementación</t>
-        </is>
-      </c>
-      <c r="G125" s="12" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="H125" s="14" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I125" s="9" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="J125" s="14" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="K125" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L125" s="11" t="inlineStr">
-        <is>
-          <t>Oscar Barragan</t>
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>Miguel Garcia</t>
+        </is>
+      </c>
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>P2471</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>ADR</t>
+        </is>
+      </c>
+      <c r="D125" s="7" t="inlineStr">
+        <is>
+          <t>ADR - AI Auditoría Médica - Ret Sw</t>
+        </is>
+      </c>
+      <c r="E125" s="7" t="inlineStr">
+        <is>
+          <t>La Administradora de los Recursos del Sistema General de Seguridad Social en Salud</t>
+        </is>
+      </c>
+      <c r="F125" s="6" t="inlineStr">
+        <is>
+          <t>Software SW</t>
+        </is>
+      </c>
+      <c r="G125" s="6" t="inlineStr">
+        <is>
+          <t>Ret Sw</t>
+        </is>
+      </c>
+      <c r="H125" s="8" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="I125" s="16" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="J125" s="8" t="n">
+        <v>2063.6</v>
+      </c>
+      <c r="K125" s="19" t="inlineStr">
+        <is>
+          <t>🔄 Reasignado</t>
+        </is>
+      </c>
+      <c r="L125" s="5" t="inlineStr">
+        <is>
+          <t>Indira Duarte</t>
         </is>
       </c>
     </row>
     <row r="126" ht="18" customHeight="1">
       <c r="A126" s="11" t="inlineStr">
         <is>
+          <t>Miguel Garcia</t>
+        </is>
+      </c>
+      <c r="B126" s="12" t="inlineStr">
+        <is>
+          <t>P2472</t>
+        </is>
+      </c>
+      <c r="C126" s="12" t="inlineStr">
+        <is>
+          <t>ADR</t>
+        </is>
+      </c>
+      <c r="D126" s="13" t="inlineStr">
+        <is>
+          <t>ADR - AI Auditoría Médica - Ret Other Vendors</t>
+        </is>
+      </c>
+      <c r="E126" s="13" t="inlineStr">
+        <is>
+          <t>La Administradora de los Recursos del Sistema General de Seguridad Social en Salud</t>
+        </is>
+      </c>
+      <c r="F126" s="12" t="inlineStr">
+        <is>
+          <t>Operación</t>
+        </is>
+      </c>
+      <c r="G126" s="12" t="inlineStr">
+        <is>
+          <t>Ret Other Vendors</t>
+        </is>
+      </c>
+      <c r="H126" s="14" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="I126" s="16" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="J126" s="14" t="n">
+        <v>2063.6</v>
+      </c>
+      <c r="K126" s="19" t="inlineStr">
+        <is>
+          <t>🔄 Reasignado</t>
+        </is>
+      </c>
+      <c r="L126" s="11" t="inlineStr">
+        <is>
+          <t>Indira Duarte</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="22" customHeight="1">
+      <c r="A127" s="22" t="inlineStr">
+        <is>
+          <t>▶  Oscar Barragan  –  56 sub-proyectos  |  ~215h est./mes  (111% capacidad)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="18" customHeight="1">
+      <c r="A128" s="5" t="inlineStr">
+        <is>
           <t>Oscar Barragan</t>
         </is>
       </c>
-      <c r="B126" s="12" t="inlineStr">
-        <is>
-          <t>P2636</t>
-        </is>
-      </c>
-      <c r="C126" s="12" t="inlineStr">
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>P2635</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="inlineStr">
         <is>
           <t>AGR</t>
         </is>
       </c>
-      <c r="D126" s="13" t="inlineStr">
-        <is>
-          <t>AGR - CP Suite ( Smartcash) Operación 2026 - Ret</t>
-        </is>
-      </c>
-      <c r="E126" s="13" t="inlineStr">
+      <c r="D128" s="7" t="inlineStr">
+        <is>
+          <t>AGR - CP Suite ( Smartcash) Operación 2026 - Fixed</t>
+        </is>
+      </c>
+      <c r="E128" s="7" t="inlineStr">
         <is>
           <t>Fiduagraria</t>
         </is>
       </c>
-      <c r="F126" s="12" t="inlineStr">
-        <is>
-          <t>Operación</t>
-        </is>
-      </c>
-      <c r="G126" s="12" t="inlineStr">
-        <is>
-          <t>Ret</t>
-        </is>
-      </c>
-      <c r="H126" s="14" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I126" s="9" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="J126" s="14" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="K126" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L126" s="11" t="inlineStr">
-        <is>
-          <t>Oscar Barragan</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="18" customHeight="1">
-      <c r="A127" s="5" t="inlineStr">
-        <is>
-          <t>Oscar Barragan</t>
-        </is>
-      </c>
-      <c r="B127" s="6" t="inlineStr">
-        <is>
-          <t>P2637</t>
-        </is>
-      </c>
-      <c r="C127" s="6" t="inlineStr">
-        <is>
-          <t>AGR</t>
-        </is>
-      </c>
-      <c r="D127" s="7" t="inlineStr">
-        <is>
-          <t>AGR - CP Suite ( Smartcash) Operación 2026 - Cloud</t>
-        </is>
-      </c>
-      <c r="E127" s="7" t="inlineStr">
-        <is>
-          <t>Fiduagraria</t>
-        </is>
-      </c>
-      <c r="F127" s="6" t="inlineStr">
-        <is>
-          <t>Data</t>
-        </is>
-      </c>
-      <c r="G127" s="6" t="inlineStr">
-        <is>
-          <t>Cloud</t>
-        </is>
-      </c>
-      <c r="H127" s="8" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I127" s="9" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="J127" s="8" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="K127" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L127" s="5" t="inlineStr">
-        <is>
-          <t>Oscar Barragan</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="18" customHeight="1">
-      <c r="A128" s="11" t="inlineStr">
-        <is>
-          <t>Oscar Barragan</t>
-        </is>
-      </c>
-      <c r="B128" s="12" t="inlineStr">
-        <is>
-          <t>P2638</t>
-        </is>
-      </c>
-      <c r="C128" s="12" t="inlineStr">
-        <is>
-          <t>AGR</t>
-        </is>
-      </c>
-      <c r="D128" s="13" t="inlineStr">
-        <is>
-          <t>AGR - CP Suite ( Smartcash) Operación 2026 - Ret SW</t>
-        </is>
-      </c>
-      <c r="E128" s="13" t="inlineStr">
-        <is>
-          <t>Fiduagraria</t>
-        </is>
-      </c>
-      <c r="F128" s="12" t="inlineStr">
-        <is>
-          <t>Software SW</t>
-        </is>
-      </c>
-      <c r="G128" s="12" t="inlineStr">
-        <is>
-          <t>Ret SW</t>
-        </is>
-      </c>
-      <c r="H128" s="14" t="n">
+      <c r="F128" s="6" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="G128" s="6" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H128" s="8" t="n">
         <v>0.8</v>
       </c>
       <c r="I128" s="9" t="n">
         <v>0.004</v>
       </c>
-      <c r="J128" s="14" t="n">
+      <c r="J128" s="8" t="n">
         <v>16.2</v>
       </c>
-      <c r="K128" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L128" s="11" t="inlineStr">
+      <c r="K128" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L128" s="5" t="inlineStr">
         <is>
           <t>Oscar Barragan</t>
         </is>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>P2639</t>
+          <t>P2636</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
@@ -7500,7 +7500,7 @@
       </c>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>AGR - Quicksight Operación 2026 - Cloud</t>
+          <t>AGR - CP Suite ( Smartcash) Operación 2026 - Ret</t>
         </is>
       </c>
       <c r="E129" s="7" t="inlineStr">
@@ -7510,22 +7510,22 @@
       </c>
       <c r="F129" s="6" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="G129" s="6" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>Ret</t>
         </is>
       </c>
       <c r="H129" s="8" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>0.015</v>
+        <v>0.004</v>
       </c>
       <c r="J129" s="8" t="n">
-        <v>64.8</v>
+        <v>16.2</v>
       </c>
       <c r="K129" s="10" t="inlineStr">
         <is>
@@ -7546,42 +7546,42 @@
       </c>
       <c r="B130" s="12" t="inlineStr">
         <is>
-          <t>P1920</t>
+          <t>P2637</t>
         </is>
       </c>
       <c r="C130" s="12" t="inlineStr">
         <is>
-          <t>BTG</t>
+          <t>AGR</t>
         </is>
       </c>
       <c r="D130" s="13" t="inlineStr">
         <is>
-          <t>BTG - SmartCash - Operación - Ret SW</t>
+          <t>AGR - CP Suite ( Smartcash) Operación 2026 - Cloud</t>
         </is>
       </c>
       <c r="E130" s="13" t="inlineStr">
         <is>
-          <t>BTG Pactual Colombia</t>
+          <t>Fiduagraria</t>
         </is>
       </c>
       <c r="F130" s="12" t="inlineStr">
         <is>
-          <t>Software SW</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="G130" s="12" t="inlineStr">
         <is>
-          <t>Ret SW</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="H130" s="14" t="n">
-        <v>19</v>
-      </c>
-      <c r="I130" s="18" t="n">
-        <v>0.098</v>
+        <v>0.8</v>
+      </c>
+      <c r="I130" s="9" t="n">
+        <v>0.004</v>
       </c>
       <c r="J130" s="14" t="n">
-        <v>373.5</v>
+        <v>16.2</v>
       </c>
       <c r="K130" s="15" t="inlineStr">
         <is>
@@ -7602,42 +7602,42 @@
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>P2012</t>
+          <t>P2638</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>BTG</t>
+          <t>AGR</t>
         </is>
       </c>
       <c r="D131" s="7" t="inlineStr">
         <is>
-          <t>BTG - SmartCash - Operación - Ret</t>
+          <t>AGR - CP Suite ( Smartcash) Operación 2026 - Ret SW</t>
         </is>
       </c>
       <c r="E131" s="7" t="inlineStr">
         <is>
-          <t>BTG Pactual</t>
+          <t>Fiduagraria</t>
         </is>
       </c>
       <c r="F131" s="6" t="inlineStr">
         <is>
-          <t>Operación</t>
+          <t>Software SW</t>
         </is>
       </c>
       <c r="G131" s="6" t="inlineStr">
         <is>
-          <t>Ret</t>
+          <t>Ret SW</t>
         </is>
       </c>
       <c r="H131" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="I131" s="18" t="n">
-        <v>0.098</v>
+        <v>0.8</v>
+      </c>
+      <c r="I131" s="9" t="n">
+        <v>0.004</v>
       </c>
       <c r="J131" s="8" t="n">
-        <v>373.5</v>
+        <v>16.2</v>
       </c>
       <c r="K131" s="10" t="inlineStr">
         <is>
@@ -7658,22 +7658,22 @@
       </c>
       <c r="B132" s="12" t="inlineStr">
         <is>
-          <t>P2121</t>
+          <t>P2639</t>
         </is>
       </c>
       <c r="C132" s="12" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>AGR</t>
         </is>
       </c>
       <c r="D132" s="13" t="inlineStr">
         <is>
-          <t>CAT - Agente Cognitivo e Infraestructura AWS - Cloud</t>
+          <t>AGR - Quicksight Operación 2026 - Cloud</t>
         </is>
       </c>
       <c r="E132" s="13" t="inlineStr">
         <is>
-          <t>Unidad Administrativa Especial de Catastro Distrital</t>
+          <t>Fiduagraria</t>
         </is>
       </c>
       <c r="F132" s="12" t="inlineStr">
@@ -7687,13 +7687,13 @@
         </is>
       </c>
       <c r="H132" s="14" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="I132" s="9" t="n">
-        <v>0.017</v>
+        <v>0.015</v>
       </c>
       <c r="J132" s="14" t="n">
-        <v>44.3</v>
+        <v>64.8</v>
       </c>
       <c r="K132" s="15" t="inlineStr">
         <is>
@@ -7714,42 +7714,42 @@
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>P2122</t>
+          <t>P1920</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>BTG</t>
         </is>
       </c>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>CAT - Agente Cognitivo e Infraestructura AWS - Ret</t>
+          <t>BTG - SmartCash - Operación - Ret SW</t>
         </is>
       </c>
       <c r="E133" s="7" t="inlineStr">
         <is>
-          <t>Unidad Administrativa Especial de Catastro Distrital</t>
+          <t>BTG Pactual Colombia</t>
         </is>
       </c>
       <c r="F133" s="6" t="inlineStr">
         <is>
-          <t>Operación</t>
+          <t>Software SW</t>
         </is>
       </c>
       <c r="G133" s="6" t="inlineStr">
         <is>
-          <t>Ret</t>
+          <t>Ret SW</t>
         </is>
       </c>
       <c r="H133" s="8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I133" s="9" t="n">
-        <v>0.017</v>
+        <v>19</v>
+      </c>
+      <c r="I133" s="18" t="n">
+        <v>0.098</v>
       </c>
       <c r="J133" s="8" t="n">
-        <v>44.3</v>
+        <v>373.5</v>
       </c>
       <c r="K133" s="10" t="inlineStr">
         <is>
@@ -7770,42 +7770,42 @@
       </c>
       <c r="B134" s="12" t="inlineStr">
         <is>
-          <t>P2123</t>
+          <t>P2012</t>
         </is>
       </c>
       <c r="C134" s="12" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>BTG</t>
         </is>
       </c>
       <c r="D134" s="13" t="inlineStr">
         <is>
-          <t>CAT - Agente Cognitivo e Infraestructura AWS - Ret SW</t>
+          <t>BTG - SmartCash - Operación - Ret</t>
         </is>
       </c>
       <c r="E134" s="13" t="inlineStr">
         <is>
-          <t>Unidad Administrativa Especial de Catastro Distrital</t>
+          <t>BTG Pactual</t>
         </is>
       </c>
       <c r="F134" s="12" t="inlineStr">
         <is>
-          <t>Software SW</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="G134" s="12" t="inlineStr">
         <is>
-          <t>Ret SW</t>
+          <t>Ret</t>
         </is>
       </c>
       <c r="H134" s="14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I134" s="9" t="n">
-        <v>0.017</v>
+        <v>19</v>
+      </c>
+      <c r="I134" s="18" t="n">
+        <v>0.098</v>
       </c>
       <c r="J134" s="14" t="n">
-        <v>44.3</v>
+        <v>373.5</v>
       </c>
       <c r="K134" s="15" t="inlineStr">
         <is>
@@ -7826,7 +7826,7 @@
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>P2124</t>
+          <t>P2121</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>CAT - Agente Cognitivo e Infraestructura AWS - Fixed</t>
+          <t>CAT - Agente Cognitivo e Infraestructura AWS - Cloud</t>
         </is>
       </c>
       <c r="E135" s="7" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="F135" s="6" t="inlineStr">
         <is>
-          <t>Implementación</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="G135" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="H135" s="8" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="B136" s="12" t="inlineStr">
         <is>
-          <t>P2736</t>
+          <t>P2122</t>
         </is>
       </c>
       <c r="C136" s="12" t="inlineStr">
@@ -7892,32 +7892,32 @@
       </c>
       <c r="D136" s="13" t="inlineStr">
         <is>
-          <t>CAT - Fase 3 - Fixed</t>
+          <t>CAT - Agente Cognitivo e Infraestructura AWS - Ret</t>
         </is>
       </c>
       <c r="E136" s="13" t="inlineStr">
         <is>
-          <t>Catastro</t>
+          <t>Unidad Administrativa Especial de Catastro Distrital</t>
         </is>
       </c>
       <c r="F136" s="12" t="inlineStr">
         <is>
-          <t>Implementación</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="G136" s="12" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Ret</t>
         </is>
       </c>
       <c r="H136" s="14" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="I136" s="9" t="n">
-        <v>0.023</v>
+        <v>0.017</v>
       </c>
       <c r="J136" s="14" t="n">
-        <v>59.1</v>
+        <v>44.3</v>
       </c>
       <c r="K136" s="15" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>P2737</t>
+          <t>P2123</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
@@ -7948,32 +7948,32 @@
       </c>
       <c r="D137" s="7" t="inlineStr">
         <is>
-          <t>CAT - Fase 3 - Ret</t>
+          <t>CAT - Agente Cognitivo e Infraestructura AWS - Ret SW</t>
         </is>
       </c>
       <c r="E137" s="7" t="inlineStr">
         <is>
-          <t>Catastro</t>
+          <t>Unidad Administrativa Especial de Catastro Distrital</t>
         </is>
       </c>
       <c r="F137" s="6" t="inlineStr">
         <is>
-          <t>Operación</t>
+          <t>Software SW</t>
         </is>
       </c>
       <c r="G137" s="6" t="inlineStr">
         <is>
-          <t>Ret</t>
+          <t>Ret SW</t>
         </is>
       </c>
       <c r="H137" s="8" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="I137" s="9" t="n">
-        <v>0.023</v>
+        <v>0.017</v>
       </c>
       <c r="J137" s="8" t="n">
-        <v>59.1</v>
+        <v>44.3</v>
       </c>
       <c r="K137" s="10" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
       </c>
       <c r="B138" s="12" t="inlineStr">
         <is>
-          <t>P2738</t>
+          <t>P2124</t>
         </is>
       </c>
       <c r="C138" s="12" t="inlineStr">
@@ -8004,32 +8004,32 @@
       </c>
       <c r="D138" s="13" t="inlineStr">
         <is>
-          <t>CAT - Fase 3 - Cloud</t>
+          <t>CAT - Agente Cognitivo e Infraestructura AWS - Fixed</t>
         </is>
       </c>
       <c r="E138" s="13" t="inlineStr">
         <is>
-          <t>Catatro</t>
+          <t>Unidad Administrativa Especial de Catastro Distrital</t>
         </is>
       </c>
       <c r="F138" s="12" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Implementación</t>
         </is>
       </c>
       <c r="G138" s="12" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H138" s="14" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="I138" s="9" t="n">
-        <v>0.023</v>
+        <v>0.017</v>
       </c>
       <c r="J138" s="14" t="n">
-        <v>59.1</v>
+        <v>44.3</v>
       </c>
       <c r="K138" s="15" t="inlineStr">
         <is>
@@ -8050,42 +8050,42 @@
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>P2214</t>
+          <t>P2736</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>PRO</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="D139" s="7" t="inlineStr">
         <is>
-          <t>PRO - SmartCash - Operación - Ret</t>
+          <t>CAT - Fase 3 - Fixed</t>
         </is>
       </c>
       <c r="E139" s="7" t="inlineStr">
         <is>
-          <t>Progresión</t>
+          <t>Catastro</t>
         </is>
       </c>
       <c r="F139" s="6" t="inlineStr">
         <is>
-          <t>Operación</t>
+          <t>Implementación</t>
         </is>
       </c>
       <c r="G139" s="6" t="inlineStr">
         <is>
-          <t>Ret</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H139" s="8" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="I139" s="9" t="n">
-        <v>0.036</v>
+        <v>0.023</v>
       </c>
       <c r="J139" s="8" t="n">
-        <v>138.7</v>
+        <v>59.1</v>
       </c>
       <c r="K139" s="10" t="inlineStr">
         <is>
@@ -8106,42 +8106,42 @@
       </c>
       <c r="B140" s="12" t="inlineStr">
         <is>
-          <t>P2215</t>
+          <t>P2737</t>
         </is>
       </c>
       <c r="C140" s="12" t="inlineStr">
         <is>
-          <t>PRO</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="D140" s="13" t="inlineStr">
         <is>
-          <t>PRO - SmartCash - Operación - Cloud</t>
+          <t>CAT - Fase 3 - Ret</t>
         </is>
       </c>
       <c r="E140" s="13" t="inlineStr">
         <is>
-          <t>Progresión</t>
+          <t>Catastro</t>
         </is>
       </c>
       <c r="F140" s="12" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="G140" s="12" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>Ret</t>
         </is>
       </c>
       <c r="H140" s="14" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="I140" s="9" t="n">
-        <v>0.036</v>
+        <v>0.023</v>
       </c>
       <c r="J140" s="14" t="n">
-        <v>138.7</v>
+        <v>59.1</v>
       </c>
       <c r="K140" s="15" t="inlineStr">
         <is>
@@ -8162,42 +8162,42 @@
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>P2717</t>
+          <t>P2738</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>UCA</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="D141" s="7" t="inlineStr">
         <is>
-          <t>UCA - Renovación Semestre 1 - 2025 - Ret</t>
+          <t>CAT - Fase 3 - Cloud</t>
         </is>
       </c>
       <c r="E141" s="7" t="inlineStr">
         <is>
-          <t>Universidad de Caldas</t>
+          <t>Catatro</t>
         </is>
       </c>
       <c r="F141" s="6" t="inlineStr">
         <is>
-          <t>Operación</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="G141" s="6" t="inlineStr">
         <is>
-          <t>Ret</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="H141" s="8" t="n">
-        <v>10</v>
+        <v>4.5</v>
       </c>
       <c r="I141" s="9" t="n">
-        <v>0.052</v>
+        <v>0.023</v>
       </c>
       <c r="J141" s="8" t="n">
-        <v>676.8</v>
+        <v>59.1</v>
       </c>
       <c r="K141" s="10" t="inlineStr">
         <is>
@@ -8218,42 +8218,42 @@
       </c>
       <c r="B142" s="12" t="inlineStr">
         <is>
-          <t>P2059</t>
+          <t>P2214</t>
         </is>
       </c>
       <c r="C142" s="12" t="inlineStr">
         <is>
-          <t>UNA</t>
+          <t>PRO</t>
         </is>
       </c>
       <c r="D142" s="13" t="inlineStr">
         <is>
-          <t>UNA - Contrato 4 - Servicio Computacion - Cloud</t>
+          <t>PRO - SmartCash - Operación - Ret</t>
         </is>
       </c>
       <c r="E142" s="13" t="inlineStr">
         <is>
-          <t>Universidad Nacional de Colombia</t>
+          <t>Progresión</t>
         </is>
       </c>
       <c r="F142" s="12" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="G142" s="12" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>Ret</t>
         </is>
       </c>
       <c r="H142" s="14" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I142" s="9" t="n">
-        <v>0.015</v>
+        <v>0.036</v>
       </c>
       <c r="J142" s="14" t="n">
-        <v>37.9</v>
+        <v>138.7</v>
       </c>
       <c r="K142" s="15" t="inlineStr">
         <is>
@@ -8274,42 +8274,42 @@
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>P2068</t>
+          <t>P2215</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>UNA</t>
+          <t>PRO</t>
         </is>
       </c>
       <c r="D143" s="7" t="inlineStr">
         <is>
-          <t>UNA - Contrato 4 - Servicio Computacion - Ret</t>
+          <t>PRO - SmartCash - Operación - Cloud</t>
         </is>
       </c>
       <c r="E143" s="7" t="inlineStr">
         <is>
-          <t>Universidad Nacional de Colombia</t>
+          <t>Progresión</t>
         </is>
       </c>
       <c r="F143" s="6" t="inlineStr">
         <is>
-          <t>Operación</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="G143" s="6" t="inlineStr">
         <is>
-          <t>Ret</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="H143" s="8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I143" s="9" t="n">
-        <v>0.015</v>
+        <v>0.036</v>
       </c>
       <c r="J143" s="8" t="n">
-        <v>37.9</v>
+        <v>138.7</v>
       </c>
       <c r="K143" s="10" t="inlineStr">
         <is>
@@ -8330,22 +8330,22 @@
       </c>
       <c r="B144" s="12" t="inlineStr">
         <is>
-          <t>P1991</t>
+          <t>P2717</t>
         </is>
       </c>
       <c r="C144" s="12" t="inlineStr">
         <is>
-          <t>UNA</t>
+          <t>UCA</t>
         </is>
       </c>
       <c r="D144" s="13" t="inlineStr">
         <is>
-          <t>UNA - Dinara de UNAL - Ret</t>
+          <t>UCA - Renovación Semestre 1 - 2025 - Ret</t>
         </is>
       </c>
       <c r="E144" s="13" t="inlineStr">
         <is>
-          <t>Universidad Nacional de Colombia</t>
+          <t>Universidad de Caldas</t>
         </is>
       </c>
       <c r="F144" s="12" t="inlineStr">
@@ -8359,13 +8359,13 @@
         </is>
       </c>
       <c r="H144" s="14" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I144" s="9" t="n">
-        <v>0.015</v>
+        <v>0.052</v>
       </c>
       <c r="J144" s="14" t="n">
-        <v>37.9</v>
+        <v>676.8</v>
       </c>
       <c r="K144" s="15" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="B145" s="6" t="inlineStr">
         <is>
-          <t>P2061</t>
+          <t>P2059</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="D145" s="7" t="inlineStr">
         <is>
-          <t>UNA - Dinara de UNAL - Cloud</t>
+          <t>UNA - Contrato 4 - Servicio Computacion - Cloud</t>
         </is>
       </c>
       <c r="E145" s="7" t="inlineStr">
@@ -8442,7 +8442,7 @@
       </c>
       <c r="B146" s="12" t="inlineStr">
         <is>
-          <t>P1973</t>
+          <t>P2068</t>
         </is>
       </c>
       <c r="C146" s="12" t="inlineStr">
@@ -8452,7 +8452,7 @@
       </c>
       <c r="D146" s="13" t="inlineStr">
         <is>
-          <t>UNA - Editorial de UNAL - Cloud</t>
+          <t>UNA - Contrato 4 - Servicio Computacion - Ret</t>
         </is>
       </c>
       <c r="E146" s="13" t="inlineStr">
@@ -8462,22 +8462,22 @@
       </c>
       <c r="F146" s="12" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="G146" s="12" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>Ret</t>
         </is>
       </c>
       <c r="H146" s="14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I146" s="9" t="n">
-        <v>0.031</v>
+        <v>0.015</v>
       </c>
       <c r="J146" s="14" t="n">
-        <v>75.8</v>
+        <v>37.9</v>
       </c>
       <c r="K146" s="15" t="inlineStr">
         <is>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>P2427</t>
+          <t>P1991</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
@@ -8508,7 +8508,7 @@
       </c>
       <c r="D147" s="7" t="inlineStr">
         <is>
-          <t>UNA - Egresados Cloud - Cloud</t>
+          <t>UNA - Dinara de UNAL - Ret</t>
         </is>
       </c>
       <c r="E147" s="7" t="inlineStr">
@@ -8518,22 +8518,22 @@
       </c>
       <c r="F147" s="6" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="G147" s="6" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>Ret</t>
         </is>
       </c>
       <c r="H147" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I147" s="9" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="J147" s="8" t="n">
-        <v>25.3</v>
+        <v>37.9</v>
       </c>
       <c r="K147" s="10" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
       </c>
       <c r="B148" s="12" t="inlineStr">
         <is>
-          <t>P2428</t>
+          <t>P2061</t>
         </is>
       </c>
       <c r="C148" s="12" t="inlineStr">
@@ -8564,7 +8564,7 @@
       </c>
       <c r="D148" s="13" t="inlineStr">
         <is>
-          <t>UNA - Egresados Cloud - Cloud</t>
+          <t>UNA - Dinara de UNAL - Cloud</t>
         </is>
       </c>
       <c r="E148" s="13" t="inlineStr">
@@ -8583,13 +8583,13 @@
         </is>
       </c>
       <c r="H148" s="14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I148" s="9" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="J148" s="14" t="n">
-        <v>25.3</v>
+        <v>37.9</v>
       </c>
       <c r="K148" s="15" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>P2429</t>
+          <t>P1973</t>
         </is>
       </c>
       <c r="C149" s="6" t="inlineStr">
@@ -8620,7 +8620,7 @@
       </c>
       <c r="D149" s="7" t="inlineStr">
         <is>
-          <t>UNA - Egresados Cloud - Cloud</t>
+          <t>UNA - Editorial de UNAL - Cloud</t>
         </is>
       </c>
       <c r="E149" s="7" t="inlineStr">
@@ -8639,13 +8639,13 @@
         </is>
       </c>
       <c r="H149" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I149" s="9" t="n">
-        <v>0.01</v>
+        <v>0.031</v>
       </c>
       <c r="J149" s="8" t="n">
-        <v>25.3</v>
+        <v>75.8</v>
       </c>
       <c r="K149" s="10" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="B150" s="12" t="inlineStr">
         <is>
-          <t>P2062</t>
+          <t>P2427</t>
         </is>
       </c>
       <c r="C150" s="12" t="inlineStr">
@@ -8676,7 +8676,7 @@
       </c>
       <c r="D150" s="13" t="inlineStr">
         <is>
-          <t>UNA - Facultad de Derecho - Cloud</t>
+          <t>UNA - Egresados Cloud - Cloud</t>
         </is>
       </c>
       <c r="E150" s="13" t="inlineStr">
@@ -8695,13 +8695,13 @@
         </is>
       </c>
       <c r="H150" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I150" s="9" t="n">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="J150" s="14" t="n">
-        <v>37.9</v>
+        <v>25.3</v>
       </c>
       <c r="K150" s="15" t="inlineStr">
         <is>
@@ -8722,7 +8722,7 @@
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>P2556</t>
+          <t>P2428</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr">
@@ -8732,7 +8732,7 @@
       </c>
       <c r="D151" s="7" t="inlineStr">
         <is>
-          <t>UNA - Facultad de Derecho - Ret</t>
+          <t>UNA - Egresados Cloud - Cloud</t>
         </is>
       </c>
       <c r="E151" s="7" t="inlineStr">
@@ -8742,22 +8742,22 @@
       </c>
       <c r="F151" s="6" t="inlineStr">
         <is>
-          <t>Operación</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="G151" s="6" t="inlineStr">
         <is>
-          <t>Ret</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="H151" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I151" s="9" t="n">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="J151" s="8" t="n">
-        <v>37.9</v>
+        <v>25.3</v>
       </c>
       <c r="K151" s="10" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
       </c>
       <c r="B152" s="12" t="inlineStr">
         <is>
-          <t>P2037</t>
+          <t>P2429</t>
         </is>
       </c>
       <c r="C152" s="12" t="inlineStr">
@@ -8788,7 +8788,7 @@
       </c>
       <c r="D152" s="13" t="inlineStr">
         <is>
-          <t>UNA - Facultad de Derecho concurso méritos - Cloud</t>
+          <t>UNA - Egresados Cloud - Cloud</t>
         </is>
       </c>
       <c r="E152" s="13" t="inlineStr">
@@ -8807,13 +8807,13 @@
         </is>
       </c>
       <c r="H152" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I152" s="9" t="n">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="J152" s="14" t="n">
-        <v>37.9</v>
+        <v>25.3</v>
       </c>
       <c r="K152" s="15" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>P2038</t>
+          <t>P2062</t>
         </is>
       </c>
       <c r="C153" s="6" t="inlineStr">
@@ -8844,7 +8844,7 @@
       </c>
       <c r="D153" s="7" t="inlineStr">
         <is>
-          <t>UNA - Facultad de Derecho concurso méritos - Ret</t>
+          <t>UNA - Facultad de Derecho - Cloud</t>
         </is>
       </c>
       <c r="E153" s="7" t="inlineStr">
@@ -8854,12 +8854,12 @@
       </c>
       <c r="F153" s="6" t="inlineStr">
         <is>
-          <t>Operación</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="G153" s="6" t="inlineStr">
         <is>
-          <t>Ret</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="H153" s="8" t="n">
@@ -8890,7 +8890,7 @@
       </c>
       <c r="B154" s="12" t="inlineStr">
         <is>
-          <t>P1975</t>
+          <t>P2556</t>
         </is>
       </c>
       <c r="C154" s="12" t="inlineStr">
@@ -8900,7 +8900,7 @@
       </c>
       <c r="D154" s="13" t="inlineStr">
         <is>
-          <t>UNA - Facultad de ingenieria - Ret</t>
+          <t>UNA - Facultad de Derecho - Ret</t>
         </is>
       </c>
       <c r="E154" s="13" t="inlineStr">
@@ -8946,7 +8946,7 @@
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>P2036</t>
+          <t>P2037</t>
         </is>
       </c>
       <c r="C155" s="6" t="inlineStr">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="D155" s="7" t="inlineStr">
         <is>
-          <t>UNA - Facultad de ingenieria - Cloud</t>
+          <t>UNA - Facultad de Derecho concurso méritos - Cloud</t>
         </is>
       </c>
       <c r="E155" s="7" t="inlineStr">
@@ -9002,7 +9002,7 @@
       </c>
       <c r="B156" s="12" t="inlineStr">
         <is>
-          <t>P1977</t>
+          <t>P2038</t>
         </is>
       </c>
       <c r="C156" s="12" t="inlineStr">
@@ -9012,7 +9012,7 @@
       </c>
       <c r="D156" s="13" t="inlineStr">
         <is>
-          <t>UNA - Fortinet - Fixed</t>
+          <t>UNA - Facultad de Derecho concurso méritos - Ret</t>
         </is>
       </c>
       <c r="E156" s="13" t="inlineStr">
@@ -9022,12 +9022,12 @@
       </c>
       <c r="F156" s="12" t="inlineStr">
         <is>
-          <t>Implementación</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="G156" s="12" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Ret</t>
         </is>
       </c>
       <c r="H156" s="14" t="n">
@@ -9058,7 +9058,7 @@
       </c>
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>P1978</t>
+          <t>P1975</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="D157" s="7" t="inlineStr">
         <is>
-          <t>UNA - Fortinet - Cloud</t>
+          <t>UNA - Facultad de ingenieria - Ret</t>
         </is>
       </c>
       <c r="E157" s="7" t="inlineStr">
@@ -9078,12 +9078,12 @@
       </c>
       <c r="F157" s="6" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="G157" s="6" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>Ret</t>
         </is>
       </c>
       <c r="H157" s="8" t="n">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="B158" s="12" t="inlineStr">
         <is>
-          <t>P2569</t>
+          <t>P2036</t>
         </is>
       </c>
       <c r="C158" s="12" t="inlineStr">
@@ -9124,7 +9124,7 @@
       </c>
       <c r="D158" s="13" t="inlineStr">
         <is>
-          <t>UNA - Fortinet 2 - Cloud</t>
+          <t>UNA - Facultad de ingenieria - Cloud</t>
         </is>
       </c>
       <c r="E158" s="13" t="inlineStr">
@@ -9143,13 +9143,13 @@
         </is>
       </c>
       <c r="H158" s="14" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="I158" s="9" t="n">
-        <v>0.008</v>
+        <v>0.015</v>
       </c>
       <c r="J158" s="14" t="n">
-        <v>19</v>
+        <v>37.9</v>
       </c>
       <c r="K158" s="15" t="inlineStr">
         <is>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>P2570</t>
+          <t>P1977</t>
         </is>
       </c>
       <c r="C159" s="6" t="inlineStr">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="D159" s="7" t="inlineStr">
         <is>
-          <t>UNA - Fortinet 2 - Ret</t>
+          <t>UNA - Fortinet - Fixed</t>
         </is>
       </c>
       <c r="E159" s="7" t="inlineStr">
@@ -9190,22 +9190,22 @@
       </c>
       <c r="F159" s="6" t="inlineStr">
         <is>
-          <t>Operación</t>
+          <t>Implementación</t>
         </is>
       </c>
       <c r="G159" s="6" t="inlineStr">
         <is>
-          <t>Ret</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H159" s="8" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="I159" s="9" t="n">
-        <v>0.008</v>
+        <v>0.015</v>
       </c>
       <c r="J159" s="8" t="n">
-        <v>19</v>
+        <v>37.9</v>
       </c>
       <c r="K159" s="10" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
       </c>
       <c r="B160" s="12" t="inlineStr">
         <is>
-          <t>P2571</t>
+          <t>P1978</t>
         </is>
       </c>
       <c r="C160" s="12" t="inlineStr">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="D160" s="13" t="inlineStr">
         <is>
-          <t>UNA - Fortinet 2 - Ret Other Vendors</t>
+          <t>UNA - Fortinet - Cloud</t>
         </is>
       </c>
       <c r="E160" s="13" t="inlineStr">
@@ -9246,22 +9246,22 @@
       </c>
       <c r="F160" s="12" t="inlineStr">
         <is>
-          <t>Operación</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="G160" s="12" t="inlineStr">
         <is>
-          <t>Ret Other Vendors</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="H160" s="14" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="I160" s="9" t="n">
-        <v>0.008</v>
+        <v>0.015</v>
       </c>
       <c r="J160" s="14" t="n">
-        <v>19</v>
+        <v>37.9</v>
       </c>
       <c r="K160" s="15" t="inlineStr">
         <is>
@@ -9282,7 +9282,7 @@
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>P2572</t>
+          <t>P2569</t>
         </is>
       </c>
       <c r="C161" s="6" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="D161" s="7" t="inlineStr">
         <is>
-          <t>UNA - Fortinet 2 - Fixed</t>
+          <t>UNA - Fortinet 2 - Cloud</t>
         </is>
       </c>
       <c r="E161" s="7" t="inlineStr">
@@ -9302,12 +9302,12 @@
       </c>
       <c r="F161" s="6" t="inlineStr">
         <is>
-          <t>Implementación</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="G161" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="H161" s="8" t="n">
@@ -9338,7 +9338,7 @@
       </c>
       <c r="B162" s="12" t="inlineStr">
         <is>
-          <t>P1979</t>
+          <t>P2570</t>
         </is>
       </c>
       <c r="C162" s="12" t="inlineStr">
@@ -9348,7 +9348,7 @@
       </c>
       <c r="D162" s="13" t="inlineStr">
         <is>
-          <t>UNA - Gestión de Información - Fixed</t>
+          <t>UNA - Fortinet 2 - Ret</t>
         </is>
       </c>
       <c r="E162" s="13" t="inlineStr">
@@ -9358,22 +9358,22 @@
       </c>
       <c r="F162" s="12" t="inlineStr">
         <is>
-          <t>Implementación</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="G162" s="12" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Ret</t>
         </is>
       </c>
       <c r="H162" s="14" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="I162" s="9" t="n">
-        <v>0.01</v>
+        <v>0.008</v>
       </c>
       <c r="J162" s="14" t="n">
-        <v>25.3</v>
+        <v>19</v>
       </c>
       <c r="K162" s="15" t="inlineStr">
         <is>
@@ -9394,7 +9394,7 @@
       </c>
       <c r="B163" s="6" t="inlineStr">
         <is>
-          <t>P1980</t>
+          <t>P2571</t>
         </is>
       </c>
       <c r="C163" s="6" t="inlineStr">
@@ -9404,7 +9404,7 @@
       </c>
       <c r="D163" s="7" t="inlineStr">
         <is>
-          <t>UNA - Gestión de Información - Ret</t>
+          <t>UNA - Fortinet 2 - Ret Other Vendors</t>
         </is>
       </c>
       <c r="E163" s="7" t="inlineStr">
@@ -9419,17 +9419,17 @@
       </c>
       <c r="G163" s="6" t="inlineStr">
         <is>
-          <t>Ret</t>
+          <t>Ret Other Vendors</t>
         </is>
       </c>
       <c r="H163" s="8" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="I163" s="9" t="n">
-        <v>0.01</v>
+        <v>0.008</v>
       </c>
       <c r="J163" s="8" t="n">
-        <v>25.3</v>
+        <v>19</v>
       </c>
       <c r="K163" s="10" t="inlineStr">
         <is>
@@ -9450,7 +9450,7 @@
       </c>
       <c r="B164" s="12" t="inlineStr">
         <is>
-          <t>P1981</t>
+          <t>P2572</t>
         </is>
       </c>
       <c r="C164" s="12" t="inlineStr">
@@ -9460,7 +9460,7 @@
       </c>
       <c r="D164" s="13" t="inlineStr">
         <is>
-          <t>UNA - Gestión de Información - Cloud</t>
+          <t>UNA - Fortinet 2 - Fixed</t>
         </is>
       </c>
       <c r="E164" s="13" t="inlineStr">
@@ -9470,22 +9470,22 @@
       </c>
       <c r="F164" s="12" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Implementación</t>
         </is>
       </c>
       <c r="G164" s="12" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H164" s="14" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="I164" s="9" t="n">
-        <v>0.01</v>
+        <v>0.008</v>
       </c>
       <c r="J164" s="14" t="n">
-        <v>25.3</v>
+        <v>19</v>
       </c>
       <c r="K164" s="15" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
       </c>
       <c r="B165" s="6" t="inlineStr">
         <is>
-          <t>P1982</t>
+          <t>P1979</t>
         </is>
       </c>
       <c r="C165" s="6" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="D165" s="7" t="inlineStr">
         <is>
-          <t>UNA - HPC Registro y Matrícula - Cloud</t>
+          <t>UNA - Gestión de Información - Fixed</t>
         </is>
       </c>
       <c r="E165" s="7" t="inlineStr">
@@ -9526,22 +9526,22 @@
       </c>
       <c r="F165" s="6" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Implementación</t>
         </is>
       </c>
       <c r="G165" s="6" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H165" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I165" s="9" t="n">
-        <v>0.031</v>
+        <v>0.01</v>
       </c>
       <c r="J165" s="8" t="n">
-        <v>75.8</v>
+        <v>25.3</v>
       </c>
       <c r="K165" s="10" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
       </c>
       <c r="B166" s="12" t="inlineStr">
         <is>
-          <t>P1983</t>
+          <t>P1980</t>
         </is>
       </c>
       <c r="C166" s="12" t="inlineStr">
@@ -9572,7 +9572,7 @@
       </c>
       <c r="D166" s="13" t="inlineStr">
         <is>
-          <t>UNA - Laboratorios Virtuales - Cloud</t>
+          <t>UNA - Gestión de Información - Ret</t>
         </is>
       </c>
       <c r="E166" s="13" t="inlineStr">
@@ -9582,22 +9582,22 @@
       </c>
       <c r="F166" s="12" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="G166" s="12" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>Ret</t>
         </is>
       </c>
       <c r="H166" s="14" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I166" s="9" t="n">
-        <v>0.031</v>
+        <v>0.01</v>
       </c>
       <c r="J166" s="14" t="n">
-        <v>75.8</v>
+        <v>25.3</v>
       </c>
       <c r="K166" s="15" t="inlineStr">
         <is>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="B167" s="6" t="inlineStr">
         <is>
-          <t>P2066</t>
+          <t>P1981</t>
         </is>
       </c>
       <c r="C167" s="6" t="inlineStr">
@@ -9628,7 +9628,7 @@
       </c>
       <c r="D167" s="7" t="inlineStr">
         <is>
-          <t>UNA - OSE 26 Admisiones - Cloud</t>
+          <t>UNA - Gestión de Información - Cloud</t>
         </is>
       </c>
       <c r="E167" s="7" t="inlineStr">
@@ -9647,13 +9647,13 @@
         </is>
       </c>
       <c r="H167" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I167" s="9" t="n">
-        <v>0.031</v>
+        <v>0.01</v>
       </c>
       <c r="J167" s="8" t="n">
-        <v>75.8</v>
+        <v>25.3</v>
       </c>
       <c r="K167" s="10" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
       </c>
       <c r="B168" s="12" t="inlineStr">
         <is>
-          <t>P2067</t>
+          <t>P1982</t>
         </is>
       </c>
       <c r="C168" s="12" t="inlineStr">
@@ -9684,7 +9684,7 @@
       </c>
       <c r="D168" s="13" t="inlineStr">
         <is>
-          <t>UNA - OSE 43 Moodle Extensión - Cloud</t>
+          <t>UNA - HPC Registro y Matrícula - Cloud</t>
         </is>
       </c>
       <c r="E168" s="13" t="inlineStr">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="H168" s="14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I168" s="9" t="n">
-        <v>0.015</v>
+        <v>0.031</v>
       </c>
       <c r="J168" s="14" t="n">
-        <v>37.9</v>
+        <v>75.8</v>
       </c>
       <c r="K168" s="15" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
       </c>
       <c r="B169" s="6" t="inlineStr">
         <is>
-          <t>P2560</t>
+          <t>P1983</t>
         </is>
       </c>
       <c r="C169" s="6" t="inlineStr">
@@ -9740,7 +9740,7 @@
       </c>
       <c r="D169" s="7" t="inlineStr">
         <is>
-          <t>UNA - OSE 43 Moodle Extensión - Ret</t>
+          <t>UNA - Laboratorios Virtuales - Cloud</t>
         </is>
       </c>
       <c r="E169" s="7" t="inlineStr">
@@ -9750,22 +9750,22 @@
       </c>
       <c r="F169" s="6" t="inlineStr">
         <is>
-          <t>Operación</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="G169" s="6" t="inlineStr">
         <is>
-          <t>Ret</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="H169" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I169" s="9" t="n">
-        <v>0.015</v>
+        <v>0.031</v>
       </c>
       <c r="J169" s="8" t="n">
-        <v>37.9</v>
+        <v>75.8</v>
       </c>
       <c r="K169" s="10" t="inlineStr">
         <is>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="B170" s="12" t="inlineStr">
         <is>
-          <t>P2063</t>
+          <t>P2066</t>
         </is>
       </c>
       <c r="C170" s="12" t="inlineStr">
@@ -9796,7 +9796,7 @@
       </c>
       <c r="D170" s="13" t="inlineStr">
         <is>
-          <t>UNA - Ofc Gestion Ambiental - Cloud</t>
+          <t>UNA - OSE 26 Admisiones - Cloud</t>
         </is>
       </c>
       <c r="E170" s="13" t="inlineStr">
@@ -9815,13 +9815,13 @@
         </is>
       </c>
       <c r="H170" s="14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I170" s="9" t="n">
-        <v>0.015</v>
+        <v>0.031</v>
       </c>
       <c r="J170" s="14" t="n">
-        <v>37.9</v>
+        <v>75.8</v>
       </c>
       <c r="K170" s="15" t="inlineStr">
         <is>
@@ -9842,7 +9842,7 @@
       </c>
       <c r="B171" s="6" t="inlineStr">
         <is>
-          <t>P2064</t>
+          <t>P2067</t>
         </is>
       </c>
       <c r="C171" s="6" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="D171" s="7" t="inlineStr">
         <is>
-          <t>UNA - Ofc Gestion Ambiental - Fixed</t>
+          <t>UNA - OSE 43 Moodle Extensión - Cloud</t>
         </is>
       </c>
       <c r="E171" s="7" t="inlineStr">
@@ -9862,12 +9862,12 @@
       </c>
       <c r="F171" s="6" t="inlineStr">
         <is>
-          <t>Implementación</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="G171" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="H171" s="8" t="n">
@@ -9898,7 +9898,7 @@
       </c>
       <c r="B172" s="12" t="inlineStr">
         <is>
-          <t>P1994</t>
+          <t>P2560</t>
         </is>
       </c>
       <c r="C172" s="12" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="D172" s="13" t="inlineStr">
         <is>
-          <t>UNA - Regalías Sikie - Cloud</t>
+          <t>UNA - OSE 43 Moodle Extensión - Ret</t>
         </is>
       </c>
       <c r="E172" s="13" t="inlineStr">
@@ -9918,22 +9918,22 @@
       </c>
       <c r="F172" s="12" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="G172" s="12" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>Ret</t>
         </is>
       </c>
       <c r="H172" s="14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I172" s="9" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="J172" s="14" t="n">
-        <v>25.3</v>
+        <v>37.9</v>
       </c>
       <c r="K172" s="15" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
       </c>
       <c r="B173" s="6" t="inlineStr">
         <is>
-          <t>P2537</t>
+          <t>P2063</t>
         </is>
       </c>
       <c r="C173" s="6" t="inlineStr">
@@ -9964,7 +9964,7 @@
       </c>
       <c r="D173" s="7" t="inlineStr">
         <is>
-          <t>UNA - Regalías Sikie - Ret</t>
+          <t>UNA - Ofc Gestion Ambiental - Cloud</t>
         </is>
       </c>
       <c r="E173" s="7" t="inlineStr">
@@ -9974,22 +9974,22 @@
       </c>
       <c r="F173" s="6" t="inlineStr">
         <is>
-          <t>Operación</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="G173" s="6" t="inlineStr">
         <is>
-          <t>Ret</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="H173" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I173" s="9" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="J173" s="8" t="n">
-        <v>25.3</v>
+        <v>37.9</v>
       </c>
       <c r="K173" s="10" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
       </c>
       <c r="B174" s="12" t="inlineStr">
         <is>
-          <t>P2537</t>
+          <t>P2064</t>
         </is>
       </c>
       <c r="C174" s="12" t="inlineStr">
@@ -10020,7 +10020,7 @@
       </c>
       <c r="D174" s="13" t="inlineStr">
         <is>
-          <t>UNA - Regalías Sikie - Ret</t>
+          <t>UNA - Ofc Gestion Ambiental - Fixed</t>
         </is>
       </c>
       <c r="E174" s="13" t="inlineStr">
@@ -10030,22 +10030,22 @@
       </c>
       <c r="F174" s="12" t="inlineStr">
         <is>
-          <t>Operación</t>
+          <t>Implementación</t>
         </is>
       </c>
       <c r="G174" s="12" t="inlineStr">
         <is>
-          <t>Ret</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H174" s="14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I174" s="9" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="J174" s="14" t="n">
-        <v>25.3</v>
+        <v>37.9</v>
       </c>
       <c r="K174" s="15" t="inlineStr">
         <is>
@@ -10066,7 +10066,7 @@
       </c>
       <c r="B175" s="6" t="inlineStr">
         <is>
-          <t>P1988</t>
+          <t>P1994</t>
         </is>
       </c>
       <c r="C175" s="6" t="inlineStr">
@@ -10076,7 +10076,7 @@
       </c>
       <c r="D175" s="7" t="inlineStr">
         <is>
-          <t>UNA - Repositorio - Cloud</t>
+          <t>UNA - Regalías Sikie - Cloud</t>
         </is>
       </c>
       <c r="E175" s="7" t="inlineStr">
@@ -10095,13 +10095,13 @@
         </is>
       </c>
       <c r="H175" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I175" s="9" t="n">
-        <v>0.031</v>
+        <v>0.01</v>
       </c>
       <c r="J175" s="8" t="n">
-        <v>75.8</v>
+        <v>25.3</v>
       </c>
       <c r="K175" s="10" t="inlineStr">
         <is>
@@ -10122,7 +10122,7 @@
       </c>
       <c r="B176" s="12" t="inlineStr">
         <is>
-          <t>P2243</t>
+          <t>P2537</t>
         </is>
       </c>
       <c r="C176" s="12" t="inlineStr">
@@ -10132,7 +10132,7 @@
       </c>
       <c r="D176" s="13" t="inlineStr">
         <is>
-          <t>UNA - Secretaría General - Fixed</t>
+          <t>UNA - Regalías Sikie - Ret</t>
         </is>
       </c>
       <c r="E176" s="13" t="inlineStr">
@@ -10142,22 +10142,22 @@
       </c>
       <c r="F176" s="12" t="inlineStr">
         <is>
-          <t>Implementación</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="G176" s="12" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Ret</t>
         </is>
       </c>
       <c r="H176" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I176" s="9" t="n">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="J176" s="14" t="n">
-        <v>37.9</v>
+        <v>25.3</v>
       </c>
       <c r="K176" s="15" t="inlineStr">
         <is>
@@ -10178,7 +10178,7 @@
       </c>
       <c r="B177" s="6" t="inlineStr">
         <is>
-          <t>P2246</t>
+          <t>P2537</t>
         </is>
       </c>
       <c r="C177" s="6" t="inlineStr">
@@ -10188,7 +10188,7 @@
       </c>
       <c r="D177" s="7" t="inlineStr">
         <is>
-          <t>UNA - Secretaría General - Cloud</t>
+          <t>UNA - Regalías Sikie - Ret</t>
         </is>
       </c>
       <c r="E177" s="7" t="inlineStr">
@@ -10198,22 +10198,22 @@
       </c>
       <c r="F177" s="6" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="G177" s="6" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>Ret</t>
         </is>
       </c>
       <c r="H177" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I177" s="9" t="n">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="J177" s="8" t="n">
-        <v>37.9</v>
+        <v>25.3</v>
       </c>
       <c r="K177" s="10" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
       </c>
       <c r="B178" s="12" t="inlineStr">
         <is>
-          <t>P1990</t>
+          <t>P1988</t>
         </is>
       </c>
       <c r="C178" s="12" t="inlineStr">
@@ -10244,7 +10244,7 @@
       </c>
       <c r="D178" s="13" t="inlineStr">
         <is>
-          <t>UNA - Soporte y Mtto Quipu 2025 - Ret</t>
+          <t>UNA - Repositorio - Cloud</t>
         </is>
       </c>
       <c r="E178" s="13" t="inlineStr">
@@ -10254,12 +10254,12 @@
       </c>
       <c r="F178" s="12" t="inlineStr">
         <is>
-          <t>Operación</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="G178" s="12" t="inlineStr">
         <is>
-          <t>Ret</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="H178" s="14" t="n">
@@ -10290,7 +10290,7 @@
       </c>
       <c r="B179" s="6" t="inlineStr">
         <is>
-          <t>P1991</t>
+          <t>P2243</t>
         </is>
       </c>
       <c r="C179" s="6" t="inlineStr">
@@ -10300,7 +10300,7 @@
       </c>
       <c r="D179" s="7" t="inlineStr">
         <is>
-          <t>UNA - Unisalud - Ret</t>
+          <t>UNA - Secretaría General - Fixed</t>
         </is>
       </c>
       <c r="E179" s="7" t="inlineStr">
@@ -10310,12 +10310,12 @@
       </c>
       <c r="F179" s="6" t="inlineStr">
         <is>
-          <t>Operación</t>
+          <t>Implementación</t>
         </is>
       </c>
       <c r="G179" s="6" t="inlineStr">
         <is>
-          <t>Ret</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H179" s="8" t="n">
@@ -10346,7 +10346,7 @@
       </c>
       <c r="B180" s="12" t="inlineStr">
         <is>
-          <t>P2065</t>
+          <t>P2246</t>
         </is>
       </c>
       <c r="C180" s="12" t="inlineStr">
@@ -10356,7 +10356,7 @@
       </c>
       <c r="D180" s="13" t="inlineStr">
         <is>
-          <t>UNA - Unisalud - Cloud</t>
+          <t>UNA - Secretaría General - Cloud</t>
         </is>
       </c>
       <c r="E180" s="13" t="inlineStr">
@@ -10389,6 +10389,174 @@
         </is>
       </c>
       <c r="L180" s="11" t="inlineStr">
+        <is>
+          <t>Oscar Barragan</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="18" customHeight="1">
+      <c r="A181" s="5" t="inlineStr">
+        <is>
+          <t>Oscar Barragan</t>
+        </is>
+      </c>
+      <c r="B181" s="6" t="inlineStr">
+        <is>
+          <t>P1990</t>
+        </is>
+      </c>
+      <c r="C181" s="6" t="inlineStr">
+        <is>
+          <t>UNA</t>
+        </is>
+      </c>
+      <c r="D181" s="7" t="inlineStr">
+        <is>
+          <t>UNA - Soporte y Mtto Quipu 2025 - Ret</t>
+        </is>
+      </c>
+      <c r="E181" s="7" t="inlineStr">
+        <is>
+          <t>Universidad Nacional de Colombia</t>
+        </is>
+      </c>
+      <c r="F181" s="6" t="inlineStr">
+        <is>
+          <t>Operación</t>
+        </is>
+      </c>
+      <c r="G181" s="6" t="inlineStr">
+        <is>
+          <t>Ret</t>
+        </is>
+      </c>
+      <c r="H181" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I181" s="9" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="J181" s="8" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="K181" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L181" s="5" t="inlineStr">
+        <is>
+          <t>Oscar Barragan</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="18" customHeight="1">
+      <c r="A182" s="11" t="inlineStr">
+        <is>
+          <t>Oscar Barragan</t>
+        </is>
+      </c>
+      <c r="B182" s="12" t="inlineStr">
+        <is>
+          <t>P1991</t>
+        </is>
+      </c>
+      <c r="C182" s="12" t="inlineStr">
+        <is>
+          <t>UNA</t>
+        </is>
+      </c>
+      <c r="D182" s="13" t="inlineStr">
+        <is>
+          <t>UNA - Unisalud - Ret</t>
+        </is>
+      </c>
+      <c r="E182" s="13" t="inlineStr">
+        <is>
+          <t>Universidad Nacional de Colombia</t>
+        </is>
+      </c>
+      <c r="F182" s="12" t="inlineStr">
+        <is>
+          <t>Operación</t>
+        </is>
+      </c>
+      <c r="G182" s="12" t="inlineStr">
+        <is>
+          <t>Ret</t>
+        </is>
+      </c>
+      <c r="H182" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I182" s="9" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="J182" s="14" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="K182" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L182" s="11" t="inlineStr">
+        <is>
+          <t>Oscar Barragan</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="18" customHeight="1">
+      <c r="A183" s="5" t="inlineStr">
+        <is>
+          <t>Oscar Barragan</t>
+        </is>
+      </c>
+      <c r="B183" s="6" t="inlineStr">
+        <is>
+          <t>P2065</t>
+        </is>
+      </c>
+      <c r="C183" s="6" t="inlineStr">
+        <is>
+          <t>UNA</t>
+        </is>
+      </c>
+      <c r="D183" s="7" t="inlineStr">
+        <is>
+          <t>UNA - Unisalud - Cloud</t>
+        </is>
+      </c>
+      <c r="E183" s="7" t="inlineStr">
+        <is>
+          <t>Universidad Nacional de Colombia</t>
+        </is>
+      </c>
+      <c r="F183" s="6" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="G183" s="6" t="inlineStr">
+        <is>
+          <t>Cloud</t>
+        </is>
+      </c>
+      <c r="H183" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I183" s="9" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="J183" s="8" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="K183" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L183" s="5" t="inlineStr">
         <is>
           <t>Oscar Barragan</t>
         </is>
@@ -10400,13 +10568,13 @@
     <mergeCell ref="A38:L38"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A57:L57"/>
-    <mergeCell ref="A73:L73"/>
-    <mergeCell ref="A104:L104"/>
+    <mergeCell ref="A78:L78"/>
+    <mergeCell ref="A76:L76"/>
+    <mergeCell ref="A107:L107"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A5:L5"/>
-    <mergeCell ref="A75:L75"/>
-    <mergeCell ref="A119:L119"/>
-    <mergeCell ref="A124:L124"/>
+    <mergeCell ref="A127:L127"/>
+    <mergeCell ref="A122:L122"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10603,19 +10771,19 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D7" s="39" t="n">
         <v>6</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>155.8</v>
+        <v>155.9</v>
       </c>
       <c r="F7" s="30" t="n">
-        <v>0.8047520661157026</v>
+        <v>0.8052685950413224</v>
       </c>
       <c r="G7" s="31" t="inlineStr">
         <is>
@@ -10813,7 +10981,7 @@
         </is>
       </c>
       <c r="E13" s="45" t="n">
-        <v>1402.9</v>
+        <v>1403</v>
       </c>
     </row>
   </sheetData>

--- a/Asignación Proyectos/3. Output/Propuesta_Reasignacion_PM_Blend360.xlsx
+++ b/Asignación Proyectos/3. Output/Propuesta_Reasignacion_PM_Blend360.xlsx
@@ -97,6 +97,12 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="0070AD47"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="00FF6B00"/>
       <sz val="10"/>
     </font>
@@ -104,12 +110,6 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00C9504C"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="0070AD47"/>
       <sz val="10"/>
     </font>
     <font>
@@ -222,7 +222,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -320,7 +320,7 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -329,22 +329,19 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -371,7 +368,7 @@
     <xf numFmtId="0" fontId="15" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -380,7 +377,7 @@
     <xf numFmtId="0" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -521,7 +518,7 @@
       <row>58</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7315200" cy="3771900"/>
+    <ext cx="7334250" cy="3771900"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -571,7 +568,7 @@
       <row>116</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10172700" cy="4419600"/>
+    <ext cx="10163175" cy="5438775"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -1773,7 +1770,7 @@
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="17" t="inlineStr">
         <is>
-          <t>▶  David Cortes  –  17 sub-proyectos  |  ~269h est./mes  (139% capacidad)</t>
+          <t>▶  David Cortes  –  16 sub-proyectos  |  ~267h est./mes  (138% capacidad)</t>
         </is>
       </c>
     </row>
@@ -2673,120 +2670,120 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>David Cortes</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>P1968</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>UBO</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>UBO - Operación Cloud - Cloud</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>UBosque</t>
-        </is>
-      </c>
-      <c r="F37" s="6" t="inlineStr">
-        <is>
-          <t>Data</t>
-        </is>
-      </c>
-      <c r="G37" s="6" t="inlineStr">
-        <is>
-          <t>Cloud</t>
-        </is>
-      </c>
-      <c r="H37" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I37" s="9" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="J37" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K37" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L37" s="5" t="inlineStr">
-        <is>
-          <t>David Cortes</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="20" t="inlineStr">
-        <is>
-          <t>▶  Diana Castro  –  18 sub-proyectos  |  ~154h est./mes  (79% capacidad)</t>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="20" t="inlineStr">
+        <is>
+          <t>▶  Diana Castro  –  19 sub-proyectos  |  ~156h est./mes  (81% capacidad)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Diana Castro</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>P1914</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>BID</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>BID - Development as a Service - Fixed</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>Banco Interamericano de Desarrollo</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="I38" s="9" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="J38" s="8" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="K38" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L38" s="5" t="inlineStr">
+        <is>
+          <t>Diana Castro</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="11" t="inlineStr">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>Diana Castro</t>
         </is>
       </c>
-      <c r="B39" s="12" t="inlineStr">
-        <is>
-          <t>P1914</t>
-        </is>
-      </c>
-      <c r="C39" s="12" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>P1915</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t>BID</t>
         </is>
       </c>
-      <c r="D39" s="13" t="inlineStr">
-        <is>
-          <t>BID - Development as a Service - Fixed</t>
-        </is>
-      </c>
-      <c r="E39" s="13" t="inlineStr">
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>BID - Development as a Service - Ret</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
         <is>
           <t>Banco Interamericano de Desarrollo</t>
         </is>
       </c>
-      <c r="F39" s="12" t="inlineStr">
-        <is>
-          <t>Implementación</t>
-        </is>
-      </c>
-      <c r="G39" s="12" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="H39" s="14" t="n">
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>Operación</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>Ret</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="n">
         <v>9</v>
       </c>
       <c r="I39" s="9" t="n">
         <v>0.046</v>
       </c>
-      <c r="J39" s="14" t="n">
+      <c r="J39" s="8" t="n">
         <v>79.8</v>
       </c>
-      <c r="K39" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L39" s="11" t="inlineStr">
+      <c r="K39" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
         <is>
           <t>Diana Castro</t>
         </is>
@@ -2800,7 +2797,7 @@
       </c>
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>P1915</t>
+          <t>P1916</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
@@ -2810,7 +2807,7 @@
       </c>
       <c r="D40" s="13" t="inlineStr">
         <is>
-          <t>BID - Development as a Service - Ret</t>
+          <t>BID - Development as a Service - Cloud</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
@@ -2820,12 +2817,12 @@
       </c>
       <c r="F40" s="12" t="inlineStr">
         <is>
-          <t>Operación</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
-          <t>Ret</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="H40" s="14" t="n">
@@ -2856,7 +2853,7 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>P1916</t>
+          <t>P1917</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -2866,7 +2863,7 @@
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>BID - Development as a Service - Cloud</t>
+          <t>BID - Development as a Service - Ret SW</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
@@ -2876,12 +2873,12 @@
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Software SW</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>Ret SW</t>
         </is>
       </c>
       <c r="H41" s="8" t="n">
@@ -2912,42 +2909,42 @@
       </c>
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>P1917</t>
+          <t>P2743</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>BID</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>BID - Development as a Service - Ret SW</t>
+          <t>CAT - API Manager - Ret</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
         <is>
-          <t>Banco Interamericano de Desarrollo</t>
+          <t>Ingenium</t>
         </is>
       </c>
       <c r="F42" s="12" t="inlineStr">
         <is>
-          <t>Software SW</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
-          <t>Ret SW</t>
+          <t>Ret</t>
         </is>
       </c>
       <c r="H42" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I42" s="9" t="n">
-        <v>0.046</v>
+        <v>0.057</v>
       </c>
       <c r="J42" s="14" t="n">
-        <v>79.8</v>
+        <v>177.2</v>
       </c>
       <c r="K42" s="15" t="inlineStr">
         <is>
@@ -2968,7 +2965,7 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>P2743</t>
+          <t>P2748</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -2978,7 +2975,7 @@
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>CAT - API Manager - Ret</t>
+          <t>CAT - API Manager - Fixed</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
@@ -2988,12 +2985,12 @@
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>Operación</t>
+          <t>Implementación</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>Ret</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H43" s="8" t="n">
@@ -3024,22 +3021,22 @@
       </c>
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>P2748</t>
+          <t>P2611</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>MEN</t>
         </is>
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>CAT - API Manager - Fixed</t>
+          <t>MEN - Operacion en AWS - Fixed</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
-          <t>Ingenium</t>
+          <t>Ministerio de educación Nacional</t>
         </is>
       </c>
       <c r="F44" s="12" t="inlineStr">
@@ -3053,22 +3050,22 @@
         </is>
       </c>
       <c r="H44" s="14" t="n">
-        <v>11</v>
+        <v>5.7</v>
       </c>
       <c r="I44" s="9" t="n">
-        <v>0.057</v>
+        <v>0.029</v>
       </c>
       <c r="J44" s="14" t="n">
-        <v>177.2</v>
-      </c>
-      <c r="K44" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>25</v>
+      </c>
+      <c r="K44" s="19" t="inlineStr">
+        <is>
+          <t>🔄 Reasignado</t>
         </is>
       </c>
       <c r="L44" s="11" t="inlineStr">
         <is>
-          <t>Diana Castro</t>
+          <t>Miguel Garcia</t>
         </is>
       </c>
     </row>
@@ -3080,7 +3077,7 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>P2611</t>
+          <t>P2612</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -3090,7 +3087,7 @@
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>MEN - Operacion en AWS - Fixed</t>
+          <t>MEN - Operacion en AWS - Ret</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
@@ -3100,12 +3097,12 @@
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>Implementación</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Ret</t>
         </is>
       </c>
       <c r="H45" s="8" t="n">
@@ -3136,7 +3133,7 @@
       </c>
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>P2612</t>
+          <t>P2634</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
@@ -3146,7 +3143,7 @@
       </c>
       <c r="D46" s="13" t="inlineStr">
         <is>
-          <t>MEN - Operacion en AWS - Ret</t>
+          <t>MEN - Operacion en AWS - Cloud</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
@@ -3156,12 +3153,12 @@
       </c>
       <c r="F46" s="12" t="inlineStr">
         <is>
-          <t>Operación</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
-          <t>Ret</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="H46" s="14" t="n">
@@ -3192,51 +3189,51 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>P2634</t>
+          <t>P2096</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>MEN</t>
+          <t>SAN</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>MEN - Operacion en AWS - Cloud</t>
+          <t>SAN - Soporte y Mantenimiento Quipu 2025 - Ret</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>Ministerio de educación Nacional</t>
+          <t>Sanidad</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>Ret</t>
         </is>
       </c>
       <c r="H47" s="8" t="n">
-        <v>5.7</v>
+        <v>10</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>0.029</v>
+        <v>0.052</v>
       </c>
       <c r="J47" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="K47" s="19" t="inlineStr">
-        <is>
-          <t>🔄 Reasignado</t>
+        <v>137.1</v>
+      </c>
+      <c r="K47" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>Miguel Garcia</t>
+          <t>Diana Castro</t>
         </is>
       </c>
     </row>
@@ -3248,51 +3245,51 @@
       </c>
       <c r="B48" s="12" t="inlineStr">
         <is>
-          <t>P2096</t>
+          <t>P2431</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>SAN</t>
+          <t>SED</t>
         </is>
       </c>
       <c r="D48" s="13" t="inlineStr">
         <is>
-          <t>SAN - Soporte y Mantenimiento Quipu 2025 - Ret</t>
+          <t>SED - Automatización procesos seguros, adquisiciones y accidentes  - Fixed</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>Sanidad</t>
+          <t>Secretaría de Educación del Distrito</t>
         </is>
       </c>
       <c r="F48" s="12" t="inlineStr">
         <is>
-          <t>Operación</t>
+          <t>Implementación</t>
         </is>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
-          <t>Ret</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H48" s="14" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I48" s="9" t="n">
-        <v>0.052</v>
+        <v>0.043</v>
       </c>
       <c r="J48" s="14" t="n">
-        <v>137.1</v>
-      </c>
-      <c r="K48" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>80.8</v>
+      </c>
+      <c r="K48" s="19" t="inlineStr">
+        <is>
+          <t>🔄 Reasignado</t>
         </is>
       </c>
       <c r="L48" s="11" t="inlineStr">
         <is>
-          <t>Diana Castro</t>
+          <t>Miguel Garcia</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3301,7 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>P2431</t>
+          <t>P2561</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -3314,7 +3311,7 @@
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>SED - Automatización procesos seguros, adquisiciones y accidentes  - Fixed</t>
+          <t>SED - Automatización procesos seguros, adquisiciones y accidentes  - Ret</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
@@ -3324,12 +3321,12 @@
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>Implementación</t>
+          <t>Software SW</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Ret</t>
         </is>
       </c>
       <c r="H49" s="8" t="n">
@@ -3360,7 +3357,7 @@
       </c>
       <c r="B50" s="12" t="inlineStr">
         <is>
-          <t>P2561</t>
+          <t>P2562</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
@@ -3370,7 +3367,7 @@
       </c>
       <c r="D50" s="13" t="inlineStr">
         <is>
-          <t>SED - Automatización procesos seguros, adquisiciones y accidentes  - Ret</t>
+          <t>SED - Automatización procesos seguros, adquisiciones y accidentes  - Ret SW</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
@@ -3385,7 +3382,7 @@
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
-          <t>Ret</t>
+          <t>Ret SW</t>
         </is>
       </c>
       <c r="H50" s="14" t="n">
@@ -3416,7 +3413,7 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>P2562</t>
+          <t>P2563</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -3426,7 +3423,7 @@
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>SED - Automatización procesos seguros, adquisiciones y accidentes  - Ret SW</t>
+          <t>SED - Automatización procesos seguros, adquisiciones y accidentes  - Cloud</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
@@ -3441,7 +3438,7 @@
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>Ret SW</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="H51" s="8" t="n">
@@ -3472,51 +3469,51 @@
       </c>
       <c r="B52" s="12" t="inlineStr">
         <is>
-          <t>P2563</t>
+          <t>P2640</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>SED</t>
+          <t>SEP</t>
         </is>
       </c>
       <c r="D52" s="13" t="inlineStr">
         <is>
-          <t>SED - Automatización procesos seguros, adquisiciones y accidentes  - Cloud</t>
+          <t>SEP - Mantenimiento y adiciones SIPU - Fixed</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
-          <t>Secretaría de Educación del Distrito</t>
+          <t>Secretaría de Planeación Distrital</t>
         </is>
       </c>
       <c r="F52" s="12" t="inlineStr">
         <is>
-          <t>Software SW</t>
+          <t>Implementación</t>
         </is>
       </c>
       <c r="G52" s="12" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H52" s="14" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="I52" s="9" t="n">
-        <v>0.043</v>
+        <v>0.046</v>
       </c>
       <c r="J52" s="14" t="n">
-        <v>80.8</v>
-      </c>
-      <c r="K52" s="19" t="inlineStr">
-        <is>
-          <t>🔄 Reasignado</t>
+        <v>6.9</v>
+      </c>
+      <c r="K52" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="L52" s="11" t="inlineStr">
         <is>
-          <t>Miguel Garcia</t>
+          <t>Diana Castro</t>
         </is>
       </c>
     </row>
@@ -3528,7 +3525,7 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>P2640</t>
+          <t>P2641</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -3538,7 +3535,7 @@
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>SEP - Mantenimiento y adiciones SIPU - Fixed</t>
+          <t>SEP - Mantenimiento y adiciones SIPU - Cloud</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
@@ -3548,12 +3545,12 @@
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>Implementación</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="H53" s="8" t="n">
@@ -3584,7 +3581,7 @@
       </c>
       <c r="B54" s="12" t="inlineStr">
         <is>
-          <t>P2641</t>
+          <t>P2642</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
@@ -3594,7 +3591,7 @@
       </c>
       <c r="D54" s="13" t="inlineStr">
         <is>
-          <t>SEP - Mantenimiento y adiciones SIPU - Cloud</t>
+          <t>SEP - Mantenimiento y adiciones SIPU - Ret</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
@@ -3604,12 +3601,12 @@
       </c>
       <c r="F54" s="12" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="G54" s="12" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>Ret</t>
         </is>
       </c>
       <c r="H54" s="14" t="n">
@@ -3640,7 +3637,7 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>P2642</t>
+          <t>P2643</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -3650,7 +3647,7 @@
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>SEP - Mantenimiento y adiciones SIPU - Ret</t>
+          <t>SEP - Mantenimiento y adiciones SIPU - Ret SW</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
@@ -3660,12 +3657,12 @@
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>Operación</t>
+          <t>Software SW</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>Ret</t>
+          <t>Ret SW</t>
         </is>
       </c>
       <c r="H55" s="8" t="n">
@@ -3696,58 +3693,58 @@
       </c>
       <c r="B56" s="12" t="inlineStr">
         <is>
-          <t>P2643</t>
+          <t>P1968</t>
         </is>
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>SEP</t>
+          <t>UBO</t>
         </is>
       </c>
       <c r="D56" s="13" t="inlineStr">
         <is>
-          <t>SEP - Mantenimiento y adiciones SIPU - Ret SW</t>
+          <t>UBO - Operación Cloud - Cloud</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>Secretaría de Planeación Distrital</t>
+          <t>UBosque</t>
         </is>
       </c>
       <c r="F56" s="12" t="inlineStr">
         <is>
-          <t>Software SW</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="G56" s="12" t="inlineStr">
         <is>
-          <t>Ret SW</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="H56" s="14" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I56" s="9" t="n">
-        <v>0.046</v>
+        <v>0.01</v>
       </c>
       <c r="J56" s="14" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="K56" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>2</v>
+      </c>
+      <c r="K56" s="19" t="inlineStr">
+        <is>
+          <t>🔄 Reasignado</t>
         </is>
       </c>
       <c r="L56" s="11" t="inlineStr">
         <is>
-          <t>Diana Castro</t>
+          <t>David Cortes</t>
         </is>
       </c>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="21" t="inlineStr">
         <is>
-          <t>▶  Diana Rojas  –  18 sub-proyectos  |  ~156h est./mes  (81% capacidad)</t>
+          <t>▶  Diana Rojas  –  15 sub-proyectos  |  ~156h est./mes  (80% capacidad)</t>
         </is>
       </c>
     </row>
@@ -3788,13 +3785,13 @@
         </is>
       </c>
       <c r="H58" s="8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="I58" s="9" t="n">
-        <v>0.049</v>
+        <v>18.8</v>
+      </c>
+      <c r="I58" s="18" t="n">
+        <v>0.09699999999999999</v>
       </c>
       <c r="J58" s="8" t="n">
-        <v>825.5</v>
+        <v>1650.9</v>
       </c>
       <c r="K58" s="10" t="inlineStr">
         <is>
@@ -3844,13 +3841,13 @@
         </is>
       </c>
       <c r="H59" s="8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="I59" s="9" t="n">
-        <v>0.049</v>
+        <v>18.8</v>
+      </c>
+      <c r="I59" s="18" t="n">
+        <v>0.09699999999999999</v>
       </c>
       <c r="J59" s="8" t="n">
-        <v>825.5</v>
+        <v>1650.9</v>
       </c>
       <c r="K59" s="10" t="inlineStr">
         <is>
@@ -3900,13 +3897,13 @@
         </is>
       </c>
       <c r="H60" s="14" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="I60" s="9" t="n">
-        <v>0.049</v>
+        <v>18.8</v>
+      </c>
+      <c r="I60" s="18" t="n">
+        <v>0.09699999999999999</v>
       </c>
       <c r="J60" s="14" t="n">
-        <v>825.5</v>
+        <v>1650.9</v>
       </c>
       <c r="K60" s="15" t="inlineStr">
         <is>
@@ -3956,13 +3953,13 @@
         </is>
       </c>
       <c r="H61" s="8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="I61" s="9" t="n">
-        <v>0.049</v>
+        <v>18.8</v>
+      </c>
+      <c r="I61" s="18" t="n">
+        <v>0.09699999999999999</v>
       </c>
       <c r="J61" s="8" t="n">
-        <v>825.5</v>
+        <v>1650.9</v>
       </c>
       <c r="K61" s="10" t="inlineStr">
         <is>
@@ -4012,13 +4009,13 @@
         </is>
       </c>
       <c r="H62" s="14" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="I62" s="9" t="n">
-        <v>0.049</v>
+        <v>18.8</v>
+      </c>
+      <c r="I62" s="18" t="n">
+        <v>0.09699999999999999</v>
       </c>
       <c r="J62" s="14" t="n">
-        <v>825.5</v>
+        <v>1650.9</v>
       </c>
       <c r="K62" s="15" t="inlineStr">
         <is>
@@ -4039,42 +4036,42 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>P2847</t>
+          <t>P1949</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>ADR</t>
+          <t>MMN</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>ADR - peración Auditoria Cuentas Medicas - Ret</t>
+          <t>MMN - Cloud Sistema de Recaudo - Fixed</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>La Administradora de los Recursos del Sistema General de Seguridad Social en Salud</t>
+          <t>Empresa De Transporte Masivo Del Valle De Aburrá Limitada</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>Operación</t>
+          <t>Implementación</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>Ret</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H63" s="8" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="I63" s="18" t="n">
-        <v>0.081</v>
+        <v>3</v>
+      </c>
+      <c r="I63" s="9" t="n">
+        <v>0.015</v>
       </c>
       <c r="J63" s="8" t="n">
-        <v>1375.8</v>
+        <v>215.8</v>
       </c>
       <c r="K63" s="10" t="inlineStr">
         <is>
@@ -4095,22 +4092,22 @@
       </c>
       <c r="B64" s="12" t="inlineStr">
         <is>
-          <t>P2848</t>
+          <t>P1950</t>
         </is>
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>ADR</t>
+          <t>MMN</t>
         </is>
       </c>
       <c r="D64" s="13" t="inlineStr">
         <is>
-          <t>ADR - peración Auditoria Cuentas Medicas - Cloud</t>
+          <t>MMN - Cloud Sistema de Recaudo - Cloud</t>
         </is>
       </c>
       <c r="E64" s="13" t="inlineStr">
         <is>
-          <t>La Administradora de los Recursos del Sistema General de Seguridad Social en Salud</t>
+          <t>Empresa De Transporte Masivo Del Valle De Aburrá Limitada</t>
         </is>
       </c>
       <c r="F64" s="12" t="inlineStr">
@@ -4124,13 +4121,13 @@
         </is>
       </c>
       <c r="H64" s="14" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="I64" s="18" t="n">
-        <v>0.081</v>
+        <v>3</v>
+      </c>
+      <c r="I64" s="9" t="n">
+        <v>0.015</v>
       </c>
       <c r="J64" s="14" t="n">
-        <v>1375.8</v>
+        <v>215.8</v>
       </c>
       <c r="K64" s="15" t="inlineStr">
         <is>
@@ -4151,42 +4148,42 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>P2849</t>
+          <t>P2225</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>ADR</t>
+          <t>MMN</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>ADR - peración Auditoria Cuentas Medicas - Ret Sw</t>
+          <t>MMN - Cloud Sistema de Recaudo - Ret Other Vendors</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>La Administradora de los Recursos del Sistema General de Seguridad Social en Salud</t>
+          <t>Empresa De Transporte Masivo Del Valle De Aburrá Limitada</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>Software SW</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>Ret Sw</t>
+          <t>Ret Other Vendors</t>
         </is>
       </c>
       <c r="H65" s="8" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="I65" s="18" t="n">
-        <v>0.081</v>
+        <v>3</v>
+      </c>
+      <c r="I65" s="9" t="n">
+        <v>0.015</v>
       </c>
       <c r="J65" s="8" t="n">
-        <v>1375.8</v>
+        <v>215.8</v>
       </c>
       <c r="K65" s="10" t="inlineStr">
         <is>
@@ -4207,7 +4204,7 @@
       </c>
       <c r="B66" s="12" t="inlineStr">
         <is>
-          <t>P1949</t>
+          <t>P2310</t>
         </is>
       </c>
       <c r="C66" s="12" t="inlineStr">
@@ -4217,7 +4214,7 @@
       </c>
       <c r="D66" s="13" t="inlineStr">
         <is>
-          <t>MMN - Cloud Sistema de Recaudo - Fixed</t>
+          <t xml:space="preserve">MMN - Cloud Sistema de Recaudo - Ret </t>
         </is>
       </c>
       <c r="E66" s="13" t="inlineStr">
@@ -4227,12 +4224,12 @@
       </c>
       <c r="F66" s="12" t="inlineStr">
         <is>
-          <t>Implementación</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="G66" s="12" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t xml:space="preserve">Ret </t>
         </is>
       </c>
       <c r="H66" s="14" t="n">
@@ -4263,51 +4260,51 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>P1950</t>
+          <t>P2723</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>MMN</t>
+          <t>SPD</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>MMN - Cloud Sistema de Recaudo - Cloud</t>
+          <t>SPD - Renovacion observatorio de datos- - Fixed</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>Empresa De Transporte Masivo Del Valle De Aburrá Limitada</t>
+          <t>Superintendencia Servicios Públicos Domiciliarios</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Implementación</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H67" s="8" t="n">
-        <v>3</v>
+        <v>6.2</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>0.015</v>
+        <v>0.032</v>
       </c>
       <c r="J67" s="8" t="n">
-        <v>215.8</v>
-      </c>
-      <c r="K67" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>103.1</v>
+      </c>
+      <c r="K67" s="19" t="inlineStr">
+        <is>
+          <t>🔄 Reasignado</t>
         </is>
       </c>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>Diana Rojas</t>
+          <t>Miguel Garcia</t>
         </is>
       </c>
     </row>
@@ -4319,51 +4316,51 @@
       </c>
       <c r="B68" s="12" t="inlineStr">
         <is>
-          <t>P2225</t>
+          <t>P2724</t>
         </is>
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>MMN</t>
+          <t>SPD</t>
         </is>
       </c>
       <c r="D68" s="13" t="inlineStr">
         <is>
-          <t>MMN - Cloud Sistema de Recaudo - Ret Other Vendors</t>
+          <t>SPD - Renovacion observatorio de datos- - Ret SW</t>
         </is>
       </c>
       <c r="E68" s="13" t="inlineStr">
         <is>
-          <t>Empresa De Transporte Masivo Del Valle De Aburrá Limitada</t>
+          <t>Superintendencia Servicios Públicos Domiciliarios</t>
         </is>
       </c>
       <c r="F68" s="12" t="inlineStr">
         <is>
-          <t>Operación</t>
+          <t>Software SW</t>
         </is>
       </c>
       <c r="G68" s="12" t="inlineStr">
         <is>
-          <t>Ret Other Vendors</t>
+          <t>Ret SW</t>
         </is>
       </c>
       <c r="H68" s="14" t="n">
-        <v>3</v>
+        <v>6.2</v>
       </c>
       <c r="I68" s="9" t="n">
-        <v>0.015</v>
+        <v>0.032</v>
       </c>
       <c r="J68" s="14" t="n">
-        <v>215.8</v>
-      </c>
-      <c r="K68" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>103.1</v>
+      </c>
+      <c r="K68" s="19" t="inlineStr">
+        <is>
+          <t>🔄 Reasignado</t>
         </is>
       </c>
       <c r="L68" s="11" t="inlineStr">
         <is>
-          <t>Diana Rojas</t>
+          <t>Miguel Garcia</t>
         </is>
       </c>
     </row>
@@ -4375,51 +4372,51 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>P2310</t>
+          <t>P2725</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>MMN</t>
+          <t>SPD</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">MMN - Cloud Sistema de Recaudo - Ret </t>
+          <t>SPD - Renovacion observatorio de datos- - Cloud</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>Empresa De Transporte Masivo Del Valle De Aburrá Limitada</t>
+          <t>Superintendencia Servicios Públicos Domiciliarios</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
-          <t>Operación</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ret </t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="H69" s="8" t="n">
-        <v>3</v>
+        <v>6.2</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>0.015</v>
+        <v>0.032</v>
       </c>
       <c r="J69" s="8" t="n">
-        <v>215.8</v>
-      </c>
-      <c r="K69" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>103.1</v>
+      </c>
+      <c r="K69" s="19" t="inlineStr">
+        <is>
+          <t>🔄 Reasignado</t>
         </is>
       </c>
       <c r="L69" s="5" t="inlineStr">
         <is>
-          <t>Diana Rojas</t>
+          <t>Miguel Garcia</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4428,7 @@
       </c>
       <c r="B70" s="12" t="inlineStr">
         <is>
-          <t>P2723</t>
+          <t>P2726</t>
         </is>
       </c>
       <c r="C70" s="12" t="inlineStr">
@@ -4441,7 +4438,7 @@
       </c>
       <c r="D70" s="13" t="inlineStr">
         <is>
-          <t>SPD - Renovacion observatorio de datos- - Fixed</t>
+          <t>SPD - Renovacion observatorio de datos- - Ret</t>
         </is>
       </c>
       <c r="E70" s="13" t="inlineStr">
@@ -4451,12 +4448,12 @@
       </c>
       <c r="F70" s="12" t="inlineStr">
         <is>
-          <t>Implementación</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="G70" s="12" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Ret</t>
         </is>
       </c>
       <c r="H70" s="14" t="n">
@@ -4487,7 +4484,7 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>P2724</t>
+          <t>P1966</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
@@ -4497,7 +4494,7 @@
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>SPD - Renovacion observatorio de datos- - Ret SW</t>
+          <t>SPD - Repositorio Único de Datos - Ret SW</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
@@ -4516,13 +4513,13 @@
         </is>
       </c>
       <c r="H71" s="8" t="n">
-        <v>6.2</v>
+        <v>12.5</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>0.032</v>
+        <v>0.065</v>
       </c>
       <c r="J71" s="8" t="n">
-        <v>103.1</v>
+        <v>206.1</v>
       </c>
       <c r="K71" s="19" t="inlineStr">
         <is>
@@ -4543,7 +4540,7 @@
       </c>
       <c r="B72" s="12" t="inlineStr">
         <is>
-          <t>P2725</t>
+          <t>P1967</t>
         </is>
       </c>
       <c r="C72" s="12" t="inlineStr">
@@ -4553,7 +4550,7 @@
       </c>
       <c r="D72" s="13" t="inlineStr">
         <is>
-          <t>SPD - Renovacion observatorio de datos- - Cloud</t>
+          <t>SPD - Repositorio Único de Datos - Cloud</t>
         </is>
       </c>
       <c r="E72" s="13" t="inlineStr">
@@ -4572,13 +4569,13 @@
         </is>
       </c>
       <c r="H72" s="14" t="n">
-        <v>6.2</v>
+        <v>12.5</v>
       </c>
       <c r="I72" s="9" t="n">
-        <v>0.032</v>
+        <v>0.065</v>
       </c>
       <c r="J72" s="14" t="n">
-        <v>103.1</v>
+        <v>206.1</v>
       </c>
       <c r="K72" s="19" t="inlineStr">
         <is>
@@ -4591,295 +4588,295 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="18" customHeight="1">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>Diana Rojas</t>
-        </is>
-      </c>
-      <c r="B73" s="6" t="inlineStr">
-        <is>
-          <t>P2726</t>
-        </is>
-      </c>
-      <c r="C73" s="6" t="inlineStr">
-        <is>
-          <t>SPD</t>
-        </is>
-      </c>
-      <c r="D73" s="7" t="inlineStr">
-        <is>
-          <t>SPD - Renovacion observatorio de datos- - Ret</t>
-        </is>
-      </c>
-      <c r="E73" s="7" t="inlineStr">
-        <is>
-          <t>Superintendencia Servicios Públicos Domiciliarios</t>
-        </is>
-      </c>
-      <c r="F73" s="6" t="inlineStr">
+    <row r="73" ht="22" customHeight="1">
+      <c r="A73" s="22" t="inlineStr">
+        <is>
+          <t>▶  Fernando Ortega  –  1 sub-proyectos  |  ~4h est./mes  (2% capacidad)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="18" customHeight="1">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>Fernando Ortega</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>P2083</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>BLD</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>BLD - Producto - Houndoc - Internal</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>Blend360</t>
+        </is>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>Interno</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="H74" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I74" s="9" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J74" s="8" t="n">
+        <v>1691</v>
+      </c>
+      <c r="K74" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L74" s="5" t="inlineStr">
+        <is>
+          <t>Fernando Ortega</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="22" customHeight="1">
+      <c r="A75" s="23" t="inlineStr">
+        <is>
+          <t>▶  Juan Bernal  –  28 sub-proyectos  |  ~149h est./mes  (77% capacidad)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="18" customHeight="1">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>Juan Bernal</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>P2615</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>CJU</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>CJU - CJU - Localizados - Cloud</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>Coljuegos</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>Cloud</t>
+        </is>
+      </c>
+      <c r="H76" s="8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I76" s="9" t="n">
+        <v>0.006999999999999999</v>
+      </c>
+      <c r="J76" s="8" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="K76" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L76" s="5" t="inlineStr">
+        <is>
+          <t>Juan Bernal</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="18" customHeight="1">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>Juan Bernal</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>P2616</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>CJU</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>CJU - CJU - Localizados - Fixed</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>Coljuegos</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H77" s="8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I77" s="9" t="n">
+        <v>0.006999999999999999</v>
+      </c>
+      <c r="J77" s="8" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="K77" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L77" s="5" t="inlineStr">
+        <is>
+          <t>Juan Bernal</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="18" customHeight="1">
+      <c r="A78" s="11" t="inlineStr">
+        <is>
+          <t>Juan Bernal</t>
+        </is>
+      </c>
+      <c r="B78" s="12" t="inlineStr">
+        <is>
+          <t>P2617</t>
+        </is>
+      </c>
+      <c r="C78" s="12" t="inlineStr">
+        <is>
+          <t>CJU</t>
+        </is>
+      </c>
+      <c r="D78" s="13" t="inlineStr">
+        <is>
+          <t>CJU - CJU - Localizados - Ret</t>
+        </is>
+      </c>
+      <c r="E78" s="13" t="inlineStr">
+        <is>
+          <t>Coljuegos</t>
+        </is>
+      </c>
+      <c r="F78" s="12" t="inlineStr">
         <is>
           <t>Operación</t>
         </is>
       </c>
-      <c r="G73" s="6" t="inlineStr">
+      <c r="G78" s="12" t="inlineStr">
         <is>
           <t>Ret</t>
         </is>
       </c>
-      <c r="H73" s="8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="I73" s="9" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="J73" s="8" t="n">
-        <v>103.1</v>
-      </c>
-      <c r="K73" s="19" t="inlineStr">
-        <is>
-          <t>🔄 Reasignado</t>
-        </is>
-      </c>
-      <c r="L73" s="5" t="inlineStr">
-        <is>
-          <t>Miguel Garcia</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="18" customHeight="1">
-      <c r="A74" s="11" t="inlineStr">
-        <is>
-          <t>Diana Rojas</t>
-        </is>
-      </c>
-      <c r="B74" s="12" t="inlineStr">
-        <is>
-          <t>P1966</t>
-        </is>
-      </c>
-      <c r="C74" s="12" t="inlineStr">
-        <is>
-          <t>SPD</t>
-        </is>
-      </c>
-      <c r="D74" s="13" t="inlineStr">
-        <is>
-          <t>SPD - Repositorio Único de Datos - Ret SW</t>
-        </is>
-      </c>
-      <c r="E74" s="13" t="inlineStr">
-        <is>
-          <t>Superintendencia Servicios Públicos Domiciliarios</t>
-        </is>
-      </c>
-      <c r="F74" s="12" t="inlineStr">
+      <c r="H78" s="14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I78" s="9" t="n">
+        <v>0.006999999999999999</v>
+      </c>
+      <c r="J78" s="14" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="K78" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="11" t="inlineStr">
+        <is>
+          <t>Juan Bernal</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="18" customHeight="1">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>Juan Bernal</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>P2618</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>CJU</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>CJU - CJU - Localizados - Ret SW</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>Coljuegos</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
         <is>
           <t>Software SW</t>
         </is>
       </c>
-      <c r="G74" s="12" t="inlineStr">
+      <c r="G79" s="6" t="inlineStr">
         <is>
           <t>Ret SW</t>
         </is>
       </c>
-      <c r="H74" s="14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="I74" s="9" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="J74" s="14" t="n">
-        <v>206.1</v>
-      </c>
-      <c r="K74" s="19" t="inlineStr">
-        <is>
-          <t>🔄 Reasignado</t>
-        </is>
-      </c>
-      <c r="L74" s="11" t="inlineStr">
-        <is>
-          <t>Miguel Garcia</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="18" customHeight="1">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>Diana Rojas</t>
-        </is>
-      </c>
-      <c r="B75" s="6" t="inlineStr">
-        <is>
-          <t>P1967</t>
-        </is>
-      </c>
-      <c r="C75" s="6" t="inlineStr">
-        <is>
-          <t>SPD</t>
-        </is>
-      </c>
-      <c r="D75" s="7" t="inlineStr">
-        <is>
-          <t>SPD - Repositorio Único de Datos - Cloud</t>
-        </is>
-      </c>
-      <c r="E75" s="7" t="inlineStr">
-        <is>
-          <t>Superintendencia Servicios Públicos Domiciliarios</t>
-        </is>
-      </c>
-      <c r="F75" s="6" t="inlineStr">
-        <is>
-          <t>Data</t>
-        </is>
-      </c>
-      <c r="G75" s="6" t="inlineStr">
-        <is>
-          <t>Cloud</t>
-        </is>
-      </c>
-      <c r="H75" s="8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="I75" s="9" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="J75" s="8" t="n">
-        <v>206.1</v>
-      </c>
-      <c r="K75" s="19" t="inlineStr">
-        <is>
-          <t>🔄 Reasignado</t>
-        </is>
-      </c>
-      <c r="L75" s="5" t="inlineStr">
-        <is>
-          <t>Miguel Garcia</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="22" customHeight="1">
-      <c r="A76" s="22" t="inlineStr">
-        <is>
-          <t>▶  Fernando Ortega  –  1 sub-proyectos  |  ~4h est./mes  (2% capacidad)</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="18" customHeight="1">
-      <c r="A77" s="11" t="inlineStr">
-        <is>
-          <t>Fernando Ortega</t>
-        </is>
-      </c>
-      <c r="B77" s="12" t="inlineStr">
-        <is>
-          <t>P2083</t>
-        </is>
-      </c>
-      <c r="C77" s="12" t="inlineStr">
-        <is>
-          <t>BLD</t>
-        </is>
-      </c>
-      <c r="D77" s="13" t="inlineStr">
-        <is>
-          <t>BLD - Producto - Houndoc - Internal</t>
-        </is>
-      </c>
-      <c r="E77" s="13" t="inlineStr">
-        <is>
-          <t>Blend360</t>
-        </is>
-      </c>
-      <c r="F77" s="12" t="inlineStr">
-        <is>
-          <t>Interno</t>
-        </is>
-      </c>
-      <c r="G77" s="12" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
-      <c r="H77" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="I77" s="9" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="J77" s="14" t="n">
-        <v>1691</v>
-      </c>
-      <c r="K77" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L77" s="11" t="inlineStr">
-        <is>
-          <t>Fernando Ortega</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="22" customHeight="1">
-      <c r="A78" s="23" t="inlineStr">
-        <is>
-          <t>▶  Juan Bernal  –  28 sub-proyectos  |  ~149h est./mes  (77% capacidad)</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="18" customHeight="1">
-      <c r="A79" s="11" t="inlineStr">
-        <is>
-          <t>Juan Bernal</t>
-        </is>
-      </c>
-      <c r="B79" s="12" t="inlineStr">
-        <is>
-          <t>P2615</t>
-        </is>
-      </c>
-      <c r="C79" s="12" t="inlineStr">
-        <is>
-          <t>CJU</t>
-        </is>
-      </c>
-      <c r="D79" s="13" t="inlineStr">
-        <is>
-          <t>CJU - CJU - Localizados - Cloud</t>
-        </is>
-      </c>
-      <c r="E79" s="13" t="inlineStr">
-        <is>
-          <t>Coljuegos</t>
-        </is>
-      </c>
-      <c r="F79" s="12" t="inlineStr">
-        <is>
-          <t>Data</t>
-        </is>
-      </c>
-      <c r="G79" s="12" t="inlineStr">
-        <is>
-          <t>Cloud</t>
-        </is>
-      </c>
-      <c r="H79" s="14" t="n">
+      <c r="H79" s="8" t="n">
         <v>1.4</v>
       </c>
       <c r="I79" s="9" t="n">
         <v>0.006999999999999999</v>
       </c>
-      <c r="J79" s="14" t="n">
+      <c r="J79" s="8" t="n">
         <v>76.5</v>
       </c>
-      <c r="K79" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L79" s="11" t="inlineStr">
+      <c r="K79" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="5" t="inlineStr">
         <is>
           <t>Juan Bernal</t>
         </is>
@@ -4893,7 +4890,7 @@
       </c>
       <c r="B80" s="12" t="inlineStr">
         <is>
-          <t>P2616</t>
+          <t>P2619</t>
         </is>
       </c>
       <c r="C80" s="12" t="inlineStr">
@@ -4903,7 +4900,7 @@
       </c>
       <c r="D80" s="13" t="inlineStr">
         <is>
-          <t>CJU - CJU - Localizados - Fixed</t>
+          <t>CJU - CJU - STecnica - Cloud</t>
         </is>
       </c>
       <c r="E80" s="13" t="inlineStr">
@@ -4913,12 +4910,12 @@
       </c>
       <c r="F80" s="12" t="inlineStr">
         <is>
-          <t>Implementación</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="G80" s="12" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="H80" s="14" t="n">
@@ -4949,7 +4946,7 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>P2617</t>
+          <t>P2620</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
@@ -4959,7 +4956,7 @@
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>CJU - CJU - Localizados - Ret</t>
+          <t>CJU - CJU - STecnica - Fixed</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
@@ -4969,12 +4966,12 @@
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>Operación</t>
+          <t>Implementación</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>Ret</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H81" s="8" t="n">
@@ -5005,7 +5002,7 @@
       </c>
       <c r="B82" s="12" t="inlineStr">
         <is>
-          <t>P2618</t>
+          <t>P2621</t>
         </is>
       </c>
       <c r="C82" s="12" t="inlineStr">
@@ -5015,7 +5012,7 @@
       </c>
       <c r="D82" s="13" t="inlineStr">
         <is>
-          <t>CJU - CJU - Localizados - Ret SW</t>
+          <t>CJU - CJU - STecnica - Ret</t>
         </is>
       </c>
       <c r="E82" s="13" t="inlineStr">
@@ -5025,12 +5022,12 @@
       </c>
       <c r="F82" s="12" t="inlineStr">
         <is>
-          <t>Software SW</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="G82" s="12" t="inlineStr">
         <is>
-          <t>Ret SW</t>
+          <t>Ret</t>
         </is>
       </c>
       <c r="H82" s="14" t="n">
@@ -5061,7 +5058,7 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>P2619</t>
+          <t>P2622</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
@@ -5071,7 +5068,7 @@
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>CJU - CJU - STecnica - Cloud</t>
+          <t>CJU - CJU - STecnica - Ret SW</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
@@ -5081,12 +5078,12 @@
       </c>
       <c r="F83" s="6" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Software SW</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>Ret SW</t>
         </is>
       </c>
       <c r="H83" s="8" t="n">
@@ -5117,7 +5114,7 @@
       </c>
       <c r="B84" s="12" t="inlineStr">
         <is>
-          <t>P2620</t>
+          <t>P2019</t>
         </is>
       </c>
       <c r="C84" s="12" t="inlineStr">
@@ -5127,7 +5124,7 @@
       </c>
       <c r="D84" s="13" t="inlineStr">
         <is>
-          <t>CJU - CJU - STecnica - Fixed</t>
+          <t>CJU - Vigilancia y MET Plus - Fixed</t>
         </is>
       </c>
       <c r="E84" s="13" t="inlineStr">
@@ -5173,7 +5170,7 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>P2621</t>
+          <t>P2020</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
@@ -5183,7 +5180,7 @@
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>CJU - CJU - STecnica - Ret</t>
+          <t>CJU - Vigilancia y MET Plus - Cloud</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
@@ -5193,12 +5190,12 @@
       </c>
       <c r="F85" s="6" t="inlineStr">
         <is>
-          <t>Operación</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>Ret</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="H85" s="8" t="n">
@@ -5229,7 +5226,7 @@
       </c>
       <c r="B86" s="12" t="inlineStr">
         <is>
-          <t>P2622</t>
+          <t>P2021</t>
         </is>
       </c>
       <c r="C86" s="12" t="inlineStr">
@@ -5239,7 +5236,7 @@
       </c>
       <c r="D86" s="13" t="inlineStr">
         <is>
-          <t>CJU - CJU - STecnica - Ret SW</t>
+          <t>CJU - Vigilancia y MET Plus - Ret</t>
         </is>
       </c>
       <c r="E86" s="13" t="inlineStr">
@@ -5249,12 +5246,12 @@
       </c>
       <c r="F86" s="12" t="inlineStr">
         <is>
-          <t>Software SW</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="G86" s="12" t="inlineStr">
         <is>
-          <t>Ret SW</t>
+          <t>Ret</t>
         </is>
       </c>
       <c r="H86" s="14" t="n">
@@ -5285,7 +5282,7 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>P2019</t>
+          <t>P2022</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
@@ -5295,7 +5292,7 @@
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>CJU - Vigilancia y MET Plus - Fixed</t>
+          <t>CJU - Vigilancia y MET Plus - Ret SW</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
@@ -5305,12 +5302,12 @@
       </c>
       <c r="F87" s="6" t="inlineStr">
         <is>
-          <t>Implementación</t>
+          <t>Software SW</t>
         </is>
       </c>
       <c r="G87" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Ret SW</t>
         </is>
       </c>
       <c r="H87" s="8" t="n">
@@ -5341,22 +5338,22 @@
       </c>
       <c r="B88" s="12" t="inlineStr">
         <is>
-          <t>P2020</t>
+          <t>P1932</t>
         </is>
       </c>
       <c r="C88" s="12" t="inlineStr">
         <is>
-          <t>CJU</t>
+          <t>DIA</t>
         </is>
       </c>
       <c r="D88" s="13" t="inlineStr">
         <is>
-          <t>CJU - Vigilancia y MET Plus - Cloud</t>
+          <t>DIA - Aprovisionamiento multinube - Lote 3 - Cloud</t>
         </is>
       </c>
       <c r="E88" s="13" t="inlineStr">
         <is>
-          <t>Coljuegos</t>
+          <t>DIAN</t>
         </is>
       </c>
       <c r="F88" s="12" t="inlineStr">
@@ -5370,13 +5367,13 @@
         </is>
       </c>
       <c r="H88" s="14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="I88" s="9" t="n">
-        <v>0.006999999999999999</v>
+        <v>20</v>
+      </c>
+      <c r="I88" s="18" t="n">
+        <v>0.103</v>
       </c>
       <c r="J88" s="14" t="n">
-        <v>76.5</v>
+        <v>65.5</v>
       </c>
       <c r="K88" s="15" t="inlineStr">
         <is>
@@ -5397,22 +5394,22 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>P2021</t>
+          <t>P2729</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>CJU</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>CJU - Vigilancia y MET Plus - Ret</t>
+          <t>ICF - Banco de items Fase 2 - Ret</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>Coljuegos</t>
+          <t>Icfes</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr">
@@ -5426,13 +5423,13 @@
         </is>
       </c>
       <c r="H89" s="8" t="n">
-        <v>1.4</v>
+        <v>5.7</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.029</v>
       </c>
       <c r="J89" s="8" t="n">
-        <v>76.5</v>
+        <v>64.5</v>
       </c>
       <c r="K89" s="10" t="inlineStr">
         <is>
@@ -5453,42 +5450,42 @@
       </c>
       <c r="B90" s="12" t="inlineStr">
         <is>
-          <t>P2022</t>
+          <t>P2730</t>
         </is>
       </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
-          <t>CJU</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="D90" s="13" t="inlineStr">
         <is>
-          <t>CJU - Vigilancia y MET Plus - Ret SW</t>
+          <t>ICF - Banco de items Fase 2 - Ret Other Vendors</t>
         </is>
       </c>
       <c r="E90" s="13" t="inlineStr">
         <is>
-          <t>Coljuegos</t>
+          <t>Icfes</t>
         </is>
       </c>
       <c r="F90" s="12" t="inlineStr">
         <is>
-          <t>Software SW</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="G90" s="12" t="inlineStr">
         <is>
-          <t>Ret SW</t>
+          <t>Ret Other Vendors</t>
         </is>
       </c>
       <c r="H90" s="14" t="n">
-        <v>1.4</v>
+        <v>5.7</v>
       </c>
       <c r="I90" s="9" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.029</v>
       </c>
       <c r="J90" s="14" t="n">
-        <v>76.5</v>
+        <v>64.5</v>
       </c>
       <c r="K90" s="15" t="inlineStr">
         <is>
@@ -5509,22 +5506,22 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>P1932</t>
+          <t>P2731</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>DIA</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>DIA - Aprovisionamiento multinube - Lote 3 - Cloud</t>
+          <t>ICF - Banco de items Fase 2 - Cloud</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>DIAN</t>
+          <t>Icfes</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
@@ -5538,13 +5535,13 @@
         </is>
       </c>
       <c r="H91" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="I91" s="18" t="n">
-        <v>0.103</v>
+        <v>5.7</v>
+      </c>
+      <c r="I91" s="9" t="n">
+        <v>0.029</v>
       </c>
       <c r="J91" s="8" t="n">
-        <v>65.5</v>
+        <v>64.5</v>
       </c>
       <c r="K91" s="10" t="inlineStr">
         <is>
@@ -5565,7 +5562,7 @@
       </c>
       <c r="B92" s="12" t="inlineStr">
         <is>
-          <t>P2729</t>
+          <t>P2742</t>
         </is>
       </c>
       <c r="C92" s="12" t="inlineStr">
@@ -5575,7 +5572,7 @@
       </c>
       <c r="D92" s="13" t="inlineStr">
         <is>
-          <t>ICF - Banco de items Fase 2 - Ret</t>
+          <t>ICF - Citación con Georreferenciación - Fixed</t>
         </is>
       </c>
       <c r="E92" s="13" t="inlineStr">
@@ -5585,22 +5582,22 @@
       </c>
       <c r="F92" s="12" t="inlineStr">
         <is>
-          <t>Operación</t>
+          <t>Implementación</t>
         </is>
       </c>
       <c r="G92" s="12" t="inlineStr">
         <is>
-          <t>Ret</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H92" s="14" t="n">
-        <v>5.7</v>
+        <v>3.4</v>
       </c>
       <c r="I92" s="9" t="n">
-        <v>0.029</v>
+        <v>0.018</v>
       </c>
       <c r="J92" s="14" t="n">
-        <v>64.5</v>
+        <v>38.7</v>
       </c>
       <c r="K92" s="15" t="inlineStr">
         <is>
@@ -5621,7 +5618,7 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>P2730</t>
+          <t>P2744</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
@@ -5631,7 +5628,7 @@
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>ICF - Banco de items Fase 2 - Ret Other Vendors</t>
+          <t>ICF - Citación con Georreferenciación - Ret</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr">
@@ -5646,17 +5643,17 @@
       </c>
       <c r="G93" s="6" t="inlineStr">
         <is>
-          <t>Ret Other Vendors</t>
+          <t>Ret</t>
         </is>
       </c>
       <c r="H93" s="8" t="n">
-        <v>5.7</v>
+        <v>3.4</v>
       </c>
       <c r="I93" s="9" t="n">
-        <v>0.029</v>
+        <v>0.018</v>
       </c>
       <c r="J93" s="8" t="n">
-        <v>64.5</v>
+        <v>38.7</v>
       </c>
       <c r="K93" s="10" t="inlineStr">
         <is>
@@ -5677,7 +5674,7 @@
       </c>
       <c r="B94" s="12" t="inlineStr">
         <is>
-          <t>P2731</t>
+          <t>P2745</t>
         </is>
       </c>
       <c r="C94" s="12" t="inlineStr">
@@ -5687,7 +5684,7 @@
       </c>
       <c r="D94" s="13" t="inlineStr">
         <is>
-          <t>ICF - Banco de items Fase 2 - Cloud</t>
+          <t>ICF - Citación con Georreferenciación - Ret SW</t>
         </is>
       </c>
       <c r="E94" s="13" t="inlineStr">
@@ -5697,22 +5694,22 @@
       </c>
       <c r="F94" s="12" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Software SW</t>
         </is>
       </c>
       <c r="G94" s="12" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>Ret SW</t>
         </is>
       </c>
       <c r="H94" s="14" t="n">
-        <v>5.7</v>
+        <v>3.4</v>
       </c>
       <c r="I94" s="9" t="n">
-        <v>0.029</v>
+        <v>0.018</v>
       </c>
       <c r="J94" s="14" t="n">
-        <v>64.5</v>
+        <v>38.7</v>
       </c>
       <c r="K94" s="15" t="inlineStr">
         <is>
@@ -5733,7 +5730,7 @@
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>P2742</t>
+          <t>P2746</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
@@ -5743,7 +5740,7 @@
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>ICF - Citación con Georreferenciación - Fixed</t>
+          <t>ICF - Citación con Georreferenciación - Other Vendors</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
@@ -5753,12 +5750,12 @@
       </c>
       <c r="F95" s="6" t="inlineStr">
         <is>
-          <t>Implementación</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="G95" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Other Vendors</t>
         </is>
       </c>
       <c r="H95" s="8" t="n">
@@ -5789,7 +5786,7 @@
       </c>
       <c r="B96" s="12" t="inlineStr">
         <is>
-          <t>P2744</t>
+          <t>P2747</t>
         </is>
       </c>
       <c r="C96" s="12" t="inlineStr">
@@ -5799,7 +5796,7 @@
       </c>
       <c r="D96" s="13" t="inlineStr">
         <is>
-          <t>ICF - Citación con Georreferenciación - Ret</t>
+          <t>ICF - Citación con Georreferenciación - Cloud</t>
         </is>
       </c>
       <c r="E96" s="13" t="inlineStr">
@@ -5809,12 +5806,12 @@
       </c>
       <c r="F96" s="12" t="inlineStr">
         <is>
-          <t>Operación</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="G96" s="12" t="inlineStr">
         <is>
-          <t>Ret</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="H96" s="14" t="n">
@@ -5845,7 +5842,7 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>P2745</t>
+          <t>P2732</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
@@ -5855,7 +5852,7 @@
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>ICF - Citación con Georreferenciación - Ret SW</t>
+          <t>ICF - Datalake 2026-1 - Ret</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
@@ -5865,22 +5862,22 @@
       </c>
       <c r="F97" s="6" t="inlineStr">
         <is>
-          <t>Software SW</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="G97" s="6" t="inlineStr">
         <is>
-          <t>Ret SW</t>
+          <t>Ret</t>
         </is>
       </c>
       <c r="H97" s="8" t="n">
-        <v>3.4</v>
+        <v>5.7</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>0.018</v>
+        <v>0.029</v>
       </c>
       <c r="J97" s="8" t="n">
-        <v>38.7</v>
+        <v>64.5</v>
       </c>
       <c r="K97" s="10" t="inlineStr">
         <is>
@@ -5901,7 +5898,7 @@
       </c>
       <c r="B98" s="12" t="inlineStr">
         <is>
-          <t>P2746</t>
+          <t>P2733</t>
         </is>
       </c>
       <c r="C98" s="12" t="inlineStr">
@@ -5911,7 +5908,7 @@
       </c>
       <c r="D98" s="13" t="inlineStr">
         <is>
-          <t>ICF - Citación con Georreferenciación - Other Vendors</t>
+          <t>ICF - Datalake 2026-1 - Cloud</t>
         </is>
       </c>
       <c r="E98" s="13" t="inlineStr">
@@ -5921,22 +5918,22 @@
       </c>
       <c r="F98" s="12" t="inlineStr">
         <is>
-          <t>Operación</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="G98" s="12" t="inlineStr">
         <is>
-          <t>Other Vendors</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="H98" s="14" t="n">
-        <v>3.4</v>
+        <v>5.7</v>
       </c>
       <c r="I98" s="9" t="n">
-        <v>0.018</v>
+        <v>0.029</v>
       </c>
       <c r="J98" s="14" t="n">
-        <v>38.7</v>
+        <v>64.5</v>
       </c>
       <c r="K98" s="15" t="inlineStr">
         <is>
@@ -5957,7 +5954,7 @@
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>P2747</t>
+          <t>P2734</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
@@ -5967,7 +5964,7 @@
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>ICF - Citación con Georreferenciación - Cloud</t>
+          <t>ICF - Datalake 2026-1 - Ret Sw</t>
         </is>
       </c>
       <c r="E99" s="7" t="inlineStr">
@@ -5977,22 +5974,22 @@
       </c>
       <c r="F99" s="6" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Software SW</t>
         </is>
       </c>
       <c r="G99" s="6" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>Ret Sw</t>
         </is>
       </c>
       <c r="H99" s="8" t="n">
-        <v>3.4</v>
+        <v>5.7</v>
       </c>
       <c r="I99" s="9" t="n">
-        <v>0.018</v>
+        <v>0.029</v>
       </c>
       <c r="J99" s="8" t="n">
-        <v>38.7</v>
+        <v>64.5</v>
       </c>
       <c r="K99" s="10" t="inlineStr">
         <is>
@@ -6013,7 +6010,7 @@
       </c>
       <c r="B100" s="12" t="inlineStr">
         <is>
-          <t>P2732</t>
+          <t>P2240</t>
         </is>
       </c>
       <c r="C100" s="12" t="inlineStr">
@@ -6023,12 +6020,12 @@
       </c>
       <c r="D100" s="13" t="inlineStr">
         <is>
-          <t>ICF - Datalake 2026-1 - Ret</t>
+          <t>ICF - Evolución Datalake Fase 2 2025 - Ret Other Vendors</t>
         </is>
       </c>
       <c r="E100" s="13" t="inlineStr">
         <is>
-          <t>Icfes</t>
+          <t>Instituto Colombiano Para La Evaluacion De La Educacion ICFES</t>
         </is>
       </c>
       <c r="F100" s="12" t="inlineStr">
@@ -6038,17 +6035,17 @@
       </c>
       <c r="G100" s="12" t="inlineStr">
         <is>
-          <t>Ret</t>
+          <t>Ret Other Vendors</t>
         </is>
       </c>
       <c r="H100" s="14" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="I100" s="9" t="n">
-        <v>0.029</v>
+        <v>17</v>
+      </c>
+      <c r="I100" s="18" t="n">
+        <v>0.08800000000000001</v>
       </c>
       <c r="J100" s="14" t="n">
-        <v>64.5</v>
+        <v>193.5</v>
       </c>
       <c r="K100" s="15" t="inlineStr">
         <is>
@@ -6069,7 +6066,7 @@
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>P2733</t>
+          <t>P2559</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
@@ -6079,32 +6076,32 @@
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>ICF - Datalake 2026-1 - Cloud</t>
+          <t>ICF - Operacion en AWS - Ret Other Vendors</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
-          <t>Icfes</t>
+          <t>ICFES</t>
         </is>
       </c>
       <c r="F101" s="6" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="G101" s="6" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>Ret Other Vendors</t>
         </is>
       </c>
       <c r="H101" s="8" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="I101" s="9" t="n">
-        <v>0.029</v>
+        <v>17</v>
+      </c>
+      <c r="I101" s="18" t="n">
+        <v>0.08800000000000001</v>
       </c>
       <c r="J101" s="8" t="n">
-        <v>64.5</v>
+        <v>193.5</v>
       </c>
       <c r="K101" s="10" t="inlineStr">
         <is>
@@ -6125,51 +6122,51 @@
       </c>
       <c r="B102" s="12" t="inlineStr">
         <is>
-          <t>P2734</t>
+          <t>P1947</t>
         </is>
       </c>
       <c r="C102" s="12" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="D102" s="13" t="inlineStr">
         <is>
-          <t>ICF - Datalake 2026-1 - Ret Sw</t>
+          <t>JPM - Cloud Managed Services 2023-25 - Ret</t>
         </is>
       </c>
       <c r="E102" s="13" t="inlineStr">
         <is>
-          <t>Icfes</t>
+          <t>JPMP - Justicia Penal Militar y Policial</t>
         </is>
       </c>
       <c r="F102" s="12" t="inlineStr">
         <is>
-          <t>Software SW</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="G102" s="12" t="inlineStr">
         <is>
-          <t>Ret Sw</t>
+          <t>Ret</t>
         </is>
       </c>
       <c r="H102" s="14" t="n">
-        <v>5.7</v>
+        <v>13.5</v>
       </c>
       <c r="I102" s="9" t="n">
-        <v>0.029</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J102" s="14" t="n">
-        <v>64.5</v>
-      </c>
-      <c r="K102" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>103.8</v>
+      </c>
+      <c r="K102" s="19" t="inlineStr">
+        <is>
+          <t>🔄 Reasignado</t>
         </is>
       </c>
       <c r="L102" s="11" t="inlineStr">
         <is>
-          <t>Juan Bernal</t>
+          <t>David Cortes</t>
         </is>
       </c>
     </row>
@@ -6181,280 +6178,280 @@
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>P2240</t>
+          <t>P1948</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>ICF - Evolución Datalake Fase 2 2025 - Ret Other Vendors</t>
+          <t>JPM - Cloud Managed Services 2023-25 - Cloud</t>
         </is>
       </c>
       <c r="E103" s="7" t="inlineStr">
         <is>
-          <t>Instituto Colombiano Para La Evaluacion De La Educacion ICFES</t>
+          <t>JPMP - Justicia Penal Militar y Policial</t>
         </is>
       </c>
       <c r="F103" s="6" t="inlineStr">
         <is>
-          <t>Operación</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="G103" s="6" t="inlineStr">
         <is>
-          <t>Ret Other Vendors</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="H103" s="8" t="n">
-        <v>17</v>
-      </c>
-      <c r="I103" s="18" t="n">
-        <v>0.08800000000000001</v>
+        <v>13.5</v>
+      </c>
+      <c r="I103" s="9" t="n">
+        <v>0.07000000000000001</v>
       </c>
       <c r="J103" s="8" t="n">
-        <v>193.5</v>
-      </c>
-      <c r="K103" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>103.8</v>
+      </c>
+      <c r="K103" s="19" t="inlineStr">
+        <is>
+          <t>🔄 Reasignado</t>
         </is>
       </c>
       <c r="L103" s="5" t="inlineStr">
         <is>
-          <t>Juan Bernal</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="18" customHeight="1">
-      <c r="A104" s="11" t="inlineStr">
-        <is>
-          <t>Juan Bernal</t>
-        </is>
-      </c>
-      <c r="B104" s="12" t="inlineStr">
-        <is>
-          <t>P2559</t>
-        </is>
-      </c>
-      <c r="C104" s="12" t="inlineStr">
-        <is>
-          <t>ICF</t>
-        </is>
-      </c>
-      <c r="D104" s="13" t="inlineStr">
-        <is>
-          <t>ICF - Operacion en AWS - Ret Other Vendors</t>
-        </is>
-      </c>
-      <c r="E104" s="13" t="inlineStr">
-        <is>
-          <t>ICFES</t>
-        </is>
-      </c>
-      <c r="F104" s="12" t="inlineStr">
-        <is>
-          <t>Operación</t>
-        </is>
-      </c>
-      <c r="G104" s="12" t="inlineStr">
-        <is>
-          <t>Ret Other Vendors</t>
-        </is>
-      </c>
-      <c r="H104" s="14" t="n">
-        <v>17</v>
-      </c>
-      <c r="I104" s="18" t="n">
-        <v>0.08800000000000001</v>
-      </c>
-      <c r="J104" s="14" t="n">
-        <v>193.5</v>
-      </c>
-      <c r="K104" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L104" s="11" t="inlineStr">
-        <is>
-          <t>Juan Bernal</t>
+          <t>David Cortes</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="22" customHeight="1">
+      <c r="A104" s="24" t="inlineStr">
+        <is>
+          <t>▶  Kelly Carbonell  –  14 sub-proyectos  |  ~119h est./mes  (62% capacidad)</t>
         </is>
       </c>
     </row>
     <row r="105" ht="18" customHeight="1">
-      <c r="A105" s="5" t="inlineStr">
-        <is>
-          <t>Juan Bernal</t>
-        </is>
-      </c>
-      <c r="B105" s="6" t="inlineStr">
-        <is>
-          <t>P1947</t>
-        </is>
-      </c>
-      <c r="C105" s="6" t="inlineStr">
-        <is>
-          <t>JPM</t>
-        </is>
-      </c>
-      <c r="D105" s="7" t="inlineStr">
-        <is>
-          <t>JPM - Cloud Managed Services 2023-25 - Ret</t>
-        </is>
-      </c>
-      <c r="E105" s="7" t="inlineStr">
-        <is>
-          <t>JPMP - Justicia Penal Militar y Policial</t>
-        </is>
-      </c>
-      <c r="F105" s="6" t="inlineStr">
-        <is>
-          <t>Operación</t>
-        </is>
-      </c>
-      <c r="G105" s="6" t="inlineStr">
-        <is>
-          <t>Ret</t>
-        </is>
-      </c>
-      <c r="H105" s="8" t="n">
-        <v>13.5</v>
+      <c r="A105" s="11" t="inlineStr">
+        <is>
+          <t>Kelly Carbonell</t>
+        </is>
+      </c>
+      <c r="B105" s="12" t="inlineStr">
+        <is>
+          <t>P2397</t>
+        </is>
+      </c>
+      <c r="C105" s="12" t="inlineStr">
+        <is>
+          <t>ACA</t>
+        </is>
+      </c>
+      <c r="D105" s="13" t="inlineStr">
+        <is>
+          <t>ACA -  Virtualización infraestructura Cali  - Cloud</t>
+        </is>
+      </c>
+      <c r="E105" s="13" t="inlineStr">
+        <is>
+          <t>Alcaldia de Cali</t>
+        </is>
+      </c>
+      <c r="F105" s="12" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="G105" s="12" t="inlineStr">
+        <is>
+          <t>Cloud</t>
+        </is>
+      </c>
+      <c r="H105" s="14" t="n">
+        <v>6.9</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="J105" s="8" t="n">
-        <v>103.8</v>
-      </c>
-      <c r="K105" s="19" t="inlineStr">
-        <is>
-          <t>🔄 Reasignado</t>
-        </is>
-      </c>
-      <c r="L105" s="5" t="inlineStr">
-        <is>
-          <t>David Cortes</t>
+        <v>0.036</v>
+      </c>
+      <c r="J105" s="14" t="n">
+        <v>226.1</v>
+      </c>
+      <c r="K105" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L105" s="11" t="inlineStr">
+        <is>
+          <t>Kelly Carbonell</t>
         </is>
       </c>
     </row>
     <row r="106" ht="18" customHeight="1">
       <c r="A106" s="11" t="inlineStr">
         <is>
-          <t>Juan Bernal</t>
+          <t>Kelly Carbonell</t>
         </is>
       </c>
       <c r="B106" s="12" t="inlineStr">
         <is>
-          <t>P1948</t>
+          <t>P2398</t>
         </is>
       </c>
       <c r="C106" s="12" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>ACA</t>
         </is>
       </c>
       <c r="D106" s="13" t="inlineStr">
         <is>
-          <t>JPM - Cloud Managed Services 2023-25 - Cloud</t>
+          <t>ACA -  Virtualización infraestructura Cali  - Ret</t>
         </is>
       </c>
       <c r="E106" s="13" t="inlineStr">
         <is>
-          <t>JPMP - Justicia Penal Militar y Policial</t>
+          <t>Alcaldia de Cali</t>
         </is>
       </c>
       <c r="F106" s="12" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="G106" s="12" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>Ret</t>
         </is>
       </c>
       <c r="H106" s="14" t="n">
-        <v>13.5</v>
+        <v>6.9</v>
       </c>
       <c r="I106" s="9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.036</v>
       </c>
       <c r="J106" s="14" t="n">
-        <v>103.8</v>
-      </c>
-      <c r="K106" s="19" t="inlineStr">
-        <is>
-          <t>🔄 Reasignado</t>
+        <v>226.1</v>
+      </c>
+      <c r="K106" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="L106" s="11" t="inlineStr">
         <is>
-          <t>David Cortes</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="22" customHeight="1">
-      <c r="A107" s="24" t="inlineStr">
-        <is>
-          <t>▶  Kelly Carbonell  –  14 sub-proyectos  |  ~119h est./mes  (62% capacidad)</t>
+          <t>Kelly Carbonell</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="18" customHeight="1">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>Kelly Carbonell</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>P2399</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>ACA</t>
+        </is>
+      </c>
+      <c r="D107" s="7" t="inlineStr">
+        <is>
+          <t>ACA -  Virtualización infraestructura Cali  - Ret SW</t>
+        </is>
+      </c>
+      <c r="E107" s="7" t="inlineStr">
+        <is>
+          <t>Alcaldia de Cali</t>
+        </is>
+      </c>
+      <c r="F107" s="6" t="inlineStr">
+        <is>
+          <t>Software SW</t>
+        </is>
+      </c>
+      <c r="G107" s="6" t="inlineStr">
+        <is>
+          <t>Ret SW</t>
+        </is>
+      </c>
+      <c r="H107" s="8" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="I107" s="9" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="J107" s="8" t="n">
+        <v>226.1</v>
+      </c>
+      <c r="K107" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L107" s="5" t="inlineStr">
+        <is>
+          <t>Kelly Carbonell</t>
         </is>
       </c>
     </row>
     <row r="108" ht="18" customHeight="1">
-      <c r="A108" s="5" t="inlineStr">
+      <c r="A108" s="11" t="inlineStr">
         <is>
           <t>Kelly Carbonell</t>
         </is>
       </c>
-      <c r="B108" s="6" t="inlineStr">
-        <is>
-          <t>P2397</t>
-        </is>
-      </c>
-      <c r="C108" s="6" t="inlineStr">
+      <c r="B108" s="12" t="inlineStr">
+        <is>
+          <t>P2400</t>
+        </is>
+      </c>
+      <c r="C108" s="12" t="inlineStr">
         <is>
           <t>ACA</t>
         </is>
       </c>
-      <c r="D108" s="7" t="inlineStr">
-        <is>
-          <t>ACA -  Virtualización infraestructura Cali  - Cloud</t>
-        </is>
-      </c>
-      <c r="E108" s="7" t="inlineStr">
+      <c r="D108" s="13" t="inlineStr">
+        <is>
+          <t>ACA -  Virtualización infraestructura Cali  - Ret Other Vendors</t>
+        </is>
+      </c>
+      <c r="E108" s="13" t="inlineStr">
         <is>
           <t>Alcaldia de Cali</t>
         </is>
       </c>
-      <c r="F108" s="6" t="inlineStr">
-        <is>
-          <t>Data</t>
-        </is>
-      </c>
-      <c r="G108" s="6" t="inlineStr">
-        <is>
-          <t>Cloud</t>
-        </is>
-      </c>
-      <c r="H108" s="8" t="n">
+      <c r="F108" s="12" t="inlineStr">
+        <is>
+          <t>Operación</t>
+        </is>
+      </c>
+      <c r="G108" s="12" t="inlineStr">
+        <is>
+          <t>Ret Other Vendors</t>
+        </is>
+      </c>
+      <c r="H108" s="14" t="n">
         <v>6.9</v>
       </c>
       <c r="I108" s="9" t="n">
         <v>0.036</v>
       </c>
-      <c r="J108" s="8" t="n">
+      <c r="J108" s="14" t="n">
         <v>226.1</v>
       </c>
-      <c r="K108" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L108" s="5" t="inlineStr">
+      <c r="K108" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L108" s="11" t="inlineStr">
         <is>
           <t>Kelly Carbonell</t>
         </is>
@@ -6468,7 +6465,7 @@
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>P2398</t>
+          <t>P2404</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
@@ -6478,7 +6475,7 @@
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>ACA -  Virtualización infraestructura Cali  - Ret</t>
+          <t>ACA - Fase III DataCali - Fixed</t>
         </is>
       </c>
       <c r="E109" s="7" t="inlineStr">
@@ -6488,22 +6485,22 @@
       </c>
       <c r="F109" s="6" t="inlineStr">
         <is>
-          <t>Operación</t>
+          <t>Implementación</t>
         </is>
       </c>
       <c r="G109" s="6" t="inlineStr">
         <is>
-          <t>Ret</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H109" s="8" t="n">
-        <v>6.9</v>
+        <v>13.8</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>0.036</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="J109" s="8" t="n">
-        <v>226.1</v>
+        <v>452.2</v>
       </c>
       <c r="K109" s="10" t="inlineStr">
         <is>
@@ -6524,7 +6521,7 @@
       </c>
       <c r="B110" s="12" t="inlineStr">
         <is>
-          <t>P2399</t>
+          <t>P2405</t>
         </is>
       </c>
       <c r="C110" s="12" t="inlineStr">
@@ -6534,7 +6531,7 @@
       </c>
       <c r="D110" s="13" t="inlineStr">
         <is>
-          <t>ACA -  Virtualización infraestructura Cali  - Ret SW</t>
+          <t>ACA - Fase III DataCali - Ret Other Vendors</t>
         </is>
       </c>
       <c r="E110" s="13" t="inlineStr">
@@ -6544,22 +6541,22 @@
       </c>
       <c r="F110" s="12" t="inlineStr">
         <is>
-          <t>Software SW</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="G110" s="12" t="inlineStr">
         <is>
-          <t>Ret SW</t>
+          <t>Ret Other Vendors</t>
         </is>
       </c>
       <c r="H110" s="14" t="n">
-        <v>6.9</v>
+        <v>13.8</v>
       </c>
       <c r="I110" s="9" t="n">
-        <v>0.036</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="J110" s="14" t="n">
-        <v>226.1</v>
+        <v>452.2</v>
       </c>
       <c r="K110" s="15" t="inlineStr">
         <is>
@@ -6580,7 +6577,7 @@
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>P2400</t>
+          <t>P2541</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
@@ -6590,7 +6587,7 @@
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>ACA -  Virtualización infraestructura Cali  - Ret Other Vendors</t>
+          <t>ACA - Hacienda a un Click - Fixed</t>
         </is>
       </c>
       <c r="E111" s="7" t="inlineStr">
@@ -6600,12 +6597,12 @@
       </c>
       <c r="F111" s="6" t="inlineStr">
         <is>
-          <t>Operación</t>
+          <t>Implementación</t>
         </is>
       </c>
       <c r="G111" s="6" t="inlineStr">
         <is>
-          <t>Ret Other Vendors</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H111" s="8" t="n">
@@ -6636,7 +6633,7 @@
       </c>
       <c r="B112" s="12" t="inlineStr">
         <is>
-          <t>P2404</t>
+          <t>P2542</t>
         </is>
       </c>
       <c r="C112" s="12" t="inlineStr">
@@ -6646,7 +6643,7 @@
       </c>
       <c r="D112" s="13" t="inlineStr">
         <is>
-          <t>ACA - Fase III DataCali - Fixed</t>
+          <t>ACA - Hacienda a un Click - Ret</t>
         </is>
       </c>
       <c r="E112" s="13" t="inlineStr">
@@ -6656,22 +6653,22 @@
       </c>
       <c r="F112" s="12" t="inlineStr">
         <is>
-          <t>Implementación</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="G112" s="12" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Ret</t>
         </is>
       </c>
       <c r="H112" s="14" t="n">
-        <v>13.8</v>
+        <v>6.9</v>
       </c>
       <c r="I112" s="9" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.036</v>
       </c>
       <c r="J112" s="14" t="n">
-        <v>452.2</v>
+        <v>226.1</v>
       </c>
       <c r="K112" s="15" t="inlineStr">
         <is>
@@ -6692,7 +6689,7 @@
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>P2405</t>
+          <t>P2543</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
@@ -6702,7 +6699,7 @@
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>ACA - Fase III DataCali - Ret Other Vendors</t>
+          <t>ACA - Hacienda a un Click - Ret SW</t>
         </is>
       </c>
       <c r="E113" s="7" t="inlineStr">
@@ -6712,22 +6709,22 @@
       </c>
       <c r="F113" s="6" t="inlineStr">
         <is>
-          <t>Operación</t>
+          <t>Software SW</t>
         </is>
       </c>
       <c r="G113" s="6" t="inlineStr">
         <is>
-          <t>Ret Other Vendors</t>
+          <t>Ret SW</t>
         </is>
       </c>
       <c r="H113" s="8" t="n">
-        <v>13.8</v>
+        <v>6.9</v>
       </c>
       <c r="I113" s="9" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.036</v>
       </c>
       <c r="J113" s="8" t="n">
-        <v>452.2</v>
+        <v>226.1</v>
       </c>
       <c r="K113" s="10" t="inlineStr">
         <is>
@@ -6748,7 +6745,7 @@
       </c>
       <c r="B114" s="12" t="inlineStr">
         <is>
-          <t>P2541</t>
+          <t>P2544</t>
         </is>
       </c>
       <c r="C114" s="12" t="inlineStr">
@@ -6758,7 +6755,7 @@
       </c>
       <c r="D114" s="13" t="inlineStr">
         <is>
-          <t>ACA - Hacienda a un Click - Fixed</t>
+          <t>ACA - Hacienda a un Click - Ret Other Vendors</t>
         </is>
       </c>
       <c r="E114" s="13" t="inlineStr">
@@ -6768,12 +6765,12 @@
       </c>
       <c r="F114" s="12" t="inlineStr">
         <is>
-          <t>Implementación</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="G114" s="12" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Ret Other Vendors</t>
         </is>
       </c>
       <c r="H114" s="14" t="n">
@@ -6804,7 +6801,7 @@
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>P2542</t>
+          <t>P2822</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
@@ -6814,7 +6811,7 @@
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>ACA - Hacienda a un Click - Ret</t>
+          <t>ACA - Secretaría de Transparencia MVP  - Fixed</t>
         </is>
       </c>
       <c r="E115" s="7" t="inlineStr">
@@ -6824,22 +6821,22 @@
       </c>
       <c r="F115" s="6" t="inlineStr">
         <is>
-          <t>Operación</t>
+          <t>Implementación</t>
         </is>
       </c>
       <c r="G115" s="6" t="inlineStr">
         <is>
-          <t>Ret</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H115" s="8" t="n">
-        <v>6.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v>0.036</v>
+        <v>0.048</v>
       </c>
       <c r="J115" s="8" t="n">
-        <v>226.1</v>
+        <v>301.5</v>
       </c>
       <c r="K115" s="10" t="inlineStr">
         <is>
@@ -6860,7 +6857,7 @@
       </c>
       <c r="B116" s="12" t="inlineStr">
         <is>
-          <t>P2543</t>
+          <t>P2823</t>
         </is>
       </c>
       <c r="C116" s="12" t="inlineStr">
@@ -6870,7 +6867,7 @@
       </c>
       <c r="D116" s="13" t="inlineStr">
         <is>
-          <t>ACA - Hacienda a un Click - Ret SW</t>
+          <t>ACA - Secretaría de Transparencia MVP  - Ret</t>
         </is>
       </c>
       <c r="E116" s="13" t="inlineStr">
@@ -6880,22 +6877,22 @@
       </c>
       <c r="F116" s="12" t="inlineStr">
         <is>
-          <t>Software SW</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="G116" s="12" t="inlineStr">
         <is>
-          <t>Ret SW</t>
+          <t>Ret</t>
         </is>
       </c>
       <c r="H116" s="14" t="n">
-        <v>6.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I116" s="9" t="n">
-        <v>0.036</v>
+        <v>0.048</v>
       </c>
       <c r="J116" s="14" t="n">
-        <v>226.1</v>
+        <v>301.5</v>
       </c>
       <c r="K116" s="15" t="inlineStr">
         <is>
@@ -6916,7 +6913,7 @@
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>P2544</t>
+          <t>P2824</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
@@ -6926,7 +6923,7 @@
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>ACA - Hacienda a un Click - Ret Other Vendors</t>
+          <t>ACA - Secretaría de Transparencia MVP  - Cloud</t>
         </is>
       </c>
       <c r="E117" s="7" t="inlineStr">
@@ -6936,22 +6933,22 @@
       </c>
       <c r="F117" s="6" t="inlineStr">
         <is>
-          <t>Operación</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="G117" s="6" t="inlineStr">
         <is>
-          <t>Ret Other Vendors</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="H117" s="8" t="n">
-        <v>6.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I117" s="9" t="n">
-        <v>0.036</v>
+        <v>0.048</v>
       </c>
       <c r="J117" s="8" t="n">
-        <v>226.1</v>
+        <v>301.5</v>
       </c>
       <c r="K117" s="10" t="inlineStr">
         <is>
@@ -6972,190 +6969,141 @@
       </c>
       <c r="B118" s="12" t="inlineStr">
         <is>
-          <t>P2822</t>
+          <t>P1923</t>
         </is>
       </c>
       <c r="C118" s="12" t="inlineStr">
         <is>
-          <t>ACA</t>
+          <t>CCC</t>
         </is>
       </c>
       <c r="D118" s="13" t="inlineStr">
         <is>
-          <t>ACA - Secretaría de Transparencia MVP  - Fixed</t>
+          <t>CCC - IaaS para DRP - Cloud</t>
         </is>
       </c>
       <c r="E118" s="13" t="inlineStr">
         <is>
-          <t>Alcaldia de Cali</t>
+          <t>Cámara de Comercio de Cali</t>
         </is>
       </c>
       <c r="F118" s="12" t="inlineStr">
         <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="G118" s="12" t="inlineStr">
+        <is>
+          <t>Cloud</t>
+        </is>
+      </c>
+      <c r="H118" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="I118" s="9" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="J118" s="14" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="K118" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L118" s="11" t="inlineStr">
+        <is>
+          <t>Kelly Carbonell</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="22" customHeight="1">
+      <c r="A119" s="25" t="inlineStr">
+        <is>
+          <t>▶  Miguel Garcia  –  7 sub-proyectos  |  ~179h est./mes  (92% capacidad)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="18" customHeight="1">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>Miguel Garcia</t>
+        </is>
+      </c>
+      <c r="B120" s="6" t="inlineStr">
+        <is>
+          <t>P2457</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
+        <is>
+          <t>ADR</t>
+        </is>
+      </c>
+      <c r="D120" s="7" t="inlineStr">
+        <is>
+          <t>ADR - AI Auditoría Médica - Fixed</t>
+        </is>
+      </c>
+      <c r="E120" s="7" t="inlineStr">
+        <is>
+          <t>La Administradora de los Recursos del Sistema General de Seguridad Social en Salud</t>
+        </is>
+      </c>
+      <c r="F120" s="6" t="inlineStr">
+        <is>
           <t>Implementación</t>
         </is>
       </c>
-      <c r="G118" s="12" t="inlineStr">
+      <c r="G120" s="6" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="H118" s="14" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="I118" s="9" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="J118" s="14" t="n">
-        <v>301.5</v>
-      </c>
-      <c r="K118" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L118" s="11" t="inlineStr">
-        <is>
-          <t>Kelly Carbonell</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="18" customHeight="1">
-      <c r="A119" s="5" t="inlineStr">
-        <is>
-          <t>Kelly Carbonell</t>
-        </is>
-      </c>
-      <c r="B119" s="6" t="inlineStr">
-        <is>
-          <t>P2823</t>
-        </is>
-      </c>
-      <c r="C119" s="6" t="inlineStr">
-        <is>
-          <t>ACA</t>
-        </is>
-      </c>
-      <c r="D119" s="7" t="inlineStr">
-        <is>
-          <t>ACA - Secretaría de Transparencia MVP  - Ret</t>
-        </is>
-      </c>
-      <c r="E119" s="7" t="inlineStr">
-        <is>
-          <t>Alcaldia de Cali</t>
-        </is>
-      </c>
-      <c r="F119" s="6" t="inlineStr">
-        <is>
-          <t>Operación</t>
-        </is>
-      </c>
-      <c r="G119" s="6" t="inlineStr">
-        <is>
-          <t>Ret</t>
-        </is>
-      </c>
-      <c r="H119" s="8" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="I119" s="9" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="J119" s="8" t="n">
-        <v>301.5</v>
-      </c>
-      <c r="K119" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L119" s="5" t="inlineStr">
-        <is>
-          <t>Kelly Carbonell</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="18" customHeight="1">
-      <c r="A120" s="11" t="inlineStr">
-        <is>
-          <t>Kelly Carbonell</t>
-        </is>
-      </c>
-      <c r="B120" s="12" t="inlineStr">
-        <is>
-          <t>P2824</t>
-        </is>
-      </c>
-      <c r="C120" s="12" t="inlineStr">
-        <is>
-          <t>ACA</t>
-        </is>
-      </c>
-      <c r="D120" s="13" t="inlineStr">
-        <is>
-          <t>ACA - Secretaría de Transparencia MVP  - Cloud</t>
-        </is>
-      </c>
-      <c r="E120" s="13" t="inlineStr">
-        <is>
-          <t>Alcaldia de Cali</t>
-        </is>
-      </c>
-      <c r="F120" s="12" t="inlineStr">
-        <is>
-          <t>Data</t>
-        </is>
-      </c>
-      <c r="G120" s="12" t="inlineStr">
-        <is>
-          <t>Cloud</t>
-        </is>
-      </c>
-      <c r="H120" s="14" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="I120" s="9" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="J120" s="14" t="n">
-        <v>301.5</v>
-      </c>
-      <c r="K120" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L120" s="11" t="inlineStr">
-        <is>
-          <t>Kelly Carbonell</t>
+      <c r="H120" s="8" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="I120" s="18" t="n">
+        <v>0.116</v>
+      </c>
+      <c r="J120" s="8" t="n">
+        <v>1031.8</v>
+      </c>
+      <c r="K120" s="19" t="inlineStr">
+        <is>
+          <t>🔄 Reasignado</t>
+        </is>
+      </c>
+      <c r="L120" s="5" t="inlineStr">
+        <is>
+          <t>Indira Duarte</t>
         </is>
       </c>
     </row>
     <row r="121" ht="18" customHeight="1">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>Kelly Carbonell</t>
+          <t>Miguel Garcia</t>
         </is>
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>P1923</t>
+          <t>P2470</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>CCC</t>
+          <t>ADR</t>
         </is>
       </c>
       <c r="D121" s="7" t="inlineStr">
         <is>
-          <t>CCC - IaaS para DRP - Cloud</t>
+          <t>ADR - AI Auditoría Médica - Cloud</t>
         </is>
       </c>
       <c r="E121" s="7" t="inlineStr">
         <is>
-          <t>Cámara de Comercio de Cali</t>
+          <t>La Administradora de los Recursos del Sistema General de Seguridad Social en Salud</t>
         </is>
       </c>
       <c r="F121" s="6" t="inlineStr">
@@ -7169,83 +7117,132 @@
         </is>
       </c>
       <c r="H121" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I121" s="9" t="n">
-        <v>0.046</v>
+        <v>22.4</v>
+      </c>
+      <c r="I121" s="18" t="n">
+        <v>0.116</v>
       </c>
       <c r="J121" s="8" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="K121" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1031.8</v>
+      </c>
+      <c r="K121" s="19" t="inlineStr">
+        <is>
+          <t>🔄 Reasignado</t>
         </is>
       </c>
       <c r="L121" s="5" t="inlineStr">
         <is>
-          <t>Kelly Carbonell</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="22" customHeight="1">
-      <c r="A122" s="25" t="inlineStr">
-        <is>
-          <t>▶  Miguel Garcia  –  4 sub-proyectos  |  ~179h est./mes  (93% capacidad)</t>
+          <t>Indira Duarte</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="18" customHeight="1">
+      <c r="A122" s="11" t="inlineStr">
+        <is>
+          <t>Miguel Garcia</t>
+        </is>
+      </c>
+      <c r="B122" s="12" t="inlineStr">
+        <is>
+          <t>P2471</t>
+        </is>
+      </c>
+      <c r="C122" s="12" t="inlineStr">
+        <is>
+          <t>ADR</t>
+        </is>
+      </c>
+      <c r="D122" s="13" t="inlineStr">
+        <is>
+          <t>ADR - AI Auditoría Médica - Ret Sw</t>
+        </is>
+      </c>
+      <c r="E122" s="13" t="inlineStr">
+        <is>
+          <t>La Administradora de los Recursos del Sistema General de Seguridad Social en Salud</t>
+        </is>
+      </c>
+      <c r="F122" s="12" t="inlineStr">
+        <is>
+          <t>Software SW</t>
+        </is>
+      </c>
+      <c r="G122" s="12" t="inlineStr">
+        <is>
+          <t>Ret Sw</t>
+        </is>
+      </c>
+      <c r="H122" s="14" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="I122" s="18" t="n">
+        <v>0.116</v>
+      </c>
+      <c r="J122" s="14" t="n">
+        <v>1031.8</v>
+      </c>
+      <c r="K122" s="19" t="inlineStr">
+        <is>
+          <t>🔄 Reasignado</t>
+        </is>
+      </c>
+      <c r="L122" s="11" t="inlineStr">
+        <is>
+          <t>Indira Duarte</t>
         </is>
       </c>
     </row>
     <row r="123" ht="18" customHeight="1">
-      <c r="A123" s="11" t="inlineStr">
+      <c r="A123" s="5" t="inlineStr">
         <is>
           <t>Miguel Garcia</t>
         </is>
       </c>
-      <c r="B123" s="12" t="inlineStr">
-        <is>
-          <t>P2457</t>
-        </is>
-      </c>
-      <c r="C123" s="12" t="inlineStr">
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>P2472</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="inlineStr">
         <is>
           <t>ADR</t>
         </is>
       </c>
-      <c r="D123" s="13" t="inlineStr">
-        <is>
-          <t>ADR - AI Auditoría Médica - Fixed</t>
-        </is>
-      </c>
-      <c r="E123" s="13" t="inlineStr">
+      <c r="D123" s="7" t="inlineStr">
+        <is>
+          <t>ADR - AI Auditoría Médica - Ret Other Vendors</t>
+        </is>
+      </c>
+      <c r="E123" s="7" t="inlineStr">
         <is>
           <t>La Administradora de los Recursos del Sistema General de Seguridad Social en Salud</t>
         </is>
       </c>
-      <c r="F123" s="12" t="inlineStr">
-        <is>
-          <t>Implementación</t>
-        </is>
-      </c>
-      <c r="G123" s="12" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="H123" s="14" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="I123" s="16" t="n">
-        <v>0.231</v>
-      </c>
-      <c r="J123" s="14" t="n">
-        <v>2063.6</v>
+      <c r="F123" s="6" t="inlineStr">
+        <is>
+          <t>Operación</t>
+        </is>
+      </c>
+      <c r="G123" s="6" t="inlineStr">
+        <is>
+          <t>Ret Other Vendors</t>
+        </is>
+      </c>
+      <c r="H123" s="8" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="I123" s="18" t="n">
+        <v>0.116</v>
+      </c>
+      <c r="J123" s="8" t="n">
+        <v>1031.8</v>
       </c>
       <c r="K123" s="19" t="inlineStr">
         <is>
           <t>🔄 Reasignado</t>
         </is>
       </c>
-      <c r="L123" s="11" t="inlineStr">
+      <c r="L123" s="5" t="inlineStr">
         <is>
           <t>Indira Duarte</t>
         </is>
@@ -7259,7 +7256,7 @@
       </c>
       <c r="B124" s="12" t="inlineStr">
         <is>
-          <t>P2470</t>
+          <t>P2847</t>
         </is>
       </c>
       <c r="C124" s="12" t="inlineStr">
@@ -7269,7 +7266,7 @@
       </c>
       <c r="D124" s="13" t="inlineStr">
         <is>
-          <t>ADR - AI Auditoría Médica - Cloud</t>
+          <t>ADR - peración Auditoria Cuentas Medicas - Ret</t>
         </is>
       </c>
       <c r="E124" s="13" t="inlineStr">
@@ -7279,22 +7276,22 @@
       </c>
       <c r="F124" s="12" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="G124" s="12" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>Ret</t>
         </is>
       </c>
       <c r="H124" s="14" t="n">
-        <v>44.8</v>
+        <v>29.8</v>
       </c>
       <c r="I124" s="16" t="n">
-        <v>0.231</v>
+        <v>0.154</v>
       </c>
       <c r="J124" s="14" t="n">
-        <v>2063.6</v>
+        <v>1375.8</v>
       </c>
       <c r="K124" s="19" t="inlineStr">
         <is>
@@ -7303,7 +7300,7 @@
       </c>
       <c r="L124" s="11" t="inlineStr">
         <is>
-          <t>Indira Duarte</t>
+          <t>Diana Rojas</t>
         </is>
       </c>
     </row>
@@ -7315,7 +7312,7 @@
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>P2471</t>
+          <t>P2848</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
@@ -7325,7 +7322,7 @@
       </c>
       <c r="D125" s="7" t="inlineStr">
         <is>
-          <t>ADR - AI Auditoría Médica - Ret Sw</t>
+          <t>ADR - peración Auditoria Cuentas Medicas - Cloud</t>
         </is>
       </c>
       <c r="E125" s="7" t="inlineStr">
@@ -7335,22 +7332,22 @@
       </c>
       <c r="F125" s="6" t="inlineStr">
         <is>
-          <t>Software SW</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="G125" s="6" t="inlineStr">
         <is>
-          <t>Ret Sw</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="H125" s="8" t="n">
-        <v>44.8</v>
+        <v>29.8</v>
       </c>
       <c r="I125" s="16" t="n">
-        <v>0.231</v>
+        <v>0.154</v>
       </c>
       <c r="J125" s="8" t="n">
-        <v>2063.6</v>
+        <v>1375.8</v>
       </c>
       <c r="K125" s="19" t="inlineStr">
         <is>
@@ -7359,7 +7356,7 @@
       </c>
       <c r="L125" s="5" t="inlineStr">
         <is>
-          <t>Indira Duarte</t>
+          <t>Diana Rojas</t>
         </is>
       </c>
     </row>
@@ -7371,7 +7368,7 @@
       </c>
       <c r="B126" s="12" t="inlineStr">
         <is>
-          <t>P2472</t>
+          <t>P2849</t>
         </is>
       </c>
       <c r="C126" s="12" t="inlineStr">
@@ -7381,7 +7378,7 @@
       </c>
       <c r="D126" s="13" t="inlineStr">
         <is>
-          <t>ADR - AI Auditoría Médica - Ret Other Vendors</t>
+          <t>ADR - peración Auditoria Cuentas Medicas - Ret Sw</t>
         </is>
       </c>
       <c r="E126" s="13" t="inlineStr">
@@ -7391,22 +7388,22 @@
       </c>
       <c r="F126" s="12" t="inlineStr">
         <is>
-          <t>Operación</t>
+          <t>Software SW</t>
         </is>
       </c>
       <c r="G126" s="12" t="inlineStr">
         <is>
-          <t>Ret Other Vendors</t>
+          <t>Ret Sw</t>
         </is>
       </c>
       <c r="H126" s="14" t="n">
-        <v>44.8</v>
+        <v>29.8</v>
       </c>
       <c r="I126" s="16" t="n">
-        <v>0.231</v>
+        <v>0.154</v>
       </c>
       <c r="J126" s="14" t="n">
-        <v>2063.6</v>
+        <v>1375.8</v>
       </c>
       <c r="K126" s="19" t="inlineStr">
         <is>
@@ -7415,7 +7412,7 @@
       </c>
       <c r="L126" s="11" t="inlineStr">
         <is>
-          <t>Indira Duarte</t>
+          <t>Diana Rojas</t>
         </is>
       </c>
     </row>
@@ -10565,16 +10562,16 @@
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A20:L20"/>
-    <mergeCell ref="A38:L38"/>
+    <mergeCell ref="A57:L57"/>
     <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A57:L57"/>
-    <mergeCell ref="A78:L78"/>
-    <mergeCell ref="A76:L76"/>
-    <mergeCell ref="A107:L107"/>
+    <mergeCell ref="A73:L73"/>
+    <mergeCell ref="A104:L104"/>
     <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A37:L37"/>
     <mergeCell ref="A5:L5"/>
+    <mergeCell ref="A75:L75"/>
+    <mergeCell ref="A119:L119"/>
     <mergeCell ref="A127:L127"/>
-    <mergeCell ref="A122:L122"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10704,16 +10701,16 @@
         <v>17</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D5" s="33" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>269.3</v>
+        <v>267.3</v>
       </c>
       <c r="F5" s="34" t="n">
-        <v>1.391012396694215</v>
+        <v>1.380681818181818</v>
       </c>
       <c r="G5" s="35" t="inlineStr">
         <is>
@@ -10725,7 +10722,7 @@
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>CSJ | FDN | HPL | IGM | MMN | SDH | UBO</t>
+          <t>CSJ | FDN | HPL | IGM | MMN | SDH</t>
         </is>
       </c>
     </row>
@@ -10739,16 +10736,16 @@
         <v>11</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6" s="37" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>153.9</v>
+        <v>155.9</v>
       </c>
       <c r="F6" s="30" t="n">
-        <v>0.7949380165289258</v>
+        <v>0.8052685950413224</v>
       </c>
       <c r="G6" s="31" t="inlineStr">
         <is>
@@ -10756,11 +10753,11 @@
         </is>
       </c>
       <c r="H6" s="38" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
-          <t>BID | CAT | MEN | SAN | SED | SEP</t>
+          <t>BID | CAT | MEN | SAN | SED | SEP | UBO</t>
         </is>
       </c>
     </row>
@@ -10774,16 +10771,16 @@
         <v>12</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D7" s="39" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>155.9</v>
+        <v>155.8</v>
       </c>
       <c r="F7" s="30" t="n">
-        <v>0.8052685950413224</v>
+        <v>0.8047520661157026</v>
       </c>
       <c r="G7" s="31" t="inlineStr">
         <is>
@@ -10914,24 +10911,24 @@
         <v>15</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D11" s="41" t="n">
-        <v>-11</v>
+        <v>7</v>
+      </c>
+      <c r="D11" s="33" t="n">
+        <v>-8</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>179.2</v>
-      </c>
-      <c r="F11" s="42" t="n">
-        <v>0.9256198347107437</v>
-      </c>
-      <c r="G11" s="43" t="inlineStr">
+        <v>179</v>
+      </c>
+      <c r="F11" s="41" t="n">
+        <v>0.9245867768595042</v>
+      </c>
+      <c r="G11" s="42" t="inlineStr">
         <is>
           <t>Carga Alta</t>
         </is>
       </c>
       <c r="H11" s="36" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
@@ -10975,13 +10972,13 @@
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="44" t="inlineStr">
+      <c r="A13" s="43" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="E13" s="45" t="n">
-        <v>1403</v>
+      <c r="E13" s="44" t="n">
+        <v>1402.7</v>
       </c>
     </row>
   </sheetData>
@@ -10999,7 +10996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -11019,7 +11016,7 @@
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="46" t="inlineStr">
+      <c r="A2" s="45" t="inlineStr">
         <is>
           <t>Los siguientes proyectos cambian de PM. Las horas estimadas se basan en el tiempo real registrado por el PM anterior en OpenAir (Marzo 2026).</t>
         </is>
@@ -11063,35 +11060,35 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="47" t="inlineStr">
+      <c r="A5" s="46" t="inlineStr">
         <is>
           <t>P2671</t>
         </is>
       </c>
-      <c r="B5" s="48" t="inlineStr">
+      <c r="B5" s="47" t="inlineStr">
         <is>
           <t>HPL - AWS Database Migration &amp; Modernization - Fixed</t>
         </is>
       </c>
-      <c r="C5" s="48" t="inlineStr">
+      <c r="C5" s="47" t="inlineStr">
         <is>
           <t xml:space="preserve">HotelPlanner </t>
         </is>
       </c>
-      <c r="D5" s="49" t="inlineStr">
+      <c r="D5" s="48" t="inlineStr">
         <is>
           <t>Miguel Garcia</t>
         </is>
       </c>
-      <c r="E5" s="50" t="inlineStr">
+      <c r="E5" s="49" t="inlineStr">
         <is>
           <t>David Cortes</t>
         </is>
       </c>
-      <c r="F5" s="51" t="n">
+      <c r="F5" s="50" t="n">
         <v>25</v>
       </c>
-      <c r="G5" s="48" t="inlineStr">
+      <c r="G5" s="47" t="inlineStr">
         <is>
           <t>Alineación con portafolio infraestructura cloud</t>
         </is>
@@ -11113,12 +11110,12 @@
           <t xml:space="preserve">HotelPlanner </t>
         </is>
       </c>
-      <c r="D6" s="52" t="inlineStr">
+      <c r="D6" s="51" t="inlineStr">
         <is>
           <t>Miguel Garcia</t>
         </is>
       </c>
-      <c r="E6" s="53" t="inlineStr">
+      <c r="E6" s="52" t="inlineStr">
         <is>
           <t>David Cortes</t>
         </is>
@@ -11133,35 +11130,35 @@
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="47" t="inlineStr">
+      <c r="A7" s="46" t="inlineStr">
         <is>
           <t>P2611</t>
         </is>
       </c>
-      <c r="B7" s="48" t="inlineStr">
+      <c r="B7" s="47" t="inlineStr">
         <is>
           <t>MEN - Operacion en AWS - Fixed</t>
         </is>
       </c>
-      <c r="C7" s="48" t="inlineStr">
+      <c r="C7" s="47" t="inlineStr">
         <is>
           <t>Ministerio de educación Nacional</t>
         </is>
       </c>
-      <c r="D7" s="49" t="inlineStr">
+      <c r="D7" s="48" t="inlineStr">
         <is>
           <t>Miguel Garcia</t>
         </is>
       </c>
-      <c r="E7" s="50" t="inlineStr">
+      <c r="E7" s="49" t="inlineStr">
         <is>
           <t>Diana Castro</t>
         </is>
       </c>
-      <c r="F7" s="51" t="n">
+      <c r="F7" s="50" t="n">
         <v>5.7</v>
       </c>
-      <c r="G7" s="48" t="inlineStr">
+      <c r="G7" s="47" t="inlineStr">
         <is>
           <t>Alineación con portafolio Educación</t>
         </is>
@@ -11183,12 +11180,12 @@
           <t>Ministerio de educación Nacional</t>
         </is>
       </c>
-      <c r="D8" s="52" t="inlineStr">
+      <c r="D8" s="51" t="inlineStr">
         <is>
           <t>Miguel Garcia</t>
         </is>
       </c>
-      <c r="E8" s="53" t="inlineStr">
+      <c r="E8" s="52" t="inlineStr">
         <is>
           <t>Diana Castro</t>
         </is>
@@ -11203,35 +11200,35 @@
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="47" t="inlineStr">
+      <c r="A9" s="46" t="inlineStr">
         <is>
           <t>P2634</t>
         </is>
       </c>
-      <c r="B9" s="48" t="inlineStr">
+      <c r="B9" s="47" t="inlineStr">
         <is>
           <t>MEN - Operacion en AWS - Cloud</t>
         </is>
       </c>
-      <c r="C9" s="48" t="inlineStr">
+      <c r="C9" s="47" t="inlineStr">
         <is>
           <t>Ministerio de educación Nacional</t>
         </is>
       </c>
-      <c r="D9" s="49" t="inlineStr">
+      <c r="D9" s="48" t="inlineStr">
         <is>
           <t>Miguel Garcia</t>
         </is>
       </c>
-      <c r="E9" s="50" t="inlineStr">
+      <c r="E9" s="49" t="inlineStr">
         <is>
           <t>Diana Castro</t>
         </is>
       </c>
-      <c r="F9" s="51" t="n">
+      <c r="F9" s="50" t="n">
         <v>5.7</v>
       </c>
-      <c r="G9" s="48" t="inlineStr">
+      <c r="G9" s="47" t="inlineStr">
         <is>
           <t>Alineación con portafolio Educación</t>
         </is>
@@ -11253,12 +11250,12 @@
           <t>Secretaría de Educación del Distrito</t>
         </is>
       </c>
-      <c r="D10" s="52" t="inlineStr">
+      <c r="D10" s="51" t="inlineStr">
         <is>
           <t>Miguel Garcia</t>
         </is>
       </c>
-      <c r="E10" s="53" t="inlineStr">
+      <c r="E10" s="52" t="inlineStr">
         <is>
           <t>Diana Castro</t>
         </is>
@@ -11273,35 +11270,35 @@
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="47" t="inlineStr">
+      <c r="A11" s="46" t="inlineStr">
         <is>
           <t>P2561</t>
         </is>
       </c>
-      <c r="B11" s="48" t="inlineStr">
+      <c r="B11" s="47" t="inlineStr">
         <is>
           <t>SED - Automatización procesos seguros, adquisiciones y accidentes  - Ret</t>
         </is>
       </c>
-      <c r="C11" s="48" t="inlineStr">
+      <c r="C11" s="47" t="inlineStr">
         <is>
           <t>Secretaría de Educación del Distrito</t>
         </is>
       </c>
-      <c r="D11" s="49" t="inlineStr">
+      <c r="D11" s="48" t="inlineStr">
         <is>
           <t>Miguel Garcia</t>
         </is>
       </c>
-      <c r="E11" s="50" t="inlineStr">
+      <c r="E11" s="49" t="inlineStr">
         <is>
           <t>Diana Castro</t>
         </is>
       </c>
-      <c r="F11" s="51" t="n">
+      <c r="F11" s="50" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="G11" s="48" t="inlineStr">
+      <c r="G11" s="47" t="inlineStr">
         <is>
           <t>Alineación con portafolio Educación</t>
         </is>
@@ -11323,12 +11320,12 @@
           <t>Secretaría de Educación del Distrito</t>
         </is>
       </c>
-      <c r="D12" s="52" t="inlineStr">
+      <c r="D12" s="51" t="inlineStr">
         <is>
           <t>Miguel Garcia</t>
         </is>
       </c>
-      <c r="E12" s="53" t="inlineStr">
+      <c r="E12" s="52" t="inlineStr">
         <is>
           <t>Diana Castro</t>
         </is>
@@ -11343,35 +11340,35 @@
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="47" t="inlineStr">
+      <c r="A13" s="46" t="inlineStr">
         <is>
           <t>P2563</t>
         </is>
       </c>
-      <c r="B13" s="48" t="inlineStr">
+      <c r="B13" s="47" t="inlineStr">
         <is>
           <t>SED - Automatización procesos seguros, adquisiciones y accidentes  - Cloud</t>
         </is>
       </c>
-      <c r="C13" s="48" t="inlineStr">
+      <c r="C13" s="47" t="inlineStr">
         <is>
           <t>Secretaría de Educación del Distrito</t>
         </is>
       </c>
-      <c r="D13" s="49" t="inlineStr">
+      <c r="D13" s="48" t="inlineStr">
         <is>
           <t>Miguel Garcia</t>
         </is>
       </c>
-      <c r="E13" s="50" t="inlineStr">
+      <c r="E13" s="49" t="inlineStr">
         <is>
           <t>Diana Castro</t>
         </is>
       </c>
-      <c r="F13" s="51" t="n">
+      <c r="F13" s="50" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="G13" s="48" t="inlineStr">
+      <c r="G13" s="47" t="inlineStr">
         <is>
           <t>Alineación con portafolio Educación</t>
         </is>
@@ -11380,68 +11377,68 @@
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="12" t="inlineStr">
         <is>
+          <t>P1968</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>UBO - Operación Cloud - Cloud</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>UBosque</t>
+        </is>
+      </c>
+      <c r="D14" s="51" t="inlineStr">
+        <is>
+          <t>David Cortes</t>
+        </is>
+      </c>
+      <c r="E14" s="52" t="inlineStr">
+        <is>
+          <t>Diana Castro</t>
+        </is>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" s="13" t="inlineStr">
+        <is>
+          <t>Alineación con portafolio Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="46" t="inlineStr">
+        <is>
           <t>P2723</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B15" s="47" t="inlineStr">
         <is>
           <t>SPD - Renovacion observatorio de datos- - Fixed</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C15" s="47" t="inlineStr">
         <is>
           <t>Superintendencia Servicios Públicos Domiciliarios</t>
         </is>
       </c>
-      <c r="D14" s="52" t="inlineStr">
+      <c r="D15" s="48" t="inlineStr">
         <is>
           <t>Miguel Garcia</t>
         </is>
       </c>
-      <c r="E14" s="53" t="inlineStr">
+      <c r="E15" s="49" t="inlineStr">
         <is>
           <t>Diana Rojas</t>
         </is>
       </c>
-      <c r="F14" s="14" t="n">
+      <c r="F15" s="50" t="n">
         <v>6.2</v>
       </c>
-      <c r="G14" s="13" t="inlineStr">
-        <is>
-          <t>Agrupación de proyectos de datos/observatorios</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="47" t="inlineStr">
-        <is>
-          <t>P2724</t>
-        </is>
-      </c>
-      <c r="B15" s="48" t="inlineStr">
-        <is>
-          <t>SPD - Renovacion observatorio de datos- - Ret SW</t>
-        </is>
-      </c>
-      <c r="C15" s="48" t="inlineStr">
-        <is>
-          <t>Superintendencia Servicios Públicos Domiciliarios</t>
-        </is>
-      </c>
-      <c r="D15" s="49" t="inlineStr">
-        <is>
-          <t>Miguel Garcia</t>
-        </is>
-      </c>
-      <c r="E15" s="50" t="inlineStr">
-        <is>
-          <t>Diana Rojas</t>
-        </is>
-      </c>
-      <c r="F15" s="51" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="G15" s="48" t="inlineStr">
+      <c r="G15" s="47" t="inlineStr">
         <is>
           <t>Agrupación de proyectos de datos/observatorios</t>
         </is>
@@ -11450,12 +11447,12 @@
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>P2725</t>
+          <t>P2724</t>
         </is>
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>SPD - Renovacion observatorio de datos- - Cloud</t>
+          <t>SPD - Renovacion observatorio de datos- - Ret SW</t>
         </is>
       </c>
       <c r="C16" s="13" t="inlineStr">
@@ -11463,12 +11460,12 @@
           <t>Superintendencia Servicios Públicos Domiciliarios</t>
         </is>
       </c>
-      <c r="D16" s="52" t="inlineStr">
+      <c r="D16" s="51" t="inlineStr">
         <is>
           <t>Miguel Garcia</t>
         </is>
       </c>
-      <c r="E16" s="53" t="inlineStr">
+      <c r="E16" s="52" t="inlineStr">
         <is>
           <t>Diana Rojas</t>
         </is>
@@ -11483,35 +11480,35 @@
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="47" t="inlineStr">
-        <is>
-          <t>P2726</t>
-        </is>
-      </c>
-      <c r="B17" s="48" t="inlineStr">
-        <is>
-          <t>SPD - Renovacion observatorio de datos- - Ret</t>
-        </is>
-      </c>
-      <c r="C17" s="48" t="inlineStr">
+      <c r="A17" s="46" t="inlineStr">
+        <is>
+          <t>P2725</t>
+        </is>
+      </c>
+      <c r="B17" s="47" t="inlineStr">
+        <is>
+          <t>SPD - Renovacion observatorio de datos- - Cloud</t>
+        </is>
+      </c>
+      <c r="C17" s="47" t="inlineStr">
         <is>
           <t>Superintendencia Servicios Públicos Domiciliarios</t>
         </is>
       </c>
-      <c r="D17" s="49" t="inlineStr">
+      <c r="D17" s="48" t="inlineStr">
         <is>
           <t>Miguel Garcia</t>
         </is>
       </c>
-      <c r="E17" s="50" t="inlineStr">
+      <c r="E17" s="49" t="inlineStr">
         <is>
           <t>Diana Rojas</t>
         </is>
       </c>
-      <c r="F17" s="51" t="n">
+      <c r="F17" s="50" t="n">
         <v>6.2</v>
       </c>
-      <c r="G17" s="48" t="inlineStr">
+      <c r="G17" s="47" t="inlineStr">
         <is>
           <t>Agrupación de proyectos de datos/observatorios</t>
         </is>
@@ -11520,68 +11517,68 @@
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="12" t="inlineStr">
         <is>
+          <t>P2726</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>SPD - Renovacion observatorio de datos- - Ret</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>Superintendencia Servicios Públicos Domiciliarios</t>
+        </is>
+      </c>
+      <c r="D18" s="51" t="inlineStr">
+        <is>
+          <t>Miguel Garcia</t>
+        </is>
+      </c>
+      <c r="E18" s="52" t="inlineStr">
+        <is>
+          <t>Diana Rojas</t>
+        </is>
+      </c>
+      <c r="F18" s="14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="G18" s="13" t="inlineStr">
+        <is>
+          <t>Agrupación de proyectos de datos/observatorios</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="46" t="inlineStr">
+        <is>
           <t>P1966</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B19" s="47" t="inlineStr">
         <is>
           <t>SPD - Repositorio Único de Datos - Ret SW</t>
         </is>
       </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="C19" s="47" t="inlineStr">
         <is>
           <t>Superintendencia Servicios Públicos Domiciliarios</t>
         </is>
       </c>
-      <c r="D18" s="52" t="inlineStr">
+      <c r="D19" s="48" t="inlineStr">
         <is>
           <t>Miguel Garcia</t>
         </is>
       </c>
-      <c r="E18" s="53" t="inlineStr">
+      <c r="E19" s="49" t="inlineStr">
         <is>
           <t>Diana Rojas</t>
         </is>
       </c>
-      <c r="F18" s="14" t="n">
+      <c r="F19" s="50" t="n">
         <v>12.5</v>
       </c>
-      <c r="G18" s="13" t="inlineStr">
-        <is>
-          <t>Agrupación de proyectos de datos/observatorios</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="47" t="inlineStr">
-        <is>
-          <t>P1967</t>
-        </is>
-      </c>
-      <c r="B19" s="48" t="inlineStr">
-        <is>
-          <t>SPD - Repositorio Único de Datos - Cloud</t>
-        </is>
-      </c>
-      <c r="C19" s="48" t="inlineStr">
-        <is>
-          <t>Superintendencia Servicios Públicos Domiciliarios</t>
-        </is>
-      </c>
-      <c r="D19" s="49" t="inlineStr">
-        <is>
-          <t>Miguel Garcia</t>
-        </is>
-      </c>
-      <c r="E19" s="50" t="inlineStr">
-        <is>
-          <t>Diana Rojas</t>
-        </is>
-      </c>
-      <c r="F19" s="51" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="G19" s="48" t="inlineStr">
+      <c r="G19" s="47" t="inlineStr">
         <is>
           <t>Agrupación de proyectos de datos/observatorios</t>
         </is>
@@ -11590,68 +11587,68 @@
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="12" t="inlineStr">
         <is>
+          <t>P1967</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>SPD - Repositorio Único de Datos - Cloud</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>Superintendencia Servicios Públicos Domiciliarios</t>
+        </is>
+      </c>
+      <c r="D20" s="51" t="inlineStr">
+        <is>
+          <t>Miguel Garcia</t>
+        </is>
+      </c>
+      <c r="E20" s="52" t="inlineStr">
+        <is>
+          <t>Diana Rojas</t>
+        </is>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G20" s="13" t="inlineStr">
+        <is>
+          <t>Agrupación de proyectos de datos/observatorios</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="46" t="inlineStr">
+        <is>
           <t>P1947</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B21" s="47" t="inlineStr">
         <is>
           <t>JPM - Cloud Managed Services 2023-25 - Ret</t>
         </is>
       </c>
-      <c r="C20" s="13" t="inlineStr">
+      <c r="C21" s="47" t="inlineStr">
         <is>
           <t>JPMP - Justicia Penal Militar y Policial</t>
         </is>
       </c>
-      <c r="D20" s="52" t="inlineStr">
+      <c r="D21" s="48" t="inlineStr">
         <is>
           <t>David Cortes</t>
         </is>
       </c>
-      <c r="E20" s="53" t="inlineStr">
+      <c r="E21" s="49" t="inlineStr">
         <is>
           <t>Juan Bernal</t>
         </is>
       </c>
-      <c r="F20" s="14" t="n">
+      <c r="F21" s="50" t="n">
         <v>13.5</v>
       </c>
-      <c r="G20" s="13" t="inlineStr">
-        <is>
-          <t>Alineación con portafolio cloud managed services</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="47" t="inlineStr">
-        <is>
-          <t>P1948</t>
-        </is>
-      </c>
-      <c r="B21" s="48" t="inlineStr">
-        <is>
-          <t>JPM - Cloud Managed Services 2023-25 - Cloud</t>
-        </is>
-      </c>
-      <c r="C21" s="48" t="inlineStr">
-        <is>
-          <t>JPMP - Justicia Penal Militar y Policial</t>
-        </is>
-      </c>
-      <c r="D21" s="49" t="inlineStr">
-        <is>
-          <t>David Cortes</t>
-        </is>
-      </c>
-      <c r="E21" s="50" t="inlineStr">
-        <is>
-          <t>Juan Bernal</t>
-        </is>
-      </c>
-      <c r="F21" s="51" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="G21" s="48" t="inlineStr">
+      <c r="G21" s="47" t="inlineStr">
         <is>
           <t>Alineación con portafolio cloud managed services</t>
         </is>
@@ -11660,68 +11657,68 @@
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="12" t="inlineStr">
         <is>
+          <t>P1948</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>JPM - Cloud Managed Services 2023-25 - Cloud</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>JPMP - Justicia Penal Militar y Policial</t>
+        </is>
+      </c>
+      <c r="D22" s="51" t="inlineStr">
+        <is>
+          <t>David Cortes</t>
+        </is>
+      </c>
+      <c r="E22" s="52" t="inlineStr">
+        <is>
+          <t>Juan Bernal</t>
+        </is>
+      </c>
+      <c r="F22" s="14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="G22" s="13" t="inlineStr">
+        <is>
+          <t>Alineación con portafolio cloud managed services</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="46" t="inlineStr">
+        <is>
           <t>P2457</t>
         </is>
       </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B23" s="47" t="inlineStr">
         <is>
           <t>ADR - AI Auditoría Médica - Fixed</t>
         </is>
       </c>
-      <c r="C22" s="13" t="inlineStr">
+      <c r="C23" s="47" t="inlineStr">
         <is>
           <t>La Administradora de los Recursos del Sistema General de Seguridad Social en Salud</t>
         </is>
       </c>
-      <c r="D22" s="52" t="inlineStr">
+      <c r="D23" s="48" t="inlineStr">
         <is>
           <t>Indira Duarte</t>
         </is>
       </c>
-      <c r="E22" s="53" t="inlineStr">
+      <c r="E23" s="49" t="inlineStr">
         <is>
           <t>Miguel Garcia</t>
         </is>
       </c>
-      <c r="F22" s="14" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="G22" s="13" t="inlineStr">
-        <is>
-          <t>Reasignación para balancear carga y alinear especialidad</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="47" t="inlineStr">
-        <is>
-          <t>P2470</t>
-        </is>
-      </c>
-      <c r="B23" s="48" t="inlineStr">
-        <is>
-          <t>ADR - AI Auditoría Médica - Cloud</t>
-        </is>
-      </c>
-      <c r="C23" s="48" t="inlineStr">
-        <is>
-          <t>La Administradora de los Recursos del Sistema General de Seguridad Social en Salud</t>
-        </is>
-      </c>
-      <c r="D23" s="49" t="inlineStr">
-        <is>
-          <t>Indira Duarte</t>
-        </is>
-      </c>
-      <c r="E23" s="50" t="inlineStr">
-        <is>
-          <t>Miguel Garcia</t>
-        </is>
-      </c>
-      <c r="F23" s="51" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="G23" s="48" t="inlineStr">
+      <c r="F23" s="50" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="G23" s="47" t="inlineStr">
         <is>
           <t>Reasignación para balancear carga y alinear especialidad</t>
         </is>
@@ -11730,68 +11727,208 @@
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="12" t="inlineStr">
         <is>
+          <t>P2470</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>ADR - AI Auditoría Médica - Cloud</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>La Administradora de los Recursos del Sistema General de Seguridad Social en Salud</t>
+        </is>
+      </c>
+      <c r="D24" s="51" t="inlineStr">
+        <is>
+          <t>Indira Duarte</t>
+        </is>
+      </c>
+      <c r="E24" s="52" t="inlineStr">
+        <is>
+          <t>Miguel Garcia</t>
+        </is>
+      </c>
+      <c r="F24" s="14" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="G24" s="13" t="inlineStr">
+        <is>
+          <t>Reasignación para balancear carga y alinear especialidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="46" t="inlineStr">
+        <is>
           <t>P2471</t>
         </is>
       </c>
-      <c r="B24" s="13" t="inlineStr">
+      <c r="B25" s="47" t="inlineStr">
         <is>
           <t>ADR - AI Auditoría Médica - Ret Sw</t>
         </is>
       </c>
-      <c r="C24" s="13" t="inlineStr">
+      <c r="C25" s="47" t="inlineStr">
         <is>
           <t>La Administradora de los Recursos del Sistema General de Seguridad Social en Salud</t>
         </is>
       </c>
-      <c r="D24" s="52" t="inlineStr">
+      <c r="D25" s="48" t="inlineStr">
         <is>
           <t>Indira Duarte</t>
         </is>
       </c>
-      <c r="E24" s="53" t="inlineStr">
+      <c r="E25" s="49" t="inlineStr">
         <is>
           <t>Miguel Garcia</t>
         </is>
       </c>
-      <c r="F24" s="14" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="G24" s="13" t="inlineStr">
+      <c r="F25" s="50" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="G25" s="47" t="inlineStr">
         <is>
           <t>Reasignación para balancear carga y alinear especialidad</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="47" t="inlineStr">
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>P2472</t>
         </is>
       </c>
-      <c r="B25" s="48" t="inlineStr">
+      <c r="B26" s="13" t="inlineStr">
         <is>
           <t>ADR - AI Auditoría Médica - Ret Other Vendors</t>
         </is>
       </c>
-      <c r="C25" s="48" t="inlineStr">
+      <c r="C26" s="13" t="inlineStr">
         <is>
           <t>La Administradora de los Recursos del Sistema General de Seguridad Social en Salud</t>
         </is>
       </c>
-      <c r="D25" s="49" t="inlineStr">
+      <c r="D26" s="51" t="inlineStr">
         <is>
           <t>Indira Duarte</t>
         </is>
       </c>
-      <c r="E25" s="50" t="inlineStr">
+      <c r="E26" s="52" t="inlineStr">
         <is>
           <t>Miguel Garcia</t>
         </is>
       </c>
-      <c r="F25" s="51" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="G25" s="48" t="inlineStr">
+      <c r="F26" s="14" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="G26" s="13" t="inlineStr">
+        <is>
+          <t>Reasignación para balancear carga y alinear especialidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="46" t="inlineStr">
+        <is>
+          <t>P2847</t>
+        </is>
+      </c>
+      <c r="B27" s="47" t="inlineStr">
+        <is>
+          <t>ADR - peración Auditoria Cuentas Medicas - Ret</t>
+        </is>
+      </c>
+      <c r="C27" s="47" t="inlineStr">
+        <is>
+          <t>La Administradora de los Recursos del Sistema General de Seguridad Social en Salud</t>
+        </is>
+      </c>
+      <c r="D27" s="48" t="inlineStr">
+        <is>
+          <t>Diana Rojas</t>
+        </is>
+      </c>
+      <c r="E27" s="49" t="inlineStr">
+        <is>
+          <t>Miguel Garcia</t>
+        </is>
+      </c>
+      <c r="F27" s="50" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="G27" s="47" t="inlineStr">
+        <is>
+          <t>Reasignación para balancear carga y alinear especialidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>P2848</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>ADR - peración Auditoria Cuentas Medicas - Cloud</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>La Administradora de los Recursos del Sistema General de Seguridad Social en Salud</t>
+        </is>
+      </c>
+      <c r="D28" s="51" t="inlineStr">
+        <is>
+          <t>Diana Rojas</t>
+        </is>
+      </c>
+      <c r="E28" s="52" t="inlineStr">
+        <is>
+          <t>Miguel Garcia</t>
+        </is>
+      </c>
+      <c r="F28" s="14" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="G28" s="13" t="inlineStr">
+        <is>
+          <t>Reasignación para balancear carga y alinear especialidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="46" t="inlineStr">
+        <is>
+          <t>P2849</t>
+        </is>
+      </c>
+      <c r="B29" s="47" t="inlineStr">
+        <is>
+          <t>ADR - peración Auditoria Cuentas Medicas - Ret Sw</t>
+        </is>
+      </c>
+      <c r="C29" s="47" t="inlineStr">
+        <is>
+          <t>La Administradora de los Recursos del Sistema General de Seguridad Social en Salud</t>
+        </is>
+      </c>
+      <c r="D29" s="48" t="inlineStr">
+        <is>
+          <t>Diana Rojas</t>
+        </is>
+      </c>
+      <c r="E29" s="49" t="inlineStr">
+        <is>
+          <t>Miguel Garcia</t>
+        </is>
+      </c>
+      <c r="F29" s="50" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="G29" s="47" t="inlineStr">
         <is>
           <t>Reasignación para balancear carga y alinear especialidad</t>
         </is>
@@ -11826,35 +11963,35 @@
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="54" t="inlineStr">
+      <c r="A2" s="53" t="inlineStr">
         <is>
           <t>Antes vs Después: Horas de gestión PM por mes</t>
         </is>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="54" t="inlineStr">
+      <c r="A30" s="53" t="inlineStr">
         <is>
           <t>Número de proyectos: Actual vs Propuesto</t>
         </is>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
-      <c r="A58" s="54" t="inlineStr">
+      <c r="A58" s="53" t="inlineStr">
         <is>
           <t>Utilización de capacidad – Propuesta</t>
         </is>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1">
-      <c r="A82" s="54" t="inlineStr">
+      <c r="A82" s="53" t="inlineStr">
         <is>
           <t>Distribución de horas por cliente (apilado)</t>
         </is>
       </c>
     </row>
     <row r="116" ht="18" customHeight="1">
-      <c r="A116" s="54" t="inlineStr">
+      <c r="A116" s="53" t="inlineStr">
         <is>
           <t>Proyectos reasignados – Horas estimadas</t>
         </is>
